--- a/Data/FlightPlan/FPL_18OCT26.xlsx
+++ b/Data/FlightPlan/FPL_18OCT26.xlsx
@@ -104,6 +104,402 @@
     <t>09:00</t>
   </si>
   <si>
+    <t>RMQ</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>KIX</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>VN-A202</t>
+  </si>
+  <si>
+    <t>09:30</t>
+  </si>
+  <si>
+    <t>13:05</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>16:50</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>PQC</t>
+  </si>
+  <si>
+    <t>22:10</t>
+  </si>
+  <si>
+    <t>PUS</t>
+  </si>
+  <si>
+    <t>23:10</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>VN-A203</t>
+  </si>
+  <si>
+    <t>DPS</t>
+  </si>
+  <si>
+    <t>08:45</t>
+  </si>
+  <si>
+    <t>13:35</t>
+  </si>
+  <si>
+    <t>14:35</t>
+  </si>
+  <si>
+    <t>17:25</t>
+  </si>
+  <si>
+    <t>BLR</t>
+  </si>
+  <si>
+    <t>19:20</t>
+  </si>
+  <si>
+    <t>22:35</t>
+  </si>
+  <si>
+    <t>23:35</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>VN-A500</t>
+  </si>
+  <si>
+    <t>NGO</t>
+  </si>
+  <si>
+    <t>09:25</t>
+  </si>
+  <si>
+    <t>12:50</t>
+  </si>
+  <si>
+    <t>KHH</t>
+  </si>
+  <si>
+    <t>17:50</t>
+  </si>
+  <si>
+    <t>18:50</t>
+  </si>
+  <si>
+    <t>20:35</t>
+  </si>
+  <si>
+    <t>VN-A521</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>14:40</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>20:20</t>
+  </si>
+  <si>
+    <t>01:40</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>VN-A526</t>
+  </si>
+  <si>
+    <t>CXR</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>TPE</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>03:10</t>
+  </si>
+  <si>
+    <t>09:50</t>
+  </si>
+  <si>
+    <t>VN-A528</t>
+  </si>
+  <si>
+    <t>THD</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>08:50</t>
+  </si>
+  <si>
+    <t>09:20</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>11:55</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>14:50</t>
+  </si>
+  <si>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>VN-A529</t>
+  </si>
+  <si>
+    <t>12:20</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>19:50</t>
+  </si>
+  <si>
+    <t>01:20</t>
+  </si>
+  <si>
+    <t>07:50</t>
+  </si>
+  <si>
+    <t>VN-A530</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>09:35</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>11:10</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>VN-A532</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>ICN</t>
+  </si>
+  <si>
+    <t>19:25</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>21:05</t>
+  </si>
+  <si>
+    <t>21:15</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>02:35</t>
+  </si>
+  <si>
+    <t>09:40</t>
+  </si>
+  <si>
+    <t>VN-A534</t>
+  </si>
+  <si>
+    <t>VDH</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>08:40</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>DAD</t>
+  </si>
+  <si>
+    <t>10:55</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>21:55</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>01:35</t>
+  </si>
+  <si>
+    <t>VN-A535</t>
+  </si>
+  <si>
+    <t>12:55</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>19:45</t>
+  </si>
+  <si>
+    <t>VN-A536</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>07:35</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>16:25</t>
+  </si>
+  <si>
+    <t>18:20</t>
+  </si>
+  <si>
+    <t>19:30</t>
+  </si>
+  <si>
+    <t>20:50</t>
+  </si>
+  <si>
+    <t>22:40</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
     <t>CGK</t>
   </si>
   <si>
@@ -113,405 +509,9 @@
     <t>12:40</t>
   </si>
   <si>
-    <t>13:30</t>
-  </si>
-  <si>
     <t>16:40</t>
   </si>
   <si>
-    <t>KIX</t>
-  </si>
-  <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>08:30</t>
-  </si>
-  <si>
-    <t>VN-A202</t>
-  </si>
-  <si>
-    <t>09:30</t>
-  </si>
-  <si>
-    <t>13:05</t>
-  </si>
-  <si>
-    <t>14:05</t>
-  </si>
-  <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>16:50</t>
-  </si>
-  <si>
-    <t>19:00</t>
-  </si>
-  <si>
-    <t>PQC</t>
-  </si>
-  <si>
-    <t>22:10</t>
-  </si>
-  <si>
-    <t>PUS</t>
-  </si>
-  <si>
-    <t>23:10</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>VN-A203</t>
-  </si>
-  <si>
-    <t>DPS</t>
-  </si>
-  <si>
-    <t>08:45</t>
-  </si>
-  <si>
-    <t>13:35</t>
-  </si>
-  <si>
-    <t>14:35</t>
-  </si>
-  <si>
-    <t>17:25</t>
-  </si>
-  <si>
-    <t>BLR</t>
-  </si>
-  <si>
-    <t>19:20</t>
-  </si>
-  <si>
-    <t>22:35</t>
-  </si>
-  <si>
-    <t>23:35</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>VN-A500</t>
-  </si>
-  <si>
-    <t>NGO</t>
-  </si>
-  <si>
-    <t>09:25</t>
-  </si>
-  <si>
-    <t>12:50</t>
-  </si>
-  <si>
-    <t>KHH</t>
-  </si>
-  <si>
-    <t>17:50</t>
-  </si>
-  <si>
-    <t>18:50</t>
-  </si>
-  <si>
-    <t>20:35</t>
-  </si>
-  <si>
-    <t>VN-A521</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>14:40</t>
-  </si>
-  <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>20:20</t>
-  </si>
-  <si>
-    <t>01:40</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>VN-A526</t>
-  </si>
-  <si>
-    <t>CXR</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>TPE</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>03:10</t>
-  </si>
-  <si>
-    <t>09:50</t>
-  </si>
-  <si>
-    <t>VN-A528</t>
-  </si>
-  <si>
-    <t>THD</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>08:50</t>
-  </si>
-  <si>
-    <t>09:20</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>10:50</t>
-  </si>
-  <si>
-    <t>11:55</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>14:50</t>
-  </si>
-  <si>
-    <t>21:20</t>
-  </si>
-  <si>
-    <t>VN-A529</t>
-  </si>
-  <si>
-    <t>12:20</t>
-  </si>
-  <si>
-    <t>RMQ</t>
-  </si>
-  <si>
-    <t>19:50</t>
-  </si>
-  <si>
-    <t>01:20</t>
-  </si>
-  <si>
-    <t>07:50</t>
-  </si>
-  <si>
-    <t>VN-A530</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>09:35</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>11:10</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>PXU</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>VN-A532</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>ICN</t>
-  </si>
-  <si>
-    <t>19:25</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>21:05</t>
-  </si>
-  <si>
-    <t>21:15</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>02:35</t>
-  </si>
-  <si>
-    <t>09:40</t>
-  </si>
-  <si>
-    <t>VN-A534</t>
-  </si>
-  <si>
-    <t>VDH</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>08:10</t>
-  </si>
-  <si>
-    <t>08:40</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>DAD</t>
-  </si>
-  <si>
-    <t>10:55</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>17:30</t>
-  </si>
-  <si>
-    <t>21:55</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>01:35</t>
-  </si>
-  <si>
-    <t>VN-A535</t>
-  </si>
-  <si>
-    <t>12:55</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>19:45</t>
-  </si>
-  <si>
-    <t>VN-A536</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>07:35</t>
-  </si>
-  <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>14:30</t>
-  </si>
-  <si>
-    <t>15:05</t>
-  </si>
-  <si>
-    <t>16:25</t>
-  </si>
-  <si>
-    <t>18:20</t>
-  </si>
-  <si>
-    <t>19:30</t>
-  </si>
-  <si>
-    <t>20:50</t>
-  </si>
-  <si>
-    <t>22:40</t>
-  </si>
-  <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
     <t>BOM</t>
   </si>
   <si>
@@ -638,6 +638,9 @@
     <t>04:05</t>
   </si>
   <si>
+    <t>07:59</t>
+  </si>
+  <si>
     <t>HUI</t>
   </si>
   <si>
@@ -1193,7 +1196,7 @@
     <t>Total Record(s): 361</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 18, 2026 00:19</t>
+    <t xml:space="preserve">Generated on  Oct 18, 2026 01:57</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -1927,7 +1930,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="7">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c t="s" r="C13" s="7">
         <v>14</v>
@@ -1960,7 +1963,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="7">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c t="s" r="C14" s="7">
         <v>14</v>
@@ -1979,10 +1982,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I14" s="7">
+        <v>19</v>
+      </c>
+      <c t="s" r="J14" s="7">
         <v>34</v>
-      </c>
-      <c t="s" r="J14" s="7">
-        <v>35</v>
       </c>
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
@@ -2009,13 +2012,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H15" s="8">
+        <v>35</v>
+      </c>
+      <c t="s" r="I15" s="7">
         <v>36</v>
       </c>
-      <c t="s" r="I15" s="7">
+      <c t="s" r="J15" s="7">
         <v>37</v>
-      </c>
-      <c t="s" r="J15" s="7">
-        <v>38</v>
       </c>
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
@@ -2048,7 +2051,7 @@
       </c>
       <c r="D17" s="7"/>
       <c t="s" r="E17" s="7">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F17" s="7">
         <v>321</v>
@@ -2060,10 +2063,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I17" s="7">
+        <v>39</v>
+      </c>
+      <c t="s" r="J17" s="7">
         <v>40</v>
-      </c>
-      <c t="s" r="J17" s="7">
-        <v>41</v>
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
@@ -2081,7 +2084,7 @@
       </c>
       <c r="D18" s="7"/>
       <c t="s" r="E18" s="7">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F18" s="7">
         <v>321</v>
@@ -2093,10 +2096,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I18" s="7">
+        <v>41</v>
+      </c>
+      <c t="s" r="J18" s="7">
         <v>42</v>
-      </c>
-      <c t="s" r="J18" s="7">
-        <v>43</v>
       </c>
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
@@ -2114,7 +2117,7 @@
       </c>
       <c r="D19" s="7"/>
       <c t="s" r="E19" s="7">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F19" s="7">
         <v>321</v>
@@ -2126,10 +2129,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I19" s="7">
+        <v>43</v>
+      </c>
+      <c t="s" r="J19" s="7">
         <v>44</v>
-      </c>
-      <c t="s" r="J19" s="7">
-        <v>45</v>
       </c>
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
@@ -2147,7 +2150,7 @@
       </c>
       <c r="D20" s="7"/>
       <c t="s" r="E20" s="7">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F20" s="7">
         <v>321</v>
@@ -2156,13 +2159,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H20" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="I20" s="7">
         <v>21</v>
       </c>
       <c t="s" r="J20" s="7">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
@@ -2180,22 +2183,22 @@
       </c>
       <c r="D21" s="7"/>
       <c t="s" r="E21" s="7">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F21" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G21" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="H21" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="I21" s="7">
         <v>48</v>
       </c>
-      <c t="s" r="I21" s="7">
+      <c t="s" r="J21" s="7">
         <v>49</v>
-      </c>
-      <c t="s" r="J21" s="7">
-        <v>50</v>
       </c>
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
@@ -2228,22 +2231,22 @@
       </c>
       <c r="D23" s="7"/>
       <c t="s" r="E23" s="7">
+        <v>50</v>
+      </c>
+      <c r="F23" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G23" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H23" s="8">
         <v>51</v>
       </c>
-      <c r="F23" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G23" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="H23" s="8">
+      <c t="s" r="I23" s="7">
         <v>52</v>
       </c>
-      <c t="s" r="I23" s="7">
+      <c t="s" r="J23" s="7">
         <v>53</v>
-      </c>
-      <c t="s" r="J23" s="7">
-        <v>54</v>
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
@@ -2261,22 +2264,22 @@
       </c>
       <c r="D24" s="7"/>
       <c t="s" r="E24" s="7">
+        <v>50</v>
+      </c>
+      <c r="F24" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G24" s="8">
         <v>51</v>
       </c>
-      <c r="F24" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G24" s="8">
-        <v>52</v>
-      </c>
       <c t="s" r="H24" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I24" s="7">
+        <v>54</v>
+      </c>
+      <c t="s" r="J24" s="7">
         <v>55</v>
-      </c>
-      <c t="s" r="J24" s="7">
-        <v>56</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
@@ -2294,7 +2297,7 @@
       </c>
       <c r="D25" s="7"/>
       <c t="s" r="E25" s="7">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F25" s="7">
         <v>321</v>
@@ -2303,13 +2306,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H25" s="8">
+        <v>56</v>
+      </c>
+      <c t="s" r="I25" s="7">
         <v>57</v>
       </c>
-      <c t="s" r="I25" s="7">
+      <c t="s" r="J25" s="7">
         <v>58</v>
-      </c>
-      <c t="s" r="J25" s="7">
-        <v>59</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
@@ -2327,22 +2330,22 @@
       </c>
       <c r="D26" s="7"/>
       <c t="s" r="E26" s="7">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F26" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G26" s="8">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c t="s" r="H26" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I26" s="7">
+        <v>59</v>
+      </c>
+      <c t="s" r="J26" s="7">
         <v>60</v>
-      </c>
-      <c t="s" r="J26" s="7">
-        <v>61</v>
       </c>
       <c r="K26" s="7"/>
       <c r="L26" s="7"/>
@@ -2375,22 +2378,22 @@
       </c>
       <c r="D28" s="7"/>
       <c t="s" r="E28" s="7">
+        <v>61</v>
+      </c>
+      <c r="F28" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G28" s="8">
         <v>62</v>
-      </c>
-      <c r="F28" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G28" s="8">
-        <v>63</v>
       </c>
       <c t="s" r="H28" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I28" s="7">
+        <v>63</v>
+      </c>
+      <c t="s" r="J28" s="7">
         <v>64</v>
-      </c>
-      <c t="s" r="J28" s="7">
-        <v>65</v>
       </c>
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
@@ -2408,7 +2411,7 @@
       </c>
       <c r="D29" s="7"/>
       <c t="s" r="E29" s="7">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F29" s="7">
         <v>321</v>
@@ -2417,13 +2420,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H29" s="8">
+        <v>65</v>
+      </c>
+      <c t="s" r="I29" s="7">
+        <v>54</v>
+      </c>
+      <c t="s" r="J29" s="7">
         <v>66</v>
-      </c>
-      <c t="s" r="I29" s="7">
-        <v>55</v>
-      </c>
-      <c t="s" r="J29" s="7">
-        <v>67</v>
       </c>
       <c r="K29" s="7"/>
       <c r="L29" s="7"/>
@@ -2441,22 +2444,22 @@
       </c>
       <c r="D30" s="7"/>
       <c t="s" r="E30" s="7">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F30" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G30" s="8">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c t="s" r="H30" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I30" s="7">
+        <v>67</v>
+      </c>
+      <c t="s" r="J30" s="7">
         <v>68</v>
-      </c>
-      <c t="s" r="J30" s="7">
-        <v>69</v>
       </c>
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
@@ -2489,7 +2492,7 @@
       </c>
       <c r="D32" s="7"/>
       <c t="s" r="E32" s="7">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F32" s="7">
         <v>321</v>
@@ -2498,13 +2501,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H32" s="8">
+        <v>70</v>
+      </c>
+      <c t="s" r="I32" s="7">
         <v>71</v>
       </c>
-      <c t="s" r="I32" s="7">
+      <c t="s" r="J32" s="7">
         <v>72</v>
-      </c>
-      <c t="s" r="J32" s="7">
-        <v>73</v>
       </c>
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
@@ -2522,22 +2525,22 @@
       </c>
       <c r="D33" s="7"/>
       <c t="s" r="E33" s="7">
+        <v>69</v>
+      </c>
+      <c r="F33" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G33" s="8">
         <v>70</v>
-      </c>
-      <c r="F33" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G33" s="8">
-        <v>71</v>
       </c>
       <c t="s" r="H33" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I33" s="7">
+        <v>73</v>
+      </c>
+      <c t="s" r="J33" s="7">
         <v>74</v>
-      </c>
-      <c t="s" r="J33" s="7">
-        <v>75</v>
       </c>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
@@ -2555,7 +2558,7 @@
       </c>
       <c r="D34" s="7"/>
       <c t="s" r="E34" s="7">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F34" s="7">
         <v>321</v>
@@ -2570,7 +2573,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J34" s="7">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
@@ -2588,7 +2591,7 @@
       </c>
       <c r="D35" s="7"/>
       <c t="s" r="E35" s="7">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F35" s="7">
         <v>321</v>
@@ -2600,10 +2603,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I35" s="7">
+        <v>76</v>
+      </c>
+      <c t="s" r="J35" s="7">
         <v>77</v>
-      </c>
-      <c t="s" r="J35" s="7">
-        <v>78</v>
       </c>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
@@ -2621,7 +2624,7 @@
       </c>
       <c r="D36" s="7"/>
       <c t="s" r="E36" s="7">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F36" s="7">
         <v>321</v>
@@ -2630,10 +2633,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H36" s="8">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c t="s" r="I36" s="7">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c t="s" r="J36" s="7">
         <v>24</v>
@@ -2665,11 +2668,11 @@
         <v>7621</v>
       </c>
       <c t="s" r="C38" s="7">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D38" s="7"/>
       <c t="s" r="E38" s="7">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F38" s="7">
         <v>321</v>
@@ -2678,13 +2681,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H38" s="8">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c t="s" r="I38" s="7">
         <v>30</v>
       </c>
       <c t="s" r="J38" s="7">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
@@ -2702,22 +2705,22 @@
       </c>
       <c r="D39" s="7"/>
       <c t="s" r="E39" s="7">
+        <v>80</v>
+      </c>
+      <c r="F39" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G39" s="8">
         <v>81</v>
       </c>
-      <c r="F39" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G39" s="8">
-        <v>82</v>
-      </c>
       <c t="s" r="H39" s="8">
+        <v>83</v>
+      </c>
+      <c t="s" r="I39" s="7">
+        <v>64</v>
+      </c>
+      <c t="s" r="J39" s="7">
         <v>84</v>
-      </c>
-      <c t="s" r="I39" s="7">
-        <v>65</v>
-      </c>
-      <c t="s" r="J39" s="7">
-        <v>85</v>
       </c>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
@@ -2735,22 +2738,22 @@
       </c>
       <c r="D40" s="7"/>
       <c t="s" r="E40" s="7">
+        <v>80</v>
+      </c>
+      <c r="F40" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G40" s="8">
+        <v>83</v>
+      </c>
+      <c t="s" r="H40" s="8">
         <v>81</v>
       </c>
-      <c r="F40" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G40" s="8">
-        <v>84</v>
-      </c>
-      <c t="s" r="H40" s="8">
-        <v>82</v>
-      </c>
       <c t="s" r="I40" s="7">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c t="s" r="J40" s="7">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
@@ -2768,22 +2771,22 @@
       </c>
       <c r="D41" s="7"/>
       <c t="s" r="E41" s="7">
+        <v>80</v>
+      </c>
+      <c r="F41" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G41" s="8">
         <v>81</v>
       </c>
-      <c r="F41" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G41" s="8">
-        <v>82</v>
-      </c>
       <c t="s" r="H41" s="8">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c t="s" r="I41" s="7">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c t="s" r="J41" s="7">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
@@ -2816,22 +2819,22 @@
       </c>
       <c r="D43" s="7"/>
       <c t="s" r="E43" s="7">
+        <v>88</v>
+      </c>
+      <c r="F43" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G43" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H43" s="8">
+        <v>89</v>
+      </c>
+      <c t="s" r="I43" s="7">
         <v>90</v>
       </c>
-      <c r="F43" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G43" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="H43" s="8">
+      <c t="s" r="J43" s="7">
         <v>91</v>
-      </c>
-      <c t="s" r="I43" s="7">
-        <v>92</v>
-      </c>
-      <c t="s" r="J43" s="7">
-        <v>93</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
@@ -2849,22 +2852,22 @@
       </c>
       <c r="D44" s="7"/>
       <c t="s" r="E44" s="7">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F44" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G44" s="8">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c t="s" r="H44" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I44" s="7">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c t="s" r="J44" s="7">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
@@ -2882,7 +2885,7 @@
       </c>
       <c r="D45" s="7"/>
       <c t="s" r="E45" s="7">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F45" s="7">
         <v>321</v>
@@ -2891,20 +2894,20 @@
         <v>26</v>
       </c>
       <c t="s" r="H45" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="I45" s="7">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c t="s" r="J45" s="7">
-        <v>97</v>
+        <v>32</v>
       </c>
       <c t="s" r="K45" s="7">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="L45" s="7"/>
       <c t="s" r="M45" s="7">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
@@ -2919,29 +2922,29 @@
       </c>
       <c r="D46" s="7"/>
       <c t="s" r="E46" s="7">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F46" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G46" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="H46" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I46" s="7">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c t="s" r="J46" s="7">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c t="s" r="K46" s="7">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="L46" s="7"/>
       <c t="s" r="M46" s="7">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
@@ -2956,7 +2959,7 @@
       </c>
       <c r="D47" s="7"/>
       <c t="s" r="E47" s="7">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F47" s="7">
         <v>321</v>
@@ -2965,13 +2968,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H47" s="8">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c t="s" r="I47" s="7">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c t="s" r="J47" s="7">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
@@ -2989,22 +2992,22 @@
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G48" s="8">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c t="s" r="H48" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I48" s="7">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c t="s" r="J48" s="7">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
@@ -3037,22 +3040,22 @@
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G50" s="8">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c t="s" r="H50" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I50" s="7">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c t="s" r="J50" s="7">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
@@ -3070,7 +3073,7 @@
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F51" s="7">
         <v>321</v>
@@ -3079,13 +3082,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H51" s="8">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c t="s" r="I51" s="7">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c t="s" r="J51" s="7">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
@@ -3103,22 +3106,22 @@
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G52" s="8">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c t="s" r="H52" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I52" s="7">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c t="s" r="J52" s="7">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
@@ -3136,7 +3139,7 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
@@ -3145,13 +3148,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H53" s="8">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c t="s" r="I53" s="7">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c t="s" r="J53" s="7">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
@@ -3184,7 +3187,7 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
@@ -3196,10 +3199,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I55" s="7">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
@@ -3217,22 +3220,22 @@
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
+        <v>107</v>
+      </c>
+      <c r="F56" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G56" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H56" s="8">
         <v>110</v>
       </c>
-      <c r="F56" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G56" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="H56" s="8">
-        <v>113</v>
-      </c>
       <c t="s" r="I56" s="7">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c t="s" r="J56" s="7">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
@@ -3250,22 +3253,22 @@
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
+        <v>107</v>
+      </c>
+      <c r="F57" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G57" s="8">
         <v>110</v>
       </c>
-      <c r="F57" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G57" s="8">
+      <c t="s" r="H57" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="I57" s="7">
         <v>113</v>
       </c>
-      <c t="s" r="H57" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="I57" s="7">
-        <v>116</v>
-      </c>
       <c t="s" r="J57" s="7">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
@@ -3283,7 +3286,7 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
@@ -3295,10 +3298,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I58" s="7">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c t="s" r="J58" s="7">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
@@ -3316,7 +3319,7 @@
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F59" s="7">
         <v>321</v>
@@ -3328,10 +3331,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I59" s="7">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c t="s" r="J59" s="7">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
@@ -3349,7 +3352,7 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
@@ -3358,13 +3361,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H60" s="8">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
@@ -3382,22 +3385,22 @@
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F61" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G61" s="8">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c t="s" r="H61" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I61" s="7">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c t="s" r="J61" s="7">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
@@ -3430,22 +3433,22 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G63" s="8">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c t="s" r="H63" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I63" s="7">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c t="s" r="J63" s="7">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
@@ -3463,29 +3466,29 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
+        <v>119</v>
+      </c>
+      <c r="F64" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G64" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H64" s="8">
+        <v>121</v>
+      </c>
+      <c t="s" r="I64" s="7">
+        <v>102</v>
+      </c>
+      <c t="s" r="J64" s="7">
         <v>122</v>
       </c>
-      <c r="F64" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G64" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="H64" s="8">
-        <v>124</v>
-      </c>
-      <c t="s" r="I64" s="7">
-        <v>105</v>
-      </c>
-      <c t="s" r="J64" s="7">
-        <v>125</v>
-      </c>
       <c t="s" r="K64" s="7">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L64" s="7"/>
       <c t="s" r="M64" s="7">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
@@ -3500,29 +3503,29 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G65" s="8">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c t="s" r="H65" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I65" s="7">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c t="s" r="J65" s="7">
         <v>23</v>
       </c>
       <c t="s" r="K65" s="7">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="L65" s="7"/>
       <c t="s" r="M65" s="7">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
@@ -3537,7 +3540,7 @@
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
@@ -3546,13 +3549,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H66" s="8">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c t="s" r="I66" s="7">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c t="s" r="J66" s="7">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
@@ -3585,22 +3588,22 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
+        <v>129</v>
+      </c>
+      <c r="F68" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G68" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H68" s="8">
+        <v>130</v>
+      </c>
+      <c t="s" r="I68" s="7">
+        <v>131</v>
+      </c>
+      <c t="s" r="J68" s="7">
         <v>132</v>
-      </c>
-      <c r="F68" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G68" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="H68" s="8">
-        <v>133</v>
-      </c>
-      <c t="s" r="I68" s="7">
-        <v>134</v>
-      </c>
-      <c t="s" r="J68" s="7">
-        <v>135</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -3618,22 +3621,22 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G69" s="8">
+        <v>130</v>
+      </c>
+      <c t="s" r="H69" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="I69" s="7">
         <v>133</v>
       </c>
-      <c t="s" r="H69" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="I69" s="7">
-        <v>136</v>
-      </c>
       <c t="s" r="J69" s="7">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
@@ -3651,7 +3654,7 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
@@ -3660,13 +3663,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H70" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
@@ -3684,22 +3687,22 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G71" s="8">
+        <v>135</v>
+      </c>
+      <c t="s" r="H71" s="8">
         <v>138</v>
       </c>
-      <c t="s" r="H71" s="8">
-        <v>141</v>
-      </c>
       <c t="s" r="I71" s="7">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -3717,22 +3720,22 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G72" s="8">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c t="s" r="H72" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
@@ -3750,22 +3753,22 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G73" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="H73" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I73" s="7">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -3783,7 +3786,7 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
@@ -3795,10 +3798,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
@@ -3816,7 +3819,7 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
@@ -3828,10 +3831,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c t="s" r="J75" s="7">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
@@ -3864,7 +3867,7 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
@@ -3873,13 +3876,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H77" s="8">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c t="s" r="I77" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -3897,22 +3900,22 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G78" s="8">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c t="s" r="H78" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -3930,7 +3933,7 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
@@ -3939,13 +3942,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H79" s="8">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
@@ -3963,22 +3966,22 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
+        <v>145</v>
+      </c>
+      <c r="F80" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G80" s="8">
+        <v>130</v>
+      </c>
+      <c t="s" r="H80" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="I80" s="7">
         <v>148</v>
       </c>
-      <c r="F80" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G80" s="8">
-        <v>133</v>
-      </c>
-      <c t="s" r="H80" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="I80" s="7">
-        <v>151</v>
-      </c>
       <c t="s" r="J80" s="7">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
@@ -4011,7 +4014,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -4020,13 +4023,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H82" s="8">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
@@ -4044,22 +4047,22 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G83" s="8">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c t="s" r="H83" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -4077,7 +4080,7 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4089,10 +4092,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4110,7 +4113,7 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4122,10 +4125,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>159</v>
+        <v>33</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4143,7 +4146,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4152,13 +4155,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H86" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -4176,22 +4179,22 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G87" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="H87" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -4209,7 +4212,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4218,13 +4221,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H88" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4242,22 +4245,22 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G89" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="H89" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
@@ -4283,14 +4286,14 @@
         <v>13</v>
       </c>
       <c r="B91" s="7">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c t="s" r="C91" s="7">
         <v>14</v>
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4299,13 +4302,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H91" s="8">
-        <v>106</v>
+        <v>163</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>97</v>
+        <v>164</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -4316,29 +4319,29 @@
         <v>13</v>
       </c>
       <c r="B92" s="7">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c t="s" r="C92" s="7">
         <v>14</v>
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
+        <v>162</v>
+      </c>
+      <c r="F92" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G92" s="8">
+        <v>163</v>
+      </c>
+      <c t="s" r="H92" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="I92" s="7">
+        <v>103</v>
+      </c>
+      <c t="s" r="J92" s="7">
         <v>166</v>
-      </c>
-      <c r="F92" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G92" s="8">
-        <v>106</v>
-      </c>
-      <c t="s" r="H92" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="I92" s="7">
-        <v>19</v>
-      </c>
-      <c t="s" r="J92" s="7">
-        <v>86</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4356,7 +4359,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4389,7 +4392,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -4452,7 +4455,7 @@
         <v>174</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -4485,7 +4488,7 @@
         <v>175</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -4548,10 +4551,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -4578,10 +4581,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H100" s="8">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c t="s" r="J100" s="7">
         <v>178</v>
@@ -4608,7 +4611,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G101" s="8">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c t="s" r="H101" s="8">
         <v>26</v>
@@ -4617,7 +4620,7 @@
         <v>179</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -4647,7 +4650,7 @@
         <v>173</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c t="s" r="J102" s="7">
         <v>180</v>
@@ -4722,7 +4725,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G105" s="8">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c t="s" r="H105" s="8">
         <v>26</v>
@@ -4758,7 +4761,7 @@
         <v>26</v>
       </c>
       <c t="s" r="H106" s="8">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c t="s" r="I106" s="7">
         <v>186</v>
@@ -4788,7 +4791,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G107" s="8">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c t="s" r="H107" s="8">
         <v>26</v>
@@ -4797,7 +4800,7 @@
         <v>188</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -4824,10 +4827,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H108" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c t="s" r="J108" s="7">
         <v>180</v>
@@ -4837,7 +4840,7 @@
       </c>
       <c r="L108" s="7"/>
       <c t="s" r="M108" s="7">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
@@ -4876,7 +4879,7 @@
         <v>26</v>
       </c>
       <c t="s" r="H110" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="I110" s="7">
         <v>30</v>
@@ -4906,16 +4909,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G111" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="H111" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -4942,10 +4945,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H112" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c t="s" r="J112" s="7">
         <v>192</v>
@@ -4972,10 +4975,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G113" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="H113" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="I113" s="7">
         <v>193</v>
@@ -5009,10 +5012,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G114" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="H114" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="I114" s="7">
         <v>20</v>
@@ -5046,7 +5049,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G115" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="H115" s="8">
         <v>26</v>
@@ -5058,7 +5061,7 @@
         <v>199</v>
       </c>
       <c t="s" r="K115" s="7">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="L115" s="7"/>
       <c t="s" r="M115" s="7">
@@ -5101,7 +5104,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H117" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="I117" s="7">
         <v>202</v>
@@ -5131,16 +5134,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G118" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="H118" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5167,10 +5170,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H119" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c t="s" r="J119" s="7">
         <v>204</v>
@@ -5197,7 +5200,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G120" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="H120" s="8">
         <v>16</v>
@@ -5233,7 +5236,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H121" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="I121" s="7">
         <v>205</v>
@@ -5263,7 +5266,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G122" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="H122" s="8">
         <v>16</v>
@@ -5272,7 +5275,7 @@
         <v>206</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5311,20 +5314,22 @@
         <v>321</v>
       </c>
       <c t="s" r="G124" s="8">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c t="s" r="H124" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="I124" s="7">
         <v>208</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
-      <c r="M124" s="7"/>
+      <c t="s" r="M124" s="7">
+        <v>209</v>
+      </c>
     </row>
     <row r="125" ht="15" customHeight="1">
       <c t="s" r="A125" s="6">
@@ -5344,16 +5349,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G125" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="H125" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5380,13 +5385,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H126" s="8">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -5410,16 +5415,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G127" s="8">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="H127" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -5446,13 +5451,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H128" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5476,16 +5481,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G129" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="H129" s="8">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c t="s" r="I129" s="7">
         <v>187</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -5518,7 +5523,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5527,10 +5532,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H131" s="8">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c t="s" r="J131" s="7">
         <v>29</v>
@@ -5551,13 +5556,13 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G132" s="8">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="H132" s="8">
         <v>26</v>
@@ -5566,7 +5571,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -5584,7 +5589,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5593,13 +5598,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H133" s="8">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5617,22 +5622,22 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G134" s="8">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c t="s" r="H134" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5650,7 +5655,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5659,13 +5664,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H135" s="8">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="I135" s="7">
         <v>194</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5683,22 +5688,22 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G136" s="8">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="H136" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -5731,7 +5736,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5740,13 +5745,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H138" s="8">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5764,19 +5769,19 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G139" s="8">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c t="s" r="H139" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c t="s" r="J139" s="7">
         <v>184</v>
@@ -5797,7 +5802,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5806,13 +5811,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H140" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -5830,22 +5835,22 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="H141" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5863,7 +5868,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5872,13 +5877,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H142" s="8">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -5892,17 +5897,17 @@
         <v>7614</v>
       </c>
       <c t="s" r="C143" s="7">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G143" s="8">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c t="s" r="H143" s="8">
         <v>16</v>
@@ -5911,7 +5916,7 @@
         <v>198</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -5925,11 +5930,11 @@
         <v>7614</v>
       </c>
       <c t="s" r="C144" s="7">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -5938,13 +5943,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H144" s="8">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -5977,22 +5982,22 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G146" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="H146" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -6010,7 +6015,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6019,13 +6024,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H147" s="8">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6043,29 +6048,29 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G148" s="8">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c t="s" r="H148" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c t="s" r="J148" s="7">
         <v>180</v>
       </c>
       <c t="s" r="K148" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L148" s="7"/>
       <c t="s" r="M148" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
@@ -6095,7 +6100,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6104,13 +6109,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H150" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6128,13 +6133,13 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G151" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="H151" s="8">
         <v>16</v>
@@ -6143,7 +6148,7 @@
         <v>29</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6161,7 +6166,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6170,13 +6175,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H152" s="8">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6194,22 +6199,22 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G153" s="8">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="H153" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6227,7 +6232,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6236,13 +6241,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H154" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6260,22 +6265,22 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G155" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="H155" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6293,7 +6298,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6305,10 +6310,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6326,7 +6331,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6338,10 +6343,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6370,17 +6375,17 @@
         <v>3524</v>
       </c>
       <c t="s" r="C159" s="7">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="H159" s="8">
         <v>16</v>
@@ -6389,7 +6394,7 @@
         <v>177</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6403,11 +6408,11 @@
         <v>3524</v>
       </c>
       <c t="s" r="C160" s="7">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6416,13 +6421,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H160" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6440,13 +6445,13 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="H161" s="8">
         <v>26</v>
@@ -6455,7 +6460,7 @@
         <v>187</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6488,19 +6493,19 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="H163" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="J163" s="7">
         <v>179</v>
@@ -6521,7 +6526,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6530,20 +6535,20 @@
         <v>26</v>
       </c>
       <c t="s" r="H164" s="8">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="I164" s="7">
         <v>20</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c t="s" r="K164" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L164" s="7"/>
       <c t="s" r="M164" s="7">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1">
@@ -6558,29 +6563,29 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G165" s="8">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="H165" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="K165" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L165" s="7"/>
       <c t="s" r="M165" s="7">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
@@ -6610,7 +6615,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6619,13 +6624,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H167" s="8">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6643,13 +6648,13 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G168" s="8">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c t="s" r="H168" s="8">
         <v>26</v>
@@ -6658,7 +6663,7 @@
         <v>171</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6676,7 +6681,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6685,13 +6690,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H169" s="8">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="I169" s="7">
         <v>30</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -6709,22 +6714,22 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G170" s="8">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="H170" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6742,7 +6747,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6751,10 +6756,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H171" s="8">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c t="s" r="J171" s="7">
         <v>194</v>
@@ -6779,29 +6784,29 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G172" s="8">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="H172" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="K172" s="7">
         <v>196</v>
       </c>
       <c r="L172" s="7"/>
       <c t="s" r="M172" s="7">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="173" ht="14.25" customHeight="1">
@@ -6816,7 +6821,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -6825,13 +6830,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -6849,22 +6854,22 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G174" s="8">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="H174" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -6897,19 +6902,19 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G176" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="H176" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="J176" s="7">
         <v>29</v>
@@ -6930,7 +6935,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -6939,13 +6944,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H177" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="I177" s="7">
         <v>24</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -6963,29 +6968,29 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G178" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="H178" s="8">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c t="s" r="K178" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L178" s="7"/>
       <c t="s" r="M178" s="7">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="179" ht="14.25" customHeight="1">
@@ -7000,29 +7005,29 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G179" s="8">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="H179" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="K179" s="7">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="L179" s="7"/>
       <c t="s" r="M179" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1">
@@ -7037,22 +7042,22 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G180" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="H180" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -7070,22 +7075,22 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G181" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7103,22 +7108,22 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="H182" s="8">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c t="s" r="I182" s="7">
         <v>188</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7136,22 +7141,22 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G183" s="8">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7169,22 +7174,22 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="H184" s="8">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7217,7 +7222,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7226,13 +7231,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H186" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="I186" s="7">
         <v>29</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7250,19 +7255,19 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G187" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="H187" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c t="s" r="J187" s="7">
         <v>177</v>
@@ -7283,7 +7288,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7292,13 +7297,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H188" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7316,22 +7321,22 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G189" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="H189" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7349,7 +7354,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7358,13 +7363,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H190" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7382,19 +7387,19 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G191" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="H191" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c t="s" r="J191" s="7">
         <v>189</v>
@@ -7415,7 +7420,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7424,13 +7429,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="I192" s="7">
         <v>199</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7448,22 +7453,22 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="H193" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7496,22 +7501,22 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G195" s="8">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7529,22 +7534,22 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c t="s" r="I196" s="7">
         <v>192</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7562,22 +7567,22 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7595,13 +7600,13 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>26</v>
@@ -7610,7 +7615,7 @@
         <v>189</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7643,7 +7648,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7652,13 +7657,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H200" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="I200" s="7">
         <v>30</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -7676,22 +7681,22 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G201" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="H201" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7709,22 +7714,22 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G202" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="H202" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7742,22 +7747,22 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G203" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="H203" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7790,22 +7795,22 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
+        <v>282</v>
+      </c>
+      <c r="F205" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G205" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H205" s="8">
         <v>281</v>
       </c>
-      <c r="F205" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G205" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="H205" s="8">
-        <v>280</v>
-      </c>
       <c t="s" r="I205" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7823,22 +7828,22 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
+        <v>282</v>
+      </c>
+      <c r="F206" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G206" s="8">
         <v>281</v>
       </c>
-      <c r="F206" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G206" s="8">
-        <v>280</v>
-      </c>
       <c t="s" r="H206" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7856,22 +7861,22 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G207" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>159</v>
+        <v>33</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7889,22 +7894,22 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c t="s" r="H208" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -7922,13 +7927,13 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G209" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="H209" s="8">
         <v>26</v>
@@ -7937,7 +7942,7 @@
         <v>182</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -7970,7 +7975,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -7982,10 +7987,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -8003,7 +8008,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8012,13 +8017,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H212" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -8036,22 +8041,22 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G213" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="H213" s="8">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8069,16 +8074,16 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G214" s="8">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="H214" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="I214" s="7">
         <v>178</v>
@@ -8102,22 +8107,22 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G215" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="H215" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8150,7 +8155,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8159,13 +8164,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H217" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8183,22 +8188,22 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G218" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="H218" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8216,7 +8221,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8225,10 +8230,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H219" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c t="s" r="J219" s="7">
         <v>194</v>
@@ -8249,19 +8254,19 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G220" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="H220" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c t="s" r="J220" s="7">
         <v>188</v>
@@ -8282,7 +8287,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8294,10 +8299,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8315,7 +8320,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8327,10 +8332,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8363,29 +8368,29 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c t="s" r="H224" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="K224" s="7">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="L224" s="7"/>
       <c t="s" r="M224" s="7">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1">
@@ -8400,7 +8405,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8412,10 +8417,10 @@
         <v>173</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8433,7 +8438,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8445,10 +8450,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8466,7 +8471,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8481,7 +8486,7 @@
         <v>205</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8499,7 +8504,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8511,10 +8516,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8547,22 +8552,22 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G230" s="8">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c t="s" r="H230" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>97</v>
+        <v>32</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -8580,22 +8585,22 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G231" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="H231" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8613,22 +8618,22 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="H232" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8646,7 +8651,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8655,13 +8660,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H233" s="8">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="I233" s="7">
         <v>189</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8679,22 +8684,22 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="H234" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8727,22 +8732,22 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G236" s="8">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -8760,22 +8765,22 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="H237" s="8">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -8793,19 +8798,19 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G238" s="8">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J238" s="7">
         <v>186</v>
@@ -8826,29 +8831,29 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="H239" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c t="s" r="J239" s="7">
         <v>179</v>
       </c>
       <c t="s" r="K239" s="7">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
@@ -8878,7 +8883,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -8890,10 +8895,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8911,7 +8916,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8920,20 +8925,20 @@
         <v>26</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c t="s" r="I242" s="7">
+        <v>103</v>
+      </c>
+      <c t="s" r="J242" s="7">
         <v>34</v>
       </c>
-      <c t="s" r="J242" s="7">
-        <v>86</v>
-      </c>
       <c t="s" r="K242" s="7">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="L242" s="7"/>
       <c t="s" r="M242" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
@@ -8948,29 +8953,29 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c t="s" r="H243" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="K243" s="7">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="L243" s="7"/>
       <c t="s" r="M243" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="244" ht="14.25" customHeight="1">
@@ -8985,7 +8990,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -8994,13 +8999,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -9033,22 +9038,22 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G246" s="8">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c t="s" r="H246" s="8">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -9066,22 +9071,22 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G247" s="8">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c t="s" r="H247" s="8">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9099,22 +9104,22 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G248" s="8">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9132,22 +9137,22 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c t="s" r="H249" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -9165,7 +9170,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9174,13 +9179,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H250" s="8">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9198,22 +9203,22 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G251" s="8">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c t="s" r="H251" s="8">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9246,7 +9251,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9255,13 +9260,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9279,13 +9284,13 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G254" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="H254" s="8">
         <v>16</v>
@@ -9294,7 +9299,7 @@
         <v>185</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9312,7 +9317,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9321,7 +9326,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H255" s="8">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c t="s" r="I255" s="7">
         <v>188</v>
@@ -9345,22 +9350,22 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G256" s="8">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c t="s" r="H256" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9393,19 +9398,19 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G258" s="8">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c t="s" r="H258" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c t="s" r="J258" s="7">
         <v>177</v>
@@ -9426,7 +9431,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9435,13 +9440,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9459,19 +9464,19 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="H260" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c t="s" r="J260" s="7">
         <v>194</v>
@@ -9492,7 +9497,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9501,7 +9506,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="I261" s="7">
         <v>187</v>
@@ -9525,22 +9530,22 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="H262" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9558,7 +9563,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9567,13 +9572,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9606,7 +9611,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F265" s="7">
         <v>320</v>
@@ -9615,13 +9620,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9639,19 +9644,19 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F266" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="H266" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c t="s" r="J266" s="7">
         <v>179</v>
@@ -9672,7 +9677,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F267" s="7">
         <v>320</v>
@@ -9681,13 +9686,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H267" s="8">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -9705,19 +9710,19 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F268" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G268" s="8">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c t="s" r="H268" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c t="s" r="J268" s="7">
         <v>181</v>
@@ -9753,7 +9758,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -9762,13 +9767,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H270" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -9786,22 +9791,22 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G271" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="H271" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9819,22 +9824,22 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G272" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="I272" s="7">
         <v>184</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9852,22 +9857,22 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G273" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="H273" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -9885,7 +9890,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -9894,13 +9899,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H274" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="I274" s="7">
         <v>196</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -9918,22 +9923,22 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G275" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="H275" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9951,7 +9956,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -9963,10 +9968,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -9999,7 +10004,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -10008,13 +10013,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -10032,22 +10037,22 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c t="s" r="H279" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -10065,7 +10070,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -10074,13 +10079,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H280" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10098,22 +10103,22 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="H281" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10131,7 +10136,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
@@ -10143,10 +10148,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10164,7 +10169,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
@@ -10176,10 +10181,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10197,7 +10202,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -10209,7 +10214,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c t="s" r="J284" s="7">
         <v>18</v>
@@ -10245,7 +10250,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
@@ -10257,10 +10262,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10278,7 +10283,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
@@ -10290,10 +10295,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10311,7 +10316,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F288" s="7">
         <v>320</v>
@@ -10320,7 +10325,7 @@
         <v>26</v>
       </c>
       <c t="s" r="H288" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="I288" s="7">
         <v>204</v>
@@ -10344,22 +10349,22 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F289" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G289" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="H289" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10377,7 +10382,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F290" s="7">
         <v>320</v>
@@ -10386,13 +10391,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H290" s="8">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10410,22 +10415,22 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F291" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G291" s="8">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="H291" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10458,7 +10463,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -10470,7 +10475,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c t="s" r="J293" s="7">
         <v>191</v>
@@ -10491,7 +10496,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -10500,13 +10505,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10524,19 +10529,19 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F295" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="H295" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J295" s="7">
         <v>20</v>
@@ -10557,7 +10562,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F296" s="7">
         <v>321</v>
@@ -10566,20 +10571,20 @@
         <v>26</v>
       </c>
       <c t="s" r="H296" s="8">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c t="s" r="K296" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L296" s="7"/>
       <c t="s" r="M296" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="297" ht="14.25" customHeight="1">
@@ -10594,25 +10599,25 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F297" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G297" s="8">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="H297" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c t="s" r="K297" s="7">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="L297" s="7"/>
       <c t="s" r="M297" s="7">
@@ -10646,7 +10651,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -10655,13 +10660,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H299" s="8">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10679,13 +10684,13 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c t="s" r="H300" s="8">
         <v>16</v>
@@ -10694,7 +10699,7 @@
         <v>176</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10712,7 +10717,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
@@ -10721,13 +10726,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10745,13 +10750,13 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="H302" s="8">
         <v>16</v>
@@ -10760,7 +10765,7 @@
         <v>194</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10778,7 +10783,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F303" s="7">
         <v>320</v>
@@ -10790,10 +10795,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
@@ -10811,7 +10816,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F304" s="7">
         <v>320</v>
@@ -10823,10 +10828,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -10859,7 +10864,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -10871,10 +10876,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10892,7 +10897,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
@@ -10901,13 +10906,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H307" s="8">
-        <v>31</v>
+        <v>163</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -10925,19 +10930,19 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G308" s="8">
-        <v>31</v>
+        <v>163</v>
       </c>
       <c t="s" r="H308" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c t="s" r="J308" s="7">
         <v>188</v>
@@ -10958,7 +10963,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
@@ -10970,10 +10975,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
@@ -11006,7 +11011,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -11015,13 +11020,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -11039,22 +11044,22 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11072,7 +11077,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11081,10 +11086,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c t="s" r="J313" s="7">
         <v>19</v>
@@ -11105,22 +11110,22 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="H314" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11138,7 +11143,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -11147,13 +11152,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H315" s="8">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11171,19 +11176,19 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G316" s="8">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c t="s" r="H316" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c t="s" r="J316" s="7">
         <v>174</v>
@@ -11219,7 +11224,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -11228,13 +11233,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11252,19 +11257,19 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c t="s" r="J319" s="7">
         <v>192</v>
@@ -11285,7 +11290,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -11294,13 +11299,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c t="s" r="I320" s="7">
         <v>204</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11318,22 +11323,22 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11351,7 +11356,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F322" s="7">
         <v>321</v>
@@ -11360,13 +11365,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H322" s="8">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11384,22 +11389,22 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F323" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G323" s="8">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c t="s" r="H323" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11432,7 +11437,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -11441,13 +11446,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11465,22 +11470,22 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c t="s" r="H326" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11498,7 +11503,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -11507,7 +11512,7 @@
         <v>26</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="I327" s="7">
         <v>30</v>
@@ -11531,22 +11536,22 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="H328" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11564,7 +11569,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11573,13 +11578,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H329" s="8">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11597,22 +11602,22 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G330" s="8">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c t="s" r="H330" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11630,7 +11635,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11639,13 +11644,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H331" s="8">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11663,22 +11668,22 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G332" s="8">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c t="s" r="H332" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11711,7 +11716,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -11723,10 +11728,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11744,7 +11749,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -11753,13 +11758,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -11777,22 +11782,22 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c t="s" r="H336" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -11810,7 +11815,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -11819,13 +11824,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H337" s="8">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11843,22 +11848,22 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G338" s="8">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="H338" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -11891,22 +11896,22 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G340" s="8">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c t="s" r="H340" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -11924,7 +11929,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
@@ -11933,13 +11938,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -11957,22 +11962,22 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F342" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G342" s="8">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c t="s" r="H342" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -11990,7 +11995,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F343" s="7">
         <v>321</v>
@@ -11999,13 +12004,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c t="s" r="I343" s="7">
         <v>169</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -12038,22 +12043,22 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G345" s="8">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c t="s" r="H345" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -12071,7 +12076,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
@@ -12080,13 +12085,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H346" s="8">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>35</v>
+        <v>166</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12104,19 +12109,19 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G347" s="8">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c t="s" r="H347" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c t="s" r="J347" s="7">
         <v>205</v>
@@ -12137,7 +12142,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
@@ -12146,13 +12151,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c t="s" r="I348" s="7">
         <v>189</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12170,22 +12175,22 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c t="s" r="H349" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12218,7 +12223,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
@@ -12230,10 +12235,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12251,7 +12256,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
@@ -12260,13 +12265,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H352" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -12284,22 +12289,22 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G353" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="H353" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12317,7 +12322,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -12329,7 +12334,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c t="s" r="J354" s="7">
         <v>193</v>
@@ -12350,7 +12355,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
@@ -12359,10 +12364,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H355" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c t="s" r="J355" s="7">
         <v>20</v>
@@ -12383,22 +12388,22 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G356" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="H356" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12431,7 +12436,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -12443,7 +12448,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c t="s" r="J358" s="7">
         <v>202</v>
@@ -12464,7 +12469,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -12473,13 +12478,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c t="s" r="I359" s="7">
         <v>191</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12497,19 +12502,19 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G360" s="8">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c t="s" r="H360" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c t="s" r="J360" s="7">
         <v>204</v>
@@ -12530,7 +12535,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -12539,13 +12544,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H361" s="8">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c t="s" r="I361" s="7">
         <v>178</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12563,13 +12568,13 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G362" s="8">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c t="s" r="H362" s="8">
         <v>16</v>
@@ -12578,7 +12583,7 @@
         <v>187</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12596,7 +12601,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -12605,10 +12610,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c t="s" r="J363" s="7">
         <v>18</v>
@@ -12644,22 +12649,22 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G365" s="8">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="I365" s="7">
         <v>171</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -12677,22 +12682,22 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="H366" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="I366" s="7">
         <v>179</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12710,22 +12715,22 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G367" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -12743,22 +12748,22 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="H368" s="8">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12791,7 +12796,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -12806,7 +12811,7 @@
         <v>29</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12824,7 +12829,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -12836,10 +12841,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>97</v>
+        <v>32</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -12857,7 +12862,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -12869,10 +12874,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12890,7 +12895,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -12902,10 +12907,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12923,7 +12928,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -12932,13 +12937,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H374" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -12956,22 +12961,22 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c t="s" r="H375" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -12989,7 +12994,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -13004,7 +13009,7 @@
         <v>182</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -13037,7 +13042,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -13046,7 +13051,7 @@
         <v>26</v>
       </c>
       <c t="s" r="H378" s="8">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c t="s" r="I378" s="7">
         <v>29</v>
@@ -13070,22 +13075,22 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c t="s" r="H379" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>33</v>
+        <v>165</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13103,7 +13108,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
@@ -13112,13 +13117,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H380" s="8">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13136,22 +13141,22 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c t="s" r="H381" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13184,7 +13189,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -13193,13 +13198,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13217,22 +13222,22 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c t="s" r="H384" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13250,7 +13255,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -13259,13 +13264,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H385" s="8">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c t="s" r="I385" s="7">
         <v>203</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13283,22 +13288,22 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G386" s="8">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c t="s" r="H386" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>159</v>
+        <v>33</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13316,7 +13321,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -13325,13 +13330,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13349,19 +13354,19 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c t="s" r="H388" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c t="s" r="J388" s="7">
         <v>181</v>
@@ -13397,7 +13402,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
@@ -13409,10 +13414,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13430,7 +13435,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
@@ -13442,10 +13447,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13463,7 +13468,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
@@ -13475,10 +13480,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>159</v>
+        <v>33</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -13496,7 +13501,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
@@ -13508,10 +13513,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13529,7 +13534,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
@@ -13541,10 +13546,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13562,7 +13567,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F395" s="7">
         <v>320</v>
@@ -13574,10 +13579,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
@@ -13610,7 +13615,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
@@ -13619,13 +13624,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H397" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13643,22 +13648,22 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G398" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="H398" s="8">
         <v>173</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13676,7 +13681,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
@@ -13685,13 +13690,13 @@
         <v>173</v>
       </c>
       <c t="s" r="H399" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -13709,22 +13714,22 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G400" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="H400" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -13742,7 +13747,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -13751,13 +13756,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="I401" s="7">
         <v>194</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -13775,22 +13780,22 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G402" s="8">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="H402" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -13808,7 +13813,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -13817,13 +13822,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H403" s="8">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -13841,22 +13846,22 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c t="s" r="H404" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -13889,7 +13894,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -13904,7 +13909,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -13922,7 +13927,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
@@ -13937,7 +13942,7 @@
         <v>191</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -13955,7 +13960,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
@@ -13964,13 +13969,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -13988,22 +13993,22 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -14021,7 +14026,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
@@ -14030,10 +14035,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H410" s="8">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c t="s" r="J410" s="7">
         <v>189</v>
@@ -14054,19 +14059,19 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G411" s="8">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="H411" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c t="s" r="J411" s="7">
         <v>199</v>
@@ -14102,22 +14107,22 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F413" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G413" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="H413" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
@@ -14135,7 +14140,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F414" s="7">
         <v>330</v>
@@ -14147,7 +14152,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c t="s" r="J414" s="7">
         <v>19</v>
@@ -14168,7 +14173,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F415" s="7">
         <v>330</v>
@@ -14183,7 +14188,7 @@
         <v>20</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
@@ -14216,22 +14221,22 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F417" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G417" s="8">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c t="s" r="H417" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -14249,7 +14254,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F418" s="7">
         <v>330</v>
@@ -14258,13 +14263,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H418" s="8">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14297,22 +14302,22 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F420" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G420" s="8">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c t="s" r="H420" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14330,7 +14335,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F421" s="7">
         <v>330</v>
@@ -14342,10 +14347,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
@@ -14378,22 +14383,22 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F423" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G423" s="8">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c t="s" r="H423" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -14411,7 +14416,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F424" s="7">
         <v>330</v>
@@ -14426,7 +14431,7 @@
         <v>181</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
@@ -14459,7 +14464,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F426" s="7">
         <v>330</v>
@@ -14468,7 +14473,7 @@
         <v>26</v>
       </c>
       <c t="s" r="H426" s="8">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c t="s" r="I426" s="7">
         <v>24</v>
@@ -14492,22 +14497,22 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F427" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G427" s="8">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c t="s" r="H427" s="8">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
@@ -14525,22 +14530,22 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F428" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G428" s="8">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c t="s" r="H428" s="8">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
@@ -14573,13 +14578,13 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F430" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G430" s="8">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c t="s" r="H430" s="8">
         <v>26</v>
@@ -14606,7 +14611,7 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F431" s="7">
         <v>330</v>
@@ -14615,13 +14620,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H431" s="8">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
@@ -14639,22 +14644,22 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F432" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G432" s="8">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c t="s" r="H432" s="8">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c t="s" r="I432" s="7">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
@@ -14672,22 +14677,22 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F433" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G433" s="8">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c t="s" r="H433" s="8">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
@@ -14720,7 +14725,7 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F435" s="7">
         <v>330</v>
@@ -14729,13 +14734,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H435" s="8">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
@@ -14753,22 +14758,22 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F436" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G436" s="8">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c t="s" r="H436" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
@@ -14776,7 +14781,7 @@
     </row>
     <row r="437" ht="15.75" customHeight="1">
       <c t="s" r="A437" s="9">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B437" s="9"/>
       <c r="C437" s="9"/>
@@ -14796,7 +14801,7 @@
     <row r="438" ht="65.25" customHeight="1"/>
     <row r="439" ht="16.5" customHeight="1">
       <c t="s" r="A439" s="10">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B439" s="10"/>
       <c r="C439" s="10"/>
@@ -14809,7 +14814,7 @@
       <c r="J439" s="10"/>
       <c r="K439" s="10"/>
       <c t="s" r="L439" s="11">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M439" s="11"/>
       <c r="N439" s="11"/>

--- a/Data/FlightPlan/FPL_18OCT26.xlsx
+++ b/Data/FlightPlan/FPL_18OCT26.xlsx
@@ -608,420 +608,420 @@
     <t>19:05</t>
   </si>
   <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>10:25</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>04:05</t>
+  </si>
+  <si>
+    <t>08:03</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>12:25</t>
+  </si>
+  <si>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>15:35</t>
+  </si>
+  <si>
+    <t>01:10</t>
+  </si>
+  <si>
+    <t>VN-A553</t>
+  </si>
+  <si>
+    <t>HPH</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>13:15</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>18:25</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>BQS</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>04:45</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>VVO</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>15:50</t>
+  </si>
+  <si>
+    <t>16:20</t>
+  </si>
+  <si>
+    <t>22:20</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>23:20</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>KHV</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>02:40</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>05:15</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>23:05</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>DLI</t>
+  </si>
+  <si>
+    <t>16:55</t>
+  </si>
+  <si>
+    <t>MFM</t>
+  </si>
+  <si>
+    <t>23:45</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
     <t>22:30</t>
   </si>
   <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>19:10</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>SIN</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>21:45</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>00:25</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>21:35</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>19:35</t>
+  </si>
+  <si>
+    <t>22:55</t>
+  </si>
+  <si>
+    <t>VN-A648</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>07:10</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>HIJ</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>SAI</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>13:25</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>22:45</t>
+  </si>
+  <si>
+    <t>00:55</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>HKT</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>17:05</t>
+  </si>
+  <si>
+    <t>DEL</t>
+  </si>
+  <si>
+    <t>00:05</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>LJG</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
     <t>23:30</t>
   </si>
   <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>10:25</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>04:05</t>
-  </si>
-  <si>
-    <t>07:59</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>12:25</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>14:25</t>
-  </si>
-  <si>
-    <t>15:35</t>
-  </si>
-  <si>
-    <t>01:10</t>
-  </si>
-  <si>
-    <t>VN-A553</t>
-  </si>
-  <si>
-    <t>HPH</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>13:15</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>18:25</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>15:25</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>BQS</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>04:45</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>VVO</t>
-  </si>
-  <si>
-    <t>13:10</t>
-  </si>
-  <si>
-    <t>15:50</t>
-  </si>
-  <si>
-    <t>16:20</t>
-  </si>
-  <si>
-    <t>22:20</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>23:20</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>KHV</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>02:40</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>05:35</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>DLI</t>
-  </si>
-  <si>
-    <t>16:55</t>
-  </si>
-  <si>
-    <t>MFM</t>
-  </si>
-  <si>
-    <t>23:45</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>19:10</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>SIN</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>07:10</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>00:25</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>21:35</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>19:35</t>
-  </si>
-  <si>
-    <t>22:55</t>
-  </si>
-  <si>
-    <t>VN-A648</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>HIJ</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>SAI</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>13:25</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>22:45</t>
-  </si>
-  <si>
-    <t>00:55</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>HKT</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>17:05</t>
-  </si>
-  <si>
-    <t>DEL</t>
-  </si>
-  <si>
-    <t>00:05</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>LJG</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>05:15</t>
-  </si>
-  <si>
-    <t>23:05</t>
-  </si>
-  <si>
     <t>VN-A663</t>
   </si>
   <si>
@@ -1196,7 +1196,7 @@
     <t>Total Record(s): 361</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 18, 2026 01:57</t>
+    <t xml:space="preserve">Generated on  Oct 18, 2026 02:27</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -5036,7 +5036,7 @@
         <v>13</v>
       </c>
       <c r="B115" s="7">
-        <v>645</v>
+        <v>631</v>
       </c>
       <c t="s" r="C115" s="7">
         <v>14</v>
@@ -5055,18 +5055,14 @@
         <v>26</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="J115" s="7">
         <v>199</v>
       </c>
-      <c t="s" r="K115" s="7">
-        <v>126</v>
-      </c>
+      <c r="K115" s="7"/>
       <c r="L115" s="7"/>
-      <c t="s" r="M115" s="7">
-        <v>200</v>
-      </c>
+      <c r="M115" s="7"/>
     </row>
     <row r="116" ht="14.25" customHeight="1">
       <c r="A116" s="6"/>
@@ -5095,7 +5091,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5107,10 +5103,10 @@
         <v>135</v>
       </c>
       <c t="s" r="I117" s="7">
+        <v>201</v>
+      </c>
+      <c t="s" r="J117" s="7">
         <v>202</v>
-      </c>
-      <c t="s" r="J117" s="7">
-        <v>203</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5128,7 +5124,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5161,7 +5157,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5176,7 +5172,7 @@
         <v>40</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5194,7 +5190,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5227,7 +5223,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5239,7 +5235,7 @@
         <v>135</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c t="s" r="J121" s="7">
         <v>21</v>
@@ -5260,7 +5256,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5272,7 +5268,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c t="s" r="J122" s="7">
         <v>126</v>
@@ -5308,7 +5304,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5320,7 +5316,7 @@
         <v>45</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c t="s" r="J124" s="7">
         <v>151</v>
@@ -5328,7 +5324,7 @@
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
       <c t="s" r="M124" s="7">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1">
@@ -5343,7 +5339,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5376,7 +5372,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5385,7 +5381,7 @@
         <v>26</v>
       </c>
       <c t="s" r="H126" s="8">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c t="s" r="I126" s="7">
         <v>154</v>
@@ -5409,22 +5405,22 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G127" s="8">
+        <v>209</v>
+      </c>
+      <c t="s" r="H127" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="I127" s="7">
         <v>210</v>
       </c>
-      <c t="s" r="H127" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="I127" s="7">
+      <c t="s" r="J127" s="7">
         <v>211</v>
-      </c>
-      <c t="s" r="J127" s="7">
-        <v>212</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -5442,7 +5438,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5454,10 +5450,10 @@
         <v>45</v>
       </c>
       <c t="s" r="I128" s="7">
+        <v>212</v>
+      </c>
+      <c t="s" r="J128" s="7">
         <v>213</v>
-      </c>
-      <c t="s" r="J128" s="7">
-        <v>214</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5475,7 +5471,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5490,7 +5486,7 @@
         <v>187</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -5523,16 +5519,16 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
+        <v>215</v>
+      </c>
+      <c r="F131" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G131" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H131" s="8">
         <v>216</v>
-      </c>
-      <c r="F131" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G131" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="H131" s="8">
-        <v>217</v>
       </c>
       <c t="s" r="I131" s="7">
         <v>108</v>
@@ -5556,13 +5552,13 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
+        <v>215</v>
+      </c>
+      <c r="F132" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G132" s="8">
         <v>216</v>
-      </c>
-      <c r="F132" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G132" s="8">
-        <v>217</v>
       </c>
       <c t="s" r="H132" s="8">
         <v>26</v>
@@ -5571,7 +5567,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -5589,7 +5585,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5622,7 +5618,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5634,10 +5630,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I134" s="7">
+        <v>218</v>
+      </c>
+      <c t="s" r="J134" s="7">
         <v>219</v>
-      </c>
-      <c t="s" r="J134" s="7">
-        <v>220</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5655,22 +5651,22 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
+        <v>215</v>
+      </c>
+      <c r="F135" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G135" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H135" s="8">
         <v>216</v>
-      </c>
-      <c r="F135" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G135" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="H135" s="8">
-        <v>217</v>
       </c>
       <c t="s" r="I135" s="7">
         <v>194</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5688,22 +5684,22 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
+        <v>215</v>
+      </c>
+      <c r="F136" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G136" s="8">
         <v>216</v>
       </c>
-      <c r="F136" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G136" s="8">
-        <v>217</v>
-      </c>
       <c t="s" r="H136" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I136" s="7">
+        <v>221</v>
+      </c>
+      <c t="s" r="J136" s="7">
         <v>222</v>
-      </c>
-      <c t="s" r="J136" s="7">
-        <v>223</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -5736,7 +5732,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5748,10 +5744,10 @@
         <v>138</v>
       </c>
       <c t="s" r="I138" s="7">
+        <v>224</v>
+      </c>
+      <c t="s" r="J138" s="7">
         <v>225</v>
-      </c>
-      <c t="s" r="J138" s="7">
-        <v>226</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5769,7 +5765,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5802,7 +5798,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5814,7 +5810,7 @@
         <v>135</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c t="s" r="J140" s="7">
         <v>103</v>
@@ -5835,7 +5831,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -5850,7 +5846,7 @@
         <v>41</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5868,7 +5864,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5880,7 +5876,7 @@
         <v>81</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c t="s" r="J142" s="7">
         <v>66</v>
@@ -5901,7 +5897,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -5934,7 +5930,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -5943,13 +5939,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H144" s="8">
+        <v>229</v>
+      </c>
+      <c t="s" r="I144" s="7">
         <v>230</v>
       </c>
-      <c t="s" r="I144" s="7">
+      <c t="s" r="J144" s="7">
         <v>231</v>
-      </c>
-      <c t="s" r="J144" s="7">
-        <v>232</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -5982,22 +5978,22 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
+        <v>232</v>
+      </c>
+      <c r="F146" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G146" s="8">
         <v>233</v>
-      </c>
-      <c r="F146" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G146" s="8">
-        <v>234</v>
       </c>
       <c t="s" r="H146" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I146" s="7">
+        <v>234</v>
+      </c>
+      <c t="s" r="J146" s="7">
         <v>235</v>
-      </c>
-      <c t="s" r="J146" s="7">
-        <v>236</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -6015,7 +6011,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6027,7 +6023,7 @@
         <v>81</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c t="s" r="J147" s="7">
         <v>76</v>
@@ -6048,7 +6044,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6066,11 +6062,11 @@
         <v>180</v>
       </c>
       <c t="s" r="K148" s="7">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L148" s="7"/>
       <c t="s" r="M148" s="7">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
@@ -6100,7 +6096,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6112,10 +6108,10 @@
         <v>135</v>
       </c>
       <c t="s" r="I150" s="7">
+        <v>239</v>
+      </c>
+      <c t="s" r="J150" s="7">
         <v>240</v>
-      </c>
-      <c t="s" r="J150" s="7">
-        <v>241</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6133,7 +6129,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6166,7 +6162,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6175,13 +6171,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H152" s="8">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c t="s" r="I152" s="7">
         <v>92</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6199,19 +6195,19 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G153" s="8">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c t="s" r="H153" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c t="s" r="J153" s="7">
         <v>102</v>
@@ -6232,7 +6228,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6265,7 +6261,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6277,10 +6273,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6298,7 +6294,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6310,7 +6306,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c t="s" r="J156" s="7">
         <v>68</v>
@@ -6331,7 +6327,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6346,7 +6342,7 @@
         <v>124</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6379,13 +6375,13 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
+        <v>246</v>
+      </c>
+      <c r="F159" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G159" s="8">
         <v>247</v>
-      </c>
-      <c r="F159" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G159" s="8">
-        <v>248</v>
       </c>
       <c t="s" r="H159" s="8">
         <v>16</v>
@@ -6394,7 +6390,7 @@
         <v>177</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6412,7 +6408,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6424,7 +6420,7 @@
         <v>45</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c t="s" r="J160" s="7">
         <v>42</v>
@@ -6445,7 +6441,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6493,19 +6489,19 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
+        <v>250</v>
+      </c>
+      <c r="F163" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G163" s="8">
         <v>251</v>
       </c>
-      <c r="F163" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G163" s="8">
-        <v>252</v>
-      </c>
       <c t="s" r="H163" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c t="s" r="J163" s="7">
         <v>179</v>
@@ -6526,7 +6522,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6535,7 +6531,7 @@
         <v>26</v>
       </c>
       <c t="s" r="H164" s="8">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c t="s" r="I164" s="7">
         <v>20</v>
@@ -6544,7 +6540,7 @@
         <v>36</v>
       </c>
       <c t="s" r="K164" s="7">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L164" s="7"/>
       <c t="s" r="M164" s="7">
@@ -6563,25 +6559,25 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G165" s="8">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c t="s" r="H165" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I165" s="7">
+        <v>254</v>
+      </c>
+      <c t="s" r="J165" s="7">
         <v>255</v>
       </c>
-      <c t="s" r="J165" s="7">
+      <c t="s" r="K165" s="7">
         <v>256</v>
-      </c>
-      <c t="s" r="K165" s="7">
-        <v>257</v>
       </c>
       <c r="L165" s="7"/>
       <c t="s" r="M165" s="7">
@@ -6608,29 +6604,29 @@
         <v>13</v>
       </c>
       <c r="B167" s="7">
-        <v>1382</v>
+        <v>120</v>
       </c>
       <c t="s" r="C167" s="7">
         <v>14</v>
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
+        <v>257</v>
+      </c>
+      <c r="F167" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G167" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H167" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I167" s="7">
         <v>258</v>
       </c>
-      <c r="F167" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G167" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="H167" s="8">
-        <v>110</v>
-      </c>
-      <c t="s" r="I167" s="7">
-        <v>259</v>
-      </c>
       <c t="s" r="J167" s="7">
-        <v>225</v>
+        <v>71</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6641,29 +6637,29 @@
         <v>13</v>
       </c>
       <c r="B168" s="7">
-        <v>1383</v>
+        <v>929</v>
       </c>
       <c t="s" r="C168" s="7">
         <v>14</v>
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G168" s="8">
-        <v>110</v>
+        <v>16</v>
       </c>
       <c t="s" r="H168" s="8">
-        <v>26</v>
+        <v>163</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>171</v>
+        <v>133</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>260</v>
+        <v>120</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6674,29 +6670,29 @@
         <v>13</v>
       </c>
       <c r="B169" s="7">
-        <v>272</v>
+        <v>928</v>
       </c>
       <c t="s" r="C169" s="7">
         <v>14</v>
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G169" s="8">
-        <v>26</v>
+        <v>163</v>
       </c>
       <c t="s" r="H169" s="8">
-        <v>217</v>
+        <v>16</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>30</v>
+        <v>123</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>261</v>
+        <v>188</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -6707,121 +6703,95 @@
         <v>13</v>
       </c>
       <c r="B170" s="7">
-        <v>273</v>
+        <v>161</v>
       </c>
       <c t="s" r="C170" s="7">
         <v>14</v>
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G170" s="8">
-        <v>217</v>
+        <v>16</v>
       </c>
       <c t="s" r="H170" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>72</v>
+        <v>259</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>103</v>
+        <v>260</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
       <c r="M170" s="7"/>
     </row>
     <row r="171" ht="14.25" customHeight="1">
-      <c t="s" r="A171" s="6">
-        <v>13</v>
-      </c>
-      <c r="B171" s="7">
-        <v>278</v>
-      </c>
-      <c t="s" r="C171" s="7">
-        <v>14</v>
-      </c>
+      <c r="A171" s="6"/>
+      <c r="B171" s="7"/>
+      <c r="C171" s="7"/>
       <c r="D171" s="7"/>
-      <c t="s" r="E171" s="7">
-        <v>258</v>
-      </c>
-      <c r="F171" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G171" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="H171" s="8">
-        <v>217</v>
-      </c>
-      <c t="s" r="I171" s="7">
-        <v>116</v>
-      </c>
-      <c t="s" r="J171" s="7">
-        <v>194</v>
-      </c>
-      <c t="s" r="K171" s="7">
-        <v>193</v>
-      </c>
+      <c r="E171" s="7"/>
+      <c r="F171" s="7"/>
+      <c r="G171" s="8"/>
+      <c r="H171" s="8"/>
+      <c r="I171" s="7"/>
+      <c r="J171" s="7"/>
+      <c r="K171" s="7"/>
       <c r="L171" s="7"/>
-      <c t="s" r="M171" s="7">
-        <v>179</v>
-      </c>
+      <c r="M171" s="7"/>
     </row>
     <row r="172" ht="14.25" customHeight="1">
       <c t="s" r="A172" s="6">
         <v>13</v>
       </c>
       <c r="B172" s="7">
-        <v>279</v>
+        <v>621</v>
       </c>
       <c t="s" r="C172" s="7">
         <v>14</v>
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G172" s="8">
-        <v>217</v>
+        <v>135</v>
       </c>
       <c t="s" r="H172" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>157</v>
+        <v>262</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>222</v>
-      </c>
-      <c t="s" r="K172" s="7">
-        <v>196</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="K172" s="7"/>
       <c r="L172" s="7"/>
-      <c t="s" r="M172" s="7">
-        <v>67</v>
-      </c>
+      <c r="M172" s="7"/>
     </row>
     <row r="173" ht="14.25" customHeight="1">
       <c t="s" r="A173" s="6">
         <v>13</v>
       </c>
       <c r="B173" s="7">
-        <v>3908</v>
+        <v>632</v>
       </c>
       <c t="s" r="C173" s="7">
         <v>14</v>
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -6830,13 +6800,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>262</v>
+        <v>135</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>263</v>
+        <v>24</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>264</v>
+        <v>92</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -6844,65 +6814,91 @@
     </row>
     <row r="174" ht="14.25" customHeight="1">
       <c t="s" r="A174" s="6">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B174" s="7">
-        <v>3909</v>
+        <v>720</v>
       </c>
       <c t="s" r="C174" s="7">
         <v>14</v>
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G174" s="8">
-        <v>262</v>
+        <v>135</v>
       </c>
       <c t="s" r="H174" s="8">
-        <v>26</v>
+        <v>216</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>265</v>
+        <v>39</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>266</v>
-      </c>
-      <c r="K174" s="7"/>
+        <v>96</v>
+      </c>
+      <c t="s" r="K174" s="7">
+        <v>217</v>
+      </c>
       <c r="L174" s="7"/>
-      <c r="M174" s="7"/>
+      <c t="s" r="M174" s="7">
+        <v>93</v>
+      </c>
     </row>
     <row r="175" ht="15" customHeight="1">
-      <c r="A175" s="6"/>
-      <c r="B175" s="7"/>
-      <c r="C175" s="7"/>
+      <c t="s" r="A175" s="6">
+        <v>13</v>
+      </c>
+      <c r="B175" s="7">
+        <v>721</v>
+      </c>
+      <c t="s" r="C175" s="7">
+        <v>14</v>
+      </c>
       <c r="D175" s="7"/>
-      <c r="E175" s="7"/>
-      <c r="F175" s="7"/>
-      <c r="G175" s="8"/>
-      <c r="H175" s="8"/>
-      <c r="I175" s="7"/>
-      <c r="J175" s="7"/>
-      <c r="K175" s="7"/>
+      <c t="s" r="E175" s="7">
+        <v>261</v>
+      </c>
+      <c r="F175" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G175" s="8">
+        <v>216</v>
+      </c>
+      <c t="s" r="H175" s="8">
+        <v>135</v>
+      </c>
+      <c t="s" r="I175" s="7">
+        <v>93</v>
+      </c>
+      <c t="s" r="J175" s="7">
+        <v>263</v>
+      </c>
+      <c t="s" r="K175" s="7">
+        <v>97</v>
+      </c>
       <c r="L175" s="7"/>
-      <c r="M175" s="7"/>
+      <c t="s" r="M175" s="7">
+        <v>234</v>
+      </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
       <c t="s" r="A176" s="6">
         <v>13</v>
       </c>
       <c r="B176" s="7">
-        <v>621</v>
+        <v>1729</v>
       </c>
       <c t="s" r="C176" s="7">
         <v>14</v>
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -6911,13 +6907,13 @@
         <v>135</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>26</v>
+        <v>264</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>268</v>
+        <v>249</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>29</v>
+        <v>140</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -6928,29 +6924,29 @@
         <v>13</v>
       </c>
       <c r="B177" s="7">
-        <v>632</v>
+        <v>1728</v>
       </c>
       <c t="s" r="C177" s="7">
         <v>14</v>
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>26</v>
+        <v>264</v>
       </c>
       <c t="s" r="H177" s="8">
         <v>135</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>24</v>
+        <v>235</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>92</v>
+        <v>265</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -6961,14 +6957,14 @@
         <v>13</v>
       </c>
       <c r="B178" s="7">
-        <v>720</v>
+        <v>8892</v>
       </c>
       <c t="s" r="C178" s="7">
         <v>14</v>
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -6977,72 +6973,64 @@
         <v>135</v>
       </c>
       <c t="s" r="H178" s="8">
-        <v>217</v>
+        <v>266</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>39</v>
+        <v>188</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>96</v>
-      </c>
-      <c t="s" r="K178" s="7">
-        <v>218</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="K178" s="7"/>
       <c r="L178" s="7"/>
-      <c t="s" r="M178" s="7">
-        <v>93</v>
-      </c>
+      <c r="M178" s="7"/>
     </row>
     <row r="179" ht="14.25" customHeight="1">
       <c t="s" r="A179" s="6">
         <v>13</v>
       </c>
       <c r="B179" s="7">
-        <v>721</v>
+        <v>8893</v>
       </c>
       <c t="s" r="C179" s="7">
         <v>14</v>
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G179" s="8">
-        <v>217</v>
+        <v>266</v>
       </c>
       <c t="s" r="H179" s="8">
         <v>135</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>93</v>
+        <v>142</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>269</v>
-      </c>
-      <c t="s" r="K179" s="7">
-        <v>97</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="K179" s="7"/>
       <c r="L179" s="7"/>
-      <c t="s" r="M179" s="7">
-        <v>235</v>
-      </c>
+      <c r="M179" s="7"/>
     </row>
     <row r="180" ht="15" customHeight="1">
       <c t="s" r="A180" s="6">
         <v>13</v>
       </c>
       <c r="B180" s="7">
-        <v>1729</v>
+        <v>878</v>
       </c>
       <c t="s" r="C180" s="7">
         <v>14</v>
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7051,47 +7039,29 @@
         <v>135</v>
       </c>
       <c t="s" r="H180" s="8">
-        <v>270</v>
+        <v>121</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
       <c r="M180" s="7"/>
     </row>
     <row r="181" ht="14.25" customHeight="1">
-      <c t="s" r="A181" s="6">
-        <v>13</v>
-      </c>
-      <c r="B181" s="7">
-        <v>1728</v>
-      </c>
-      <c t="s" r="C181" s="7">
-        <v>14</v>
-      </c>
+      <c r="A181" s="6"/>
+      <c r="B181" s="7"/>
+      <c r="C181" s="7"/>
       <c r="D181" s="7"/>
-      <c t="s" r="E181" s="7">
-        <v>267</v>
-      </c>
-      <c r="F181" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G181" s="8">
-        <v>270</v>
-      </c>
-      <c t="s" r="H181" s="8">
-        <v>135</v>
-      </c>
-      <c t="s" r="I181" s="7">
-        <v>236</v>
-      </c>
-      <c t="s" r="J181" s="7">
-        <v>271</v>
-      </c>
+      <c r="E181" s="7"/>
+      <c r="F181" s="7"/>
+      <c r="G181" s="8"/>
+      <c r="H181" s="8"/>
+      <c r="I181" s="7"/>
+      <c r="J181" s="7"/>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c r="M181" s="7"/>
@@ -7101,29 +7071,29 @@
         <v>13</v>
       </c>
       <c r="B182" s="7">
-        <v>8892</v>
+        <v>503</v>
       </c>
       <c t="s" r="C182" s="7">
         <v>14</v>
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H182" s="8">
         <v>135</v>
       </c>
-      <c t="s" r="H182" s="8">
-        <v>272</v>
-      </c>
       <c t="s" r="I182" s="7">
-        <v>188</v>
+        <v>29</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>160</v>
+        <v>91</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7134,29 +7104,29 @@
         <v>13</v>
       </c>
       <c r="B183" s="7">
-        <v>8893</v>
+        <v>524</v>
       </c>
       <c t="s" r="C183" s="7">
         <v>14</v>
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G183" s="8">
-        <v>272</v>
+        <v>135</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>135</v>
+        <v>16</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>142</v>
+        <v>92</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7167,45 +7137,63 @@
         <v>13</v>
       </c>
       <c r="B184" s="7">
-        <v>878</v>
+        <v>507</v>
       </c>
       <c t="s" r="C184" s="7">
         <v>14</v>
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H184" s="8">
         <v>135</v>
       </c>
-      <c t="s" r="H184" s="8">
-        <v>121</v>
-      </c>
       <c t="s" r="I184" s="7">
-        <v>273</v>
+        <v>114</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
       <c r="M184" s="7"/>
     </row>
     <row r="185" ht="15" customHeight="1">
-      <c r="A185" s="6"/>
-      <c r="B185" s="7"/>
-      <c r="C185" s="7"/>
+      <c t="s" r="A185" s="6">
+        <v>13</v>
+      </c>
+      <c r="B185" s="7">
+        <v>510</v>
+      </c>
+      <c t="s" r="C185" s="7">
+        <v>14</v>
+      </c>
       <c r="D185" s="7"/>
-      <c r="E185" s="7"/>
-      <c r="F185" s="7"/>
-      <c r="G185" s="8"/>
-      <c r="H185" s="8"/>
-      <c r="I185" s="7"/>
-      <c r="J185" s="7"/>
+      <c t="s" r="E185" s="7">
+        <v>268</v>
+      </c>
+      <c r="F185" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G185" s="8">
+        <v>135</v>
+      </c>
+      <c t="s" r="H185" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I185" s="7">
+        <v>218</v>
+      </c>
+      <c t="s" r="J185" s="7">
+        <v>54</v>
+      </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
       <c r="M185" s="7"/>
@@ -7215,14 +7203,14 @@
         <v>13</v>
       </c>
       <c r="B186" s="7">
-        <v>503</v>
+        <v>405</v>
       </c>
       <c t="s" r="C186" s="7">
         <v>14</v>
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7231,13 +7219,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H186" s="8">
-        <v>135</v>
+        <v>264</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>29</v>
+        <v>235</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7248,29 +7236,29 @@
         <v>13</v>
       </c>
       <c r="B187" s="7">
-        <v>524</v>
+        <v>406</v>
       </c>
       <c t="s" r="C187" s="7">
         <v>14</v>
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G187" s="8">
-        <v>135</v>
+        <v>264</v>
       </c>
       <c t="s" r="H187" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7281,14 +7269,14 @@
         <v>13</v>
       </c>
       <c r="B188" s="7">
-        <v>507</v>
+        <v>7526</v>
       </c>
       <c t="s" r="C188" s="7">
         <v>14</v>
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7297,13 +7285,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H188" s="8">
-        <v>135</v>
+        <v>269</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>114</v>
+        <v>270</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>73</v>
+        <v>214</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7311,66 +7299,48 @@
     </row>
     <row r="189" ht="14.25" customHeight="1">
       <c t="s" r="A189" s="6">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B189" s="7">
-        <v>510</v>
+        <v>7527</v>
       </c>
       <c t="s" r="C189" s="7">
         <v>14</v>
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G189" s="8">
-        <v>135</v>
+        <v>269</v>
       </c>
       <c t="s" r="H189" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>219</v>
+        <v>271</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>54</v>
+        <v>272</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c r="M189" s="7"/>
     </row>
     <row r="190" ht="15" customHeight="1">
-      <c t="s" r="A190" s="6">
-        <v>13</v>
-      </c>
-      <c r="B190" s="7">
-        <v>405</v>
-      </c>
-      <c t="s" r="C190" s="7">
-        <v>14</v>
-      </c>
+      <c r="A190" s="6"/>
+      <c r="B190" s="7"/>
+      <c r="C190" s="7"/>
       <c r="D190" s="7"/>
-      <c t="s" r="E190" s="7">
-        <v>274</v>
-      </c>
-      <c r="F190" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G190" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H190" s="8">
-        <v>270</v>
-      </c>
-      <c t="s" r="I190" s="7">
-        <v>236</v>
-      </c>
-      <c t="s" r="J190" s="7">
-        <v>75</v>
-      </c>
+      <c r="E190" s="7"/>
+      <c r="F190" s="7"/>
+      <c r="G190" s="8"/>
+      <c r="H190" s="8"/>
+      <c r="I190" s="7"/>
+      <c r="J190" s="7"/>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
       <c r="M190" s="7"/>
@@ -7380,29 +7350,29 @@
         <v>13</v>
       </c>
       <c r="B191" s="7">
-        <v>406</v>
+        <v>919</v>
       </c>
       <c t="s" r="C191" s="7">
         <v>14</v>
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G191" s="8">
-        <v>270</v>
+        <v>47</v>
       </c>
       <c t="s" r="H191" s="8">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>189</v>
+        <v>53</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7413,29 +7383,29 @@
         <v>13</v>
       </c>
       <c r="B192" s="7">
-        <v>7526</v>
+        <v>5530</v>
       </c>
       <c t="s" r="C192" s="7">
         <v>14</v>
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G192" s="8">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>215</v>
+        <v>55</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7443,81 +7413,81 @@
     </row>
     <row r="193" ht="14.25" customHeight="1">
       <c t="s" r="A193" s="6">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B193" s="7">
-        <v>7527</v>
+        <v>5531</v>
       </c>
       <c t="s" r="C193" s="7">
         <v>14</v>
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
+        <v>273</v>
+      </c>
+      <c r="F193" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G193" s="8">
+        <v>266</v>
+      </c>
+      <c t="s" r="H193" s="8">
+        <v>81</v>
+      </c>
+      <c t="s" r="I193" s="7">
+        <v>76</v>
+      </c>
+      <c t="s" r="J193" s="7">
         <v>274</v>
-      </c>
-      <c r="F193" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G193" s="8">
-        <v>262</v>
-      </c>
-      <c t="s" r="H193" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I193" s="7">
-        <v>275</v>
-      </c>
-      <c t="s" r="J193" s="7">
-        <v>276</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
       <c r="M193" s="7"/>
     </row>
     <row r="194" ht="14.25" customHeight="1">
-      <c r="A194" s="6"/>
-      <c r="B194" s="7"/>
-      <c r="C194" s="7"/>
+      <c t="s" r="A194" s="6">
+        <v>13</v>
+      </c>
+      <c r="B194" s="7">
+        <v>1601</v>
+      </c>
+      <c t="s" r="C194" s="7">
+        <v>14</v>
+      </c>
       <c r="D194" s="7"/>
-      <c r="E194" s="7"/>
-      <c r="F194" s="7"/>
-      <c r="G194" s="8"/>
-      <c r="H194" s="8"/>
-      <c r="I194" s="7"/>
-      <c r="J194" s="7"/>
+      <c t="s" r="E194" s="7">
+        <v>273</v>
+      </c>
+      <c r="F194" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G194" s="8">
+        <v>81</v>
+      </c>
+      <c t="s" r="H194" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="I194" s="7">
+        <v>189</v>
+      </c>
+      <c t="s" r="J194" s="7">
+        <v>275</v>
+      </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
       <c r="M194" s="7"/>
     </row>
     <row r="195" ht="15" customHeight="1">
-      <c t="s" r="A195" s="6">
-        <v>13</v>
-      </c>
-      <c r="B195" s="7">
-        <v>919</v>
-      </c>
-      <c t="s" r="C195" s="7">
-        <v>14</v>
-      </c>
+      <c r="A195" s="6"/>
+      <c r="B195" s="7"/>
+      <c r="C195" s="7"/>
       <c r="D195" s="7"/>
-      <c t="s" r="E195" s="7">
-        <v>277</v>
-      </c>
-      <c r="F195" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G195" s="8">
-        <v>47</v>
-      </c>
-      <c t="s" r="H195" s="8">
-        <v>81</v>
-      </c>
-      <c t="s" r="I195" s="7">
-        <v>136</v>
-      </c>
-      <c t="s" r="J195" s="7">
-        <v>53</v>
-      </c>
+      <c r="E195" s="7"/>
+      <c r="F195" s="7"/>
+      <c r="G195" s="8"/>
+      <c r="H195" s="8"/>
+      <c r="I195" s="7"/>
+      <c r="J195" s="7"/>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
       <c r="M195" s="7"/>
@@ -7527,29 +7497,29 @@
         <v>13</v>
       </c>
       <c r="B196" s="7">
-        <v>5530</v>
+        <v>811</v>
       </c>
       <c t="s" r="C196" s="7">
         <v>14</v>
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
+        <v>276</v>
+      </c>
+      <c r="F196" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G196" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H196" s="8">
         <v>277</v>
       </c>
-      <c r="F196" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G196" s="8">
-        <v>81</v>
-      </c>
-      <c t="s" r="H196" s="8">
-        <v>272</v>
-      </c>
       <c t="s" r="I196" s="7">
-        <v>192</v>
+        <v>30</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7560,29 +7530,29 @@
         <v>13</v>
       </c>
       <c r="B197" s="7">
-        <v>5531</v>
+        <v>984</v>
       </c>
       <c t="s" r="C197" s="7">
         <v>14</v>
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
+        <v>276</v>
+      </c>
+      <c r="F197" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G197" s="8">
         <v>277</v>
       </c>
-      <c r="F197" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G197" s="8">
-        <v>272</v>
-      </c>
       <c t="s" r="H197" s="8">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>278</v>
+        <v>248</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7593,78 +7563,78 @@
         <v>13</v>
       </c>
       <c r="B198" s="7">
-        <v>1601</v>
+        <v>983</v>
       </c>
       <c t="s" r="C198" s="7">
         <v>14</v>
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
+        <v>276</v>
+      </c>
+      <c r="F198" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G198" s="8">
+        <v>45</v>
+      </c>
+      <c t="s" r="H198" s="8">
         <v>277</v>
       </c>
-      <c r="F198" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G198" s="8">
-        <v>81</v>
-      </c>
-      <c t="s" r="H198" s="8">
-        <v>26</v>
-      </c>
       <c t="s" r="I198" s="7">
-        <v>189</v>
+        <v>243</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>279</v>
+        <v>244</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
       <c r="M198" s="7"/>
     </row>
     <row r="199" ht="14.25" customHeight="1">
-      <c r="A199" s="6"/>
-      <c r="B199" s="7"/>
-      <c r="C199" s="7"/>
+      <c t="s" r="A199" s="6">
+        <v>13</v>
+      </c>
+      <c r="B199" s="7">
+        <v>812</v>
+      </c>
+      <c t="s" r="C199" s="7">
+        <v>14</v>
+      </c>
       <c r="D199" s="7"/>
-      <c r="E199" s="7"/>
-      <c r="F199" s="7"/>
-      <c r="G199" s="8"/>
-      <c r="H199" s="8"/>
-      <c r="I199" s="7"/>
-      <c r="J199" s="7"/>
+      <c t="s" r="E199" s="7">
+        <v>276</v>
+      </c>
+      <c r="F199" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G199" s="8">
+        <v>277</v>
+      </c>
+      <c t="s" r="H199" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="I199" s="7">
+        <v>159</v>
+      </c>
+      <c t="s" r="J199" s="7">
+        <v>68</v>
+      </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
       <c r="M199" s="7"/>
     </row>
     <row r="200" ht="15" customHeight="1">
-      <c t="s" r="A200" s="6">
-        <v>13</v>
-      </c>
-      <c r="B200" s="7">
-        <v>811</v>
-      </c>
-      <c t="s" r="C200" s="7">
-        <v>14</v>
-      </c>
+      <c r="A200" s="6"/>
+      <c r="B200" s="7"/>
+      <c r="C200" s="7"/>
       <c r="D200" s="7"/>
-      <c t="s" r="E200" s="7">
-        <v>280</v>
-      </c>
-      <c r="F200" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G200" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="H200" s="8">
-        <v>281</v>
-      </c>
-      <c t="s" r="I200" s="7">
-        <v>30</v>
-      </c>
-      <c t="s" r="J200" s="7">
-        <v>95</v>
-      </c>
+      <c r="E200" s="7"/>
+      <c r="F200" s="7"/>
+      <c r="G200" s="8"/>
+      <c r="H200" s="8"/>
+      <c r="I200" s="7"/>
+      <c r="J200" s="7"/>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
       <c r="M200" s="7"/>
@@ -7674,29 +7644,29 @@
         <v>13</v>
       </c>
       <c r="B201" s="7">
-        <v>984</v>
+        <v>1382</v>
       </c>
       <c t="s" r="C201" s="7">
         <v>14</v>
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G201" s="8">
-        <v>281</v>
+        <v>26</v>
       </c>
       <c t="s" r="H201" s="8">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>40</v>
+        <v>279</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>249</v>
+        <v>224</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7707,29 +7677,29 @@
         <v>13</v>
       </c>
       <c r="B202" s="7">
-        <v>983</v>
+        <v>1383</v>
       </c>
       <c t="s" r="C202" s="7">
         <v>14</v>
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
+        <v>278</v>
+      </c>
+      <c r="F202" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G202" s="8">
+        <v>110</v>
+      </c>
+      <c t="s" r="H202" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="I202" s="7">
+        <v>171</v>
+      </c>
+      <c t="s" r="J202" s="7">
         <v>280</v>
-      </c>
-      <c r="F202" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G202" s="8">
-        <v>45</v>
-      </c>
-      <c t="s" r="H202" s="8">
-        <v>281</v>
-      </c>
-      <c t="s" r="I202" s="7">
-        <v>244</v>
-      </c>
-      <c t="s" r="J202" s="7">
-        <v>245</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7740,45 +7710,63 @@
         <v>13</v>
       </c>
       <c r="B203" s="7">
-        <v>812</v>
+        <v>272</v>
       </c>
       <c t="s" r="C203" s="7">
         <v>14</v>
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G203" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H203" s="8">
+        <v>216</v>
+      </c>
+      <c t="s" r="I203" s="7">
+        <v>30</v>
+      </c>
+      <c t="s" r="J203" s="7">
         <v>281</v>
-      </c>
-      <c t="s" r="H203" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="I203" s="7">
-        <v>159</v>
-      </c>
-      <c t="s" r="J203" s="7">
-        <v>68</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c r="M203" s="7"/>
     </row>
     <row r="204" ht="14.25" customHeight="1">
-      <c r="A204" s="6"/>
-      <c r="B204" s="7"/>
-      <c r="C204" s="7"/>
+      <c t="s" r="A204" s="6">
+        <v>13</v>
+      </c>
+      <c r="B204" s="7">
+        <v>273</v>
+      </c>
+      <c t="s" r="C204" s="7">
+        <v>14</v>
+      </c>
       <c r="D204" s="7"/>
-      <c r="E204" s="7"/>
-      <c r="F204" s="7"/>
-      <c r="G204" s="8"/>
-      <c r="H204" s="8"/>
-      <c r="I204" s="7"/>
-      <c r="J204" s="7"/>
+      <c t="s" r="E204" s="7">
+        <v>278</v>
+      </c>
+      <c r="F204" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G204" s="8">
+        <v>216</v>
+      </c>
+      <c t="s" r="H204" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="I204" s="7">
+        <v>72</v>
+      </c>
+      <c t="s" r="J204" s="7">
+        <v>103</v>
+      </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
       <c r="M204" s="7"/>
@@ -7788,14 +7776,14 @@
         <v>13</v>
       </c>
       <c r="B205" s="7">
-        <v>813</v>
+        <v>278</v>
       </c>
       <c t="s" r="C205" s="7">
         <v>14</v>
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7804,79 +7792,87 @@
         <v>26</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>281</v>
+        <v>216</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>283</v>
+        <v>116</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>134</v>
-      </c>
-      <c r="K205" s="7"/>
+        <v>194</v>
+      </c>
+      <c t="s" r="K205" s="7">
+        <v>193</v>
+      </c>
       <c r="L205" s="7"/>
-      <c r="M205" s="7"/>
+      <c t="s" r="M205" s="7">
+        <v>179</v>
+      </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
       <c t="s" r="A206" s="6">
         <v>13</v>
       </c>
       <c r="B206" s="7">
-        <v>970</v>
+        <v>279</v>
       </c>
       <c t="s" r="C206" s="7">
         <v>14</v>
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>281</v>
+        <v>216</v>
       </c>
       <c t="s" r="H206" s="8">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>284</v>
+        <v>157</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>235</v>
-      </c>
-      <c r="K206" s="7"/>
+        <v>221</v>
+      </c>
+      <c t="s" r="K206" s="7">
+        <v>196</v>
+      </c>
       <c r="L206" s="7"/>
-      <c r="M206" s="7"/>
+      <c t="s" r="M206" s="7">
+        <v>67</v>
+      </c>
     </row>
     <row r="207" ht="14.25" customHeight="1">
       <c t="s" r="A207" s="6">
         <v>13</v>
       </c>
       <c r="B207" s="7">
-        <v>8510</v>
+        <v>3908</v>
       </c>
       <c t="s" r="C207" s="7">
         <v>14</v>
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
+        <v>278</v>
+      </c>
+      <c r="F207" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G207" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H207" s="8">
+        <v>269</v>
+      </c>
+      <c t="s" r="I207" s="7">
         <v>282</v>
       </c>
-      <c r="F207" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G207" s="8">
-        <v>135</v>
-      </c>
-      <c t="s" r="H207" s="8">
-        <v>31</v>
-      </c>
-      <c t="s" r="I207" s="7">
-        <v>33</v>
-      </c>
       <c t="s" r="J207" s="7">
-        <v>34</v>
+        <v>283</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7884,81 +7880,81 @@
     </row>
     <row r="208" ht="14.25" customHeight="1">
       <c t="s" r="A208" s="6">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B208" s="7">
-        <v>8511</v>
+        <v>3909</v>
       </c>
       <c t="s" r="C208" s="7">
         <v>14</v>
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>31</v>
+        <v>269</v>
       </c>
       <c t="s" r="H208" s="8">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>44</v>
+        <v>284</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>68</v>
+        <v>285</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
       <c r="M208" s="7"/>
     </row>
     <row r="209" ht="14.25" customHeight="1">
-      <c t="s" r="A209" s="6">
-        <v>13</v>
-      </c>
-      <c r="B209" s="7">
-        <v>631</v>
-      </c>
-      <c t="s" r="C209" s="7">
-        <v>14</v>
-      </c>
+      <c r="A209" s="6"/>
+      <c r="B209" s="7"/>
+      <c r="C209" s="7"/>
       <c r="D209" s="7"/>
-      <c t="s" r="E209" s="7">
-        <v>282</v>
-      </c>
-      <c r="F209" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G209" s="8">
-        <v>135</v>
-      </c>
-      <c t="s" r="H209" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="I209" s="7">
-        <v>182</v>
-      </c>
-      <c t="s" r="J209" s="7">
-        <v>285</v>
-      </c>
+      <c r="E209" s="7"/>
+      <c r="F209" s="7"/>
+      <c r="G209" s="8"/>
+      <c r="H209" s="8"/>
+      <c r="I209" s="7"/>
+      <c r="J209" s="7"/>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c r="M209" s="7"/>
     </row>
     <row r="210" ht="15" customHeight="1">
-      <c r="A210" s="6"/>
-      <c r="B210" s="7"/>
-      <c r="C210" s="7"/>
+      <c t="s" r="A210" s="6">
+        <v>13</v>
+      </c>
+      <c r="B210" s="7">
+        <v>129</v>
+      </c>
+      <c t="s" r="C210" s="7">
+        <v>14</v>
+      </c>
       <c r="D210" s="7"/>
-      <c r="E210" s="7"/>
-      <c r="F210" s="7"/>
-      <c r="G210" s="8"/>
-      <c r="H210" s="8"/>
-      <c r="I210" s="7"/>
-      <c r="J210" s="7"/>
+      <c t="s" r="E210" s="7">
+        <v>286</v>
+      </c>
+      <c r="F210" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G210" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H210" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="I210" s="7">
+        <v>52</v>
+      </c>
+      <c t="s" r="J210" s="7">
+        <v>136</v>
+      </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c r="M210" s="7"/>
@@ -7968,7 +7964,7 @@
         <v>13</v>
       </c>
       <c r="B211" s="7">
-        <v>129</v>
+        <v>335</v>
       </c>
       <c t="s" r="C211" s="7">
         <v>14</v>
@@ -7981,16 +7977,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G211" s="8">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c t="s" r="H211" s="8">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>52</v>
+        <v>287</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>136</v>
+        <v>210</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -8001,7 +7997,7 @@
         <v>13</v>
       </c>
       <c r="B212" s="7">
-        <v>335</v>
+        <v>766</v>
       </c>
       <c t="s" r="C212" s="7">
         <v>14</v>
@@ -8014,16 +8010,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G212" s="8">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c t="s" r="H212" s="8">
-        <v>45</v>
+        <v>216</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>287</v>
+        <v>120</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>211</v>
+        <v>156</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -8034,7 +8030,7 @@
         <v>13</v>
       </c>
       <c r="B213" s="7">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c t="s" r="C213" s="7">
         <v>14</v>
@@ -8047,16 +8043,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G213" s="8">
+        <v>216</v>
+      </c>
+      <c t="s" r="H213" s="8">
         <v>45</v>
       </c>
-      <c t="s" r="H213" s="8">
-        <v>217</v>
-      </c>
       <c t="s" r="I213" s="7">
-        <v>120</v>
+        <v>178</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>156</v>
+        <v>187</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8067,7 +8063,7 @@
         <v>13</v>
       </c>
       <c r="B214" s="7">
-        <v>767</v>
+        <v>338</v>
       </c>
       <c t="s" r="C214" s="7">
         <v>14</v>
@@ -8080,65 +8076,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G214" s="8">
-        <v>217</v>
+        <v>45</v>
       </c>
       <c t="s" r="H214" s="8">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>187</v>
+        <v>57</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
       <c r="M214" s="7"/>
     </row>
     <row r="215" ht="15" customHeight="1">
-      <c t="s" r="A215" s="6">
-        <v>13</v>
-      </c>
-      <c r="B215" s="7">
-        <v>338</v>
-      </c>
-      <c t="s" r="C215" s="7">
-        <v>14</v>
-      </c>
+      <c r="A215" s="6"/>
+      <c r="B215" s="7"/>
+      <c r="C215" s="7"/>
       <c r="D215" s="7"/>
-      <c t="s" r="E215" s="7">
-        <v>286</v>
-      </c>
-      <c r="F215" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G215" s="8">
-        <v>45</v>
-      </c>
-      <c t="s" r="H215" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="I215" s="7">
-        <v>158</v>
-      </c>
-      <c t="s" r="J215" s="7">
-        <v>57</v>
-      </c>
+      <c r="E215" s="7"/>
+      <c r="F215" s="7"/>
+      <c r="G215" s="8"/>
+      <c r="H215" s="8"/>
+      <c r="I215" s="7"/>
+      <c r="J215" s="7"/>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
       <c r="M215" s="7"/>
     </row>
     <row r="216" ht="14.25" customHeight="1">
-      <c r="A216" s="6"/>
-      <c r="B216" s="7"/>
-      <c r="C216" s="7"/>
+      <c t="s" r="A216" s="6">
+        <v>13</v>
+      </c>
+      <c r="B216" s="7">
+        <v>447</v>
+      </c>
+      <c t="s" r="C216" s="7">
+        <v>14</v>
+      </c>
       <c r="D216" s="7"/>
-      <c r="E216" s="7"/>
-      <c r="F216" s="7"/>
-      <c r="G216" s="8"/>
-      <c r="H216" s="8"/>
-      <c r="I216" s="7"/>
-      <c r="J216" s="7"/>
+      <c t="s" r="E216" s="7">
+        <v>288</v>
+      </c>
+      <c r="F216" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G216" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H216" s="8">
+        <v>45</v>
+      </c>
+      <c t="s" r="I216" s="7">
+        <v>52</v>
+      </c>
+      <c t="s" r="J216" s="7">
+        <v>96</v>
+      </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
       <c r="M216" s="7"/>
@@ -8148,7 +8144,7 @@
         <v>13</v>
       </c>
       <c r="B217" s="7">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c t="s" r="C217" s="7">
         <v>14</v>
@@ -8161,16 +8157,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
+        <v>45</v>
+      </c>
+      <c t="s" r="H217" s="8">
         <v>16</v>
       </c>
-      <c t="s" r="H217" s="8">
-        <v>45</v>
-      </c>
       <c t="s" r="I217" s="7">
-        <v>52</v>
+        <v>287</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8181,7 +8177,7 @@
         <v>13</v>
       </c>
       <c r="B218" s="7">
-        <v>440</v>
+        <v>407</v>
       </c>
       <c t="s" r="C218" s="7">
         <v>14</v>
@@ -8194,16 +8190,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G218" s="8">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c t="s" r="H218" s="8">
-        <v>16</v>
+        <v>264</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>287</v>
+        <v>41</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>103</v>
+        <v>194</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8214,7 +8210,7 @@
         <v>13</v>
       </c>
       <c r="B219" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c t="s" r="C219" s="7">
         <v>14</v>
@@ -8227,16 +8223,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G219" s="8">
+        <v>264</v>
+      </c>
+      <c t="s" r="H219" s="8">
         <v>16</v>
       </c>
-      <c t="s" r="H219" s="8">
-        <v>270</v>
-      </c>
       <c t="s" r="I219" s="7">
-        <v>41</v>
+        <v>157</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8247,7 +8243,7 @@
         <v>13</v>
       </c>
       <c r="B220" s="7">
-        <v>408</v>
+        <v>1127</v>
       </c>
       <c t="s" r="C220" s="7">
         <v>14</v>
@@ -8260,16 +8256,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G220" s="8">
-        <v>270</v>
+        <v>16</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>157</v>
+        <v>57</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>188</v>
+        <v>289</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8280,7 +8276,7 @@
         <v>13</v>
       </c>
       <c r="B221" s="7">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c t="s" r="C221" s="7">
         <v>14</v>
@@ -8293,75 +8289,79 @@
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H221" s="8">
         <v>16</v>
       </c>
-      <c t="s" r="H221" s="8">
-        <v>26</v>
-      </c>
       <c t="s" r="I221" s="7">
-        <v>57</v>
+        <v>290</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
       <c r="M221" s="7"/>
     </row>
     <row r="222" ht="14.25" customHeight="1">
-      <c t="s" r="A222" s="6">
-        <v>13</v>
-      </c>
-      <c r="B222" s="7">
-        <v>1128</v>
-      </c>
-      <c t="s" r="C222" s="7">
-        <v>14</v>
-      </c>
+      <c r="A222" s="6"/>
+      <c r="B222" s="7"/>
+      <c r="C222" s="7"/>
       <c r="D222" s="7"/>
-      <c t="s" r="E222" s="7">
-        <v>288</v>
-      </c>
-      <c r="F222" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G222" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="H222" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I222" s="7">
-        <v>290</v>
-      </c>
-      <c t="s" r="J222" s="7">
-        <v>291</v>
-      </c>
+      <c r="E222" s="7"/>
+      <c r="F222" s="7"/>
+      <c r="G222" s="8"/>
+      <c r="H222" s="8"/>
+      <c r="I222" s="7"/>
+      <c r="J222" s="7"/>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
       <c r="M222" s="7"/>
     </row>
     <row r="223" ht="14.25" customHeight="1">
-      <c r="A223" s="6"/>
-      <c r="B223" s="7"/>
-      <c r="C223" s="7"/>
+      <c t="s" r="A223" s="6">
+        <v>13</v>
+      </c>
+      <c r="B223" s="7">
+        <v>869</v>
+      </c>
+      <c t="s" r="C223" s="7">
+        <v>14</v>
+      </c>
       <c r="D223" s="7"/>
-      <c r="E223" s="7"/>
-      <c r="F223" s="7"/>
-      <c r="G223" s="8"/>
-      <c r="H223" s="8"/>
-      <c r="I223" s="7"/>
-      <c r="J223" s="7"/>
-      <c r="K223" s="7"/>
+      <c t="s" r="E223" s="7">
+        <v>292</v>
+      </c>
+      <c r="F223" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G223" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="H223" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="I223" s="7">
+        <v>132</v>
+      </c>
+      <c t="s" r="J223" s="7">
+        <v>242</v>
+      </c>
+      <c t="s" r="K223" s="7">
+        <v>91</v>
+      </c>
       <c r="L223" s="7"/>
-      <c r="M223" s="7"/>
+      <c t="s" r="M223" s="7">
+        <v>115</v>
+      </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
       <c t="s" r="A224" s="6">
         <v>13</v>
       </c>
       <c r="B224" s="7">
-        <v>869</v>
+        <v>214</v>
       </c>
       <c t="s" r="C224" s="7">
         <v>14</v>
@@ -8374,31 +8374,27 @@
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c t="s" r="H224" s="8">
-        <v>26</v>
+        <v>173</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>243</v>
-      </c>
-      <c t="s" r="K224" s="7">
-        <v>91</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="K224" s="7"/>
       <c r="L224" s="7"/>
-      <c t="s" r="M224" s="7">
-        <v>115</v>
-      </c>
+      <c r="M224" s="7"/>
     </row>
     <row r="225" ht="15" customHeight="1">
       <c t="s" r="A225" s="6">
         <v>13</v>
       </c>
       <c r="B225" s="7">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c t="s" r="C225" s="7">
         <v>14</v>
@@ -8411,16 +8407,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G225" s="8">
-        <v>26</v>
+        <v>173</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>173</v>
+        <v>26</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>123</v>
+        <v>236</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>236</v>
+        <v>76</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8431,7 +8427,7 @@
         <v>13</v>
       </c>
       <c r="B226" s="7">
-        <v>213</v>
+        <v>154</v>
       </c>
       <c t="s" r="C226" s="7">
         <v>14</v>
@@ -8444,16 +8440,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>173</v>
+        <v>26</v>
       </c>
       <c t="s" r="H226" s="8">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>237</v>
+        <v>204</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>76</v>
+        <v>259</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8464,7 +8460,7 @@
         <v>13</v>
       </c>
       <c r="B227" s="7">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c t="s" r="C227" s="7">
         <v>14</v>
@@ -8477,65 +8473,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G227" s="8">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>205</v>
+        <v>293</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>293</v>
+        <v>267</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
       <c r="M227" s="7"/>
     </row>
     <row r="228" ht="14.25" customHeight="1">
-      <c t="s" r="A228" s="6">
-        <v>13</v>
-      </c>
-      <c r="B228" s="7">
-        <v>163</v>
-      </c>
-      <c t="s" r="C228" s="7">
-        <v>14</v>
-      </c>
+      <c r="A228" s="6"/>
+      <c r="B228" s="7"/>
+      <c r="C228" s="7"/>
       <c r="D228" s="7"/>
-      <c t="s" r="E228" s="7">
-        <v>292</v>
-      </c>
-      <c r="F228" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G228" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H228" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="I228" s="7">
-        <v>294</v>
-      </c>
-      <c t="s" r="J228" s="7">
-        <v>273</v>
-      </c>
+      <c r="E228" s="7"/>
+      <c r="F228" s="7"/>
+      <c r="G228" s="8"/>
+      <c r="H228" s="8"/>
+      <c r="I228" s="7"/>
+      <c r="J228" s="7"/>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
       <c r="M228" s="7"/>
     </row>
     <row r="229" ht="14.25" customHeight="1">
-      <c r="A229" s="6"/>
-      <c r="B229" s="7"/>
-      <c r="C229" s="7"/>
+      <c t="s" r="A229" s="6">
+        <v>13</v>
+      </c>
+      <c r="B229" s="7">
+        <v>989</v>
+      </c>
+      <c t="s" r="C229" s="7">
+        <v>14</v>
+      </c>
       <c r="D229" s="7"/>
-      <c r="E229" s="7"/>
-      <c r="F229" s="7"/>
-      <c r="G229" s="8"/>
-      <c r="H229" s="8"/>
-      <c r="I229" s="7"/>
-      <c r="J229" s="7"/>
+      <c t="s" r="E229" s="7">
+        <v>294</v>
+      </c>
+      <c r="F229" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G229" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="H229" s="8">
+        <v>135</v>
+      </c>
+      <c t="s" r="I229" s="7">
+        <v>295</v>
+      </c>
+      <c t="s" r="J229" s="7">
+        <v>32</v>
+      </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
       <c r="M229" s="7"/>
@@ -8545,29 +8541,29 @@
         <v>13</v>
       </c>
       <c r="B230" s="7">
-        <v>989</v>
+        <v>973</v>
       </c>
       <c t="s" r="C230" s="7">
         <v>14</v>
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G230" s="8">
-        <v>47</v>
+        <v>135</v>
       </c>
       <c t="s" r="H230" s="8">
-        <v>135</v>
+        <v>277</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>296</v>
+        <v>234</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>32</v>
+        <v>265</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -8578,29 +8574,29 @@
         <v>13</v>
       </c>
       <c r="B231" s="7">
-        <v>973</v>
+        <v>814</v>
       </c>
       <c t="s" r="C231" s="7">
         <v>14</v>
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G231" s="8">
-        <v>135</v>
+        <v>277</v>
       </c>
       <c t="s" r="H231" s="8">
-        <v>281</v>
+        <v>26</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>271</v>
+        <v>44</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8611,29 +8607,29 @@
         <v>13</v>
       </c>
       <c r="B232" s="7">
-        <v>814</v>
+        <v>3900</v>
       </c>
       <c t="s" r="C232" s="7">
         <v>14</v>
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
-        <v>281</v>
+        <v>26</v>
       </c>
       <c t="s" r="H232" s="8">
-        <v>26</v>
+        <v>296</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>221</v>
+        <v>189</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8641,81 +8637,81 @@
     </row>
     <row r="233" ht="14.25" customHeight="1">
       <c t="s" r="A233" s="6">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B233" s="7">
-        <v>3900</v>
+        <v>3901</v>
       </c>
       <c t="s" r="C233" s="7">
         <v>14</v>
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G233" s="8">
-        <v>26</v>
+        <v>296</v>
       </c>
       <c t="s" r="H233" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="I233" s="7">
         <v>297</v>
       </c>
-      <c t="s" r="I233" s="7">
-        <v>189</v>
-      </c>
       <c t="s" r="J233" s="7">
-        <v>36</v>
+        <v>298</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
       <c r="M233" s="7"/>
     </row>
     <row r="234" ht="14.25" customHeight="1">
-      <c t="s" r="A234" s="6">
-        <v>22</v>
-      </c>
-      <c r="B234" s="7">
-        <v>3901</v>
-      </c>
-      <c t="s" r="C234" s="7">
-        <v>14</v>
-      </c>
+      <c r="A234" s="6"/>
+      <c r="B234" s="7"/>
+      <c r="C234" s="7"/>
       <c r="D234" s="7"/>
-      <c t="s" r="E234" s="7">
-        <v>295</v>
-      </c>
-      <c r="F234" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G234" s="8">
-        <v>297</v>
-      </c>
-      <c t="s" r="H234" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="I234" s="7">
-        <v>298</v>
-      </c>
-      <c t="s" r="J234" s="7">
-        <v>299</v>
-      </c>
+      <c r="E234" s="7"/>
+      <c r="F234" s="7"/>
+      <c r="G234" s="8"/>
+      <c r="H234" s="8"/>
+      <c r="I234" s="7"/>
+      <c r="J234" s="7"/>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
       <c r="M234" s="7"/>
     </row>
     <row r="235" ht="15" customHeight="1">
-      <c r="A235" s="6"/>
-      <c r="B235" s="7"/>
-      <c r="C235" s="7"/>
+      <c t="s" r="A235" s="6">
+        <v>13</v>
+      </c>
+      <c r="B235" s="7">
+        <v>879</v>
+      </c>
+      <c t="s" r="C235" s="7">
+        <v>14</v>
+      </c>
       <c r="D235" s="7"/>
-      <c r="E235" s="7"/>
-      <c r="F235" s="7"/>
-      <c r="G235" s="8"/>
-      <c r="H235" s="8"/>
-      <c r="I235" s="7"/>
-      <c r="J235" s="7"/>
+      <c t="s" r="E235" s="7">
+        <v>299</v>
+      </c>
+      <c r="F235" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G235" s="8">
+        <v>121</v>
+      </c>
+      <c t="s" r="H235" s="8">
+        <v>135</v>
+      </c>
+      <c t="s" r="I235" s="7">
+        <v>240</v>
+      </c>
+      <c t="s" r="J235" s="7">
+        <v>128</v>
+      </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
       <c r="M235" s="7"/>
@@ -8725,29 +8721,29 @@
         <v>13</v>
       </c>
       <c r="B236" s="7">
-        <v>879</v>
+        <v>8890</v>
       </c>
       <c t="s" r="C236" s="7">
         <v>14</v>
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G236" s="8">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>135</v>
+        <v>266</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>241</v>
+        <v>137</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -8758,29 +8754,29 @@
         <v>13</v>
       </c>
       <c r="B237" s="7">
-        <v>8890</v>
+        <v>8891</v>
       </c>
       <c t="s" r="C237" s="7">
         <v>14</v>
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
+        <v>266</v>
+      </c>
+      <c t="s" r="H237" s="8">
         <v>135</v>
       </c>
-      <c t="s" r="H237" s="8">
-        <v>272</v>
-      </c>
       <c t="s" r="I237" s="7">
-        <v>137</v>
+        <v>235</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>99</v>
+        <v>186</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -8791,82 +8787,82 @@
         <v>13</v>
       </c>
       <c r="B238" s="7">
-        <v>8891</v>
+        <v>633</v>
       </c>
       <c t="s" r="C238" s="7">
         <v>14</v>
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
+        <v>299</v>
+      </c>
+      <c r="F238" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G238" s="8">
+        <v>135</v>
+      </c>
+      <c t="s" r="H238" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="I238" s="7">
+        <v>99</v>
+      </c>
+      <c t="s" r="J238" s="7">
+        <v>179</v>
+      </c>
+      <c t="s" r="K238" s="7">
+        <v>141</v>
+      </c>
+      <c r="L238" s="7"/>
+      <c t="s" r="M238" s="7">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="239" ht="14.25" customHeight="1">
+      <c r="A239" s="6"/>
+      <c r="B239" s="7"/>
+      <c r="C239" s="7"/>
+      <c r="D239" s="7"/>
+      <c r="E239" s="7"/>
+      <c r="F239" s="7"/>
+      <c r="G239" s="8"/>
+      <c r="H239" s="8"/>
+      <c r="I239" s="7"/>
+      <c r="J239" s="7"/>
+      <c r="K239" s="7"/>
+      <c r="L239" s="7"/>
+      <c r="M239" s="7"/>
+    </row>
+    <row r="240" ht="15" customHeight="1">
+      <c t="s" r="A240" s="6">
+        <v>13</v>
+      </c>
+      <c r="B240" s="7">
+        <v>823</v>
+      </c>
+      <c t="s" r="C240" s="7">
+        <v>14</v>
+      </c>
+      <c r="D240" s="7"/>
+      <c t="s" r="E240" s="7">
         <v>300</v>
       </c>
-      <c r="F238" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G238" s="8">
-        <v>272</v>
-      </c>
-      <c t="s" r="H238" s="8">
-        <v>135</v>
-      </c>
-      <c t="s" r="I238" s="7">
-        <v>236</v>
-      </c>
-      <c t="s" r="J238" s="7">
-        <v>186</v>
-      </c>
-      <c r="K238" s="7"/>
-      <c r="L238" s="7"/>
-      <c r="M238" s="7"/>
-    </row>
-    <row r="239" ht="14.25" customHeight="1">
-      <c t="s" r="A239" s="6">
-        <v>13</v>
-      </c>
-      <c r="B239" s="7">
-        <v>633</v>
-      </c>
-      <c t="s" r="C239" s="7">
-        <v>14</v>
-      </c>
-      <c r="D239" s="7"/>
-      <c t="s" r="E239" s="7">
-        <v>300</v>
-      </c>
-      <c r="F239" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G239" s="8">
-        <v>135</v>
-      </c>
-      <c t="s" r="H239" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="I239" s="7">
-        <v>99</v>
-      </c>
-      <c t="s" r="J239" s="7">
-        <v>179</v>
-      </c>
-      <c t="s" r="K239" s="7">
-        <v>141</v>
-      </c>
-      <c r="L239" s="7"/>
-      <c t="s" r="M239" s="7">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="240" ht="15" customHeight="1">
-      <c r="A240" s="6"/>
-      <c r="B240" s="7"/>
-      <c r="C240" s="7"/>
-      <c r="D240" s="7"/>
-      <c r="E240" s="7"/>
-      <c r="F240" s="7"/>
-      <c r="G240" s="8"/>
-      <c r="H240" s="8"/>
-      <c r="I240" s="7"/>
-      <c r="J240" s="7"/>
+      <c r="F240" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G240" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H240" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="I240" s="7">
+        <v>225</v>
+      </c>
+      <c t="s" r="J240" s="7">
+        <v>146</v>
+      </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
       <c r="M240" s="7"/>
@@ -8876,152 +8872,152 @@
         <v>13</v>
       </c>
       <c r="B241" s="7">
-        <v>823</v>
+        <v>842</v>
       </c>
       <c t="s" r="C241" s="7">
         <v>14</v>
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c t="s" r="H241" s="8">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>226</v>
+        <v>103</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>146</v>
-      </c>
-      <c r="K241" s="7"/>
+        <v>34</v>
+      </c>
+      <c t="s" r="K241" s="7">
+        <v>116</v>
+      </c>
       <c r="L241" s="7"/>
-      <c r="M241" s="7"/>
+      <c t="s" r="M241" s="7">
+        <v>221</v>
+      </c>
     </row>
     <row r="242" ht="14.25" customHeight="1">
       <c t="s" r="A242" s="6">
         <v>13</v>
       </c>
       <c r="B242" s="7">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c t="s" r="C242" s="7">
         <v>14</v>
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>103</v>
+        <v>44</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>34</v>
+        <v>230</v>
       </c>
       <c t="s" r="K242" s="7">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="L242" s="7"/>
       <c t="s" r="M242" s="7">
-        <v>222</v>
+        <v>301</v>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
       <c t="s" r="A243" s="6">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B243" s="7">
-        <v>843</v>
+        <v>91</v>
       </c>
       <c t="s" r="C243" s="7">
         <v>14</v>
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c t="s" r="H243" s="8">
-        <v>26</v>
+        <v>251</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>231</v>
-      </c>
-      <c t="s" r="K243" s="7">
-        <v>122</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="K243" s="7"/>
       <c r="L243" s="7"/>
-      <c t="s" r="M243" s="7">
-        <v>302</v>
-      </c>
+      <c r="M243" s="7"/>
     </row>
     <row r="244" ht="14.25" customHeight="1">
-      <c t="s" r="A244" s="6">
-        <v>22</v>
-      </c>
-      <c r="B244" s="7">
-        <v>91</v>
-      </c>
-      <c t="s" r="C244" s="7">
-        <v>14</v>
-      </c>
+      <c r="A244" s="6"/>
+      <c r="B244" s="7"/>
+      <c r="C244" s="7"/>
       <c r="D244" s="7"/>
-      <c t="s" r="E244" s="7">
-        <v>301</v>
-      </c>
-      <c r="F244" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G244" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="H244" s="8">
-        <v>252</v>
-      </c>
-      <c t="s" r="I244" s="7">
-        <v>36</v>
-      </c>
-      <c t="s" r="J244" s="7">
-        <v>226</v>
-      </c>
+      <c r="E244" s="7"/>
+      <c r="F244" s="7"/>
+      <c r="G244" s="8"/>
+      <c r="H244" s="8"/>
+      <c r="I244" s="7"/>
+      <c r="J244" s="7"/>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
       <c r="M244" s="7"/>
     </row>
     <row r="245" ht="15" customHeight="1">
-      <c r="A245" s="6"/>
-      <c r="B245" s="7"/>
-      <c r="C245" s="7"/>
+      <c t="s" r="A245" s="6">
+        <v>13</v>
+      </c>
+      <c r="B245" s="7">
+        <v>835</v>
+      </c>
+      <c t="s" r="C245" s="7">
+        <v>14</v>
+      </c>
       <c r="D245" s="7"/>
-      <c r="E245" s="7"/>
-      <c r="F245" s="7"/>
-      <c r="G245" s="8"/>
-      <c r="H245" s="8"/>
-      <c r="I245" s="7"/>
-      <c r="J245" s="7"/>
+      <c t="s" r="E245" s="7">
+        <v>302</v>
+      </c>
+      <c r="F245" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G245" s="8">
+        <v>121</v>
+      </c>
+      <c t="s" r="H245" s="8">
+        <v>81</v>
+      </c>
+      <c t="s" r="I245" s="7">
+        <v>224</v>
+      </c>
+      <c t="s" r="J245" s="7">
+        <v>112</v>
+      </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
       <c r="M245" s="7"/>
@@ -9031,29 +9027,29 @@
         <v>13</v>
       </c>
       <c r="B246" s="7">
-        <v>835</v>
+        <v>730</v>
       </c>
       <c t="s" r="C246" s="7">
         <v>14</v>
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G246" s="8">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c t="s" r="H246" s="8">
-        <v>81</v>
+        <v>216</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>112</v>
+        <v>210</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -9064,29 +9060,29 @@
         <v>13</v>
       </c>
       <c r="B247" s="7">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c t="s" r="C247" s="7">
         <v>14</v>
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
+        <v>302</v>
+      </c>
+      <c r="F247" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G247" s="8">
+        <v>216</v>
+      </c>
+      <c t="s" r="H247" s="8">
+        <v>81</v>
+      </c>
+      <c t="s" r="I247" s="7">
+        <v>146</v>
+      </c>
+      <c t="s" r="J247" s="7">
         <v>303</v>
-      </c>
-      <c r="F247" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G247" s="8">
-        <v>81</v>
-      </c>
-      <c t="s" r="H247" s="8">
-        <v>217</v>
-      </c>
-      <c t="s" r="I247" s="7">
-        <v>242</v>
-      </c>
-      <c t="s" r="J247" s="7">
-        <v>211</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9097,26 +9093,26 @@
         <v>13</v>
       </c>
       <c r="B248" s="7">
-        <v>731</v>
+        <v>774</v>
       </c>
       <c t="s" r="C248" s="7">
         <v>14</v>
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G248" s="8">
-        <v>217</v>
+        <v>81</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>81</v>
+        <v>16</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>146</v>
+        <v>227</v>
       </c>
       <c t="s" r="J248" s="7">
         <v>304</v>
@@ -9130,26 +9126,26 @@
         <v>13</v>
       </c>
       <c r="B249" s="7">
-        <v>774</v>
+        <v>787</v>
       </c>
       <c t="s" r="C249" s="7">
         <v>14</v>
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H249" s="8">
         <v>81</v>
       </c>
-      <c t="s" r="H249" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I249" s="7">
-        <v>228</v>
+        <v>66</v>
       </c>
       <c t="s" r="J249" s="7">
         <v>305</v>
@@ -9163,78 +9159,78 @@
         <v>13</v>
       </c>
       <c r="B250" s="7">
-        <v>787</v>
+        <v>834</v>
       </c>
       <c t="s" r="C250" s="7">
         <v>14</v>
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G250" s="8">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c t="s" r="H250" s="8">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>66</v>
+        <v>306</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>306</v>
+        <v>279</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
       <c r="M250" s="7"/>
     </row>
     <row r="251" ht="14.25" customHeight="1">
-      <c t="s" r="A251" s="6">
-        <v>13</v>
-      </c>
-      <c r="B251" s="7">
-        <v>834</v>
-      </c>
-      <c t="s" r="C251" s="7">
-        <v>14</v>
-      </c>
+      <c r="A251" s="6"/>
+      <c r="B251" s="7"/>
+      <c r="C251" s="7"/>
       <c r="D251" s="7"/>
-      <c t="s" r="E251" s="7">
-        <v>303</v>
-      </c>
-      <c r="F251" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G251" s="8">
-        <v>81</v>
-      </c>
-      <c t="s" r="H251" s="8">
-        <v>121</v>
-      </c>
-      <c t="s" r="I251" s="7">
-        <v>307</v>
-      </c>
-      <c t="s" r="J251" s="7">
-        <v>259</v>
-      </c>
+      <c r="E251" s="7"/>
+      <c r="F251" s="7"/>
+      <c r="G251" s="8"/>
+      <c r="H251" s="8"/>
+      <c r="I251" s="7"/>
+      <c r="J251" s="7"/>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c r="M251" s="7"/>
     </row>
     <row r="252" ht="14.25" customHeight="1">
-      <c r="A252" s="6"/>
-      <c r="B252" s="7"/>
-      <c r="C252" s="7"/>
+      <c t="s" r="A252" s="6">
+        <v>13</v>
+      </c>
+      <c r="B252" s="7">
+        <v>915</v>
+      </c>
+      <c t="s" r="C252" s="7">
+        <v>14</v>
+      </c>
       <c r="D252" s="7"/>
-      <c r="E252" s="7"/>
-      <c r="F252" s="7"/>
-      <c r="G252" s="8"/>
-      <c r="H252" s="8"/>
-      <c r="I252" s="7"/>
-      <c r="J252" s="7"/>
+      <c t="s" r="E252" s="7">
+        <v>307</v>
+      </c>
+      <c r="F252" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G252" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H252" s="8">
+        <v>277</v>
+      </c>
+      <c t="s" r="I252" s="7">
+        <v>112</v>
+      </c>
+      <c t="s" r="J252" s="7">
+        <v>116</v>
+      </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
       <c r="M252" s="7"/>
@@ -9244,29 +9240,29 @@
         <v>13</v>
       </c>
       <c r="B253" s="7">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c t="s" r="C253" s="7">
         <v>14</v>
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G253" s="8">
+        <v>277</v>
+      </c>
+      <c t="s" r="H253" s="8">
         <v>16</v>
       </c>
-      <c t="s" r="H253" s="8">
-        <v>281</v>
-      </c>
       <c t="s" r="I253" s="7">
-        <v>112</v>
+        <v>185</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>116</v>
+        <v>55</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9277,29 +9273,29 @@
         <v>13</v>
       </c>
       <c r="B254" s="7">
-        <v>916</v>
+        <v>781</v>
       </c>
       <c t="s" r="C254" s="7">
         <v>14</v>
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G254" s="8">
-        <v>281</v>
+        <v>16</v>
       </c>
       <c t="s" r="H254" s="8">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9310,78 +9306,78 @@
         <v>13</v>
       </c>
       <c r="B255" s="7">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c t="s" r="C255" s="7">
         <v>14</v>
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
+        <v>307</v>
+      </c>
+      <c r="F255" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G255" s="8">
+        <v>81</v>
+      </c>
+      <c t="s" r="H255" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I255" s="7">
+        <v>68</v>
+      </c>
+      <c t="s" r="J255" s="7">
         <v>308</v>
-      </c>
-      <c r="F255" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G255" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H255" s="8">
-        <v>81</v>
-      </c>
-      <c t="s" r="I255" s="7">
-        <v>188</v>
-      </c>
-      <c t="s" r="J255" s="7">
-        <v>21</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
       <c r="M255" s="7"/>
     </row>
     <row r="256" ht="14.25" customHeight="1">
-      <c t="s" r="A256" s="6">
-        <v>13</v>
-      </c>
-      <c r="B256" s="7">
-        <v>780</v>
-      </c>
-      <c t="s" r="C256" s="7">
-        <v>14</v>
-      </c>
+      <c r="A256" s="6"/>
+      <c r="B256" s="7"/>
+      <c r="C256" s="7"/>
       <c r="D256" s="7"/>
-      <c t="s" r="E256" s="7">
-        <v>308</v>
-      </c>
-      <c r="F256" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G256" s="8">
-        <v>81</v>
-      </c>
-      <c t="s" r="H256" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I256" s="7">
-        <v>68</v>
-      </c>
-      <c t="s" r="J256" s="7">
-        <v>309</v>
-      </c>
+      <c r="E256" s="7"/>
+      <c r="F256" s="7"/>
+      <c r="G256" s="8"/>
+      <c r="H256" s="8"/>
+      <c r="I256" s="7"/>
+      <c r="J256" s="7"/>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c r="M256" s="7"/>
     </row>
     <row r="257" ht="14.25" customHeight="1">
-      <c r="A257" s="6"/>
-      <c r="B257" s="7"/>
-      <c r="C257" s="7"/>
+      <c t="s" r="A257" s="6">
+        <v>13</v>
+      </c>
+      <c r="B257" s="7">
+        <v>981</v>
+      </c>
+      <c t="s" r="C257" s="7">
+        <v>14</v>
+      </c>
       <c r="D257" s="7"/>
-      <c r="E257" s="7"/>
-      <c r="F257" s="7"/>
-      <c r="G257" s="8"/>
-      <c r="H257" s="8"/>
-      <c r="I257" s="7"/>
-      <c r="J257" s="7"/>
+      <c t="s" r="E257" s="7">
+        <v>309</v>
+      </c>
+      <c r="F257" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G257" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="H257" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I257" s="7">
+        <v>132</v>
+      </c>
+      <c t="s" r="J257" s="7">
+        <v>177</v>
+      </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
       <c r="M257" s="7"/>
@@ -9391,29 +9387,29 @@
         <v>13</v>
       </c>
       <c r="B258" s="7">
-        <v>981</v>
+        <v>901</v>
       </c>
       <c t="s" r="C258" s="7">
         <v>14</v>
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
+        <v>309</v>
+      </c>
+      <c r="F258" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G258" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H258" s="8">
         <v>310</v>
       </c>
-      <c r="F258" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G258" s="8">
-        <v>47</v>
-      </c>
-      <c t="s" r="H258" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I258" s="7">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>177</v>
+        <v>139</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9424,29 +9420,29 @@
         <v>13</v>
       </c>
       <c r="B259" s="7">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c t="s" r="C259" s="7">
         <v>14</v>
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
+        <v>309</v>
+      </c>
+      <c r="F259" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G259" s="8">
         <v>310</v>
       </c>
-      <c r="F259" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G259" s="8">
+      <c t="s" r="H259" s="8">
         <v>16</v>
       </c>
-      <c t="s" r="H259" s="8">
-        <v>311</v>
-      </c>
       <c t="s" r="I259" s="7">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>139</v>
+        <v>194</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9457,29 +9453,29 @@
         <v>13</v>
       </c>
       <c r="B260" s="7">
-        <v>902</v>
+        <v>517</v>
       </c>
       <c t="s" r="C260" s="7">
         <v>14</v>
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>311</v>
+        <v>16</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>41</v>
+        <v>187</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -9490,29 +9486,29 @@
         <v>13</v>
       </c>
       <c r="B261" s="7">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c t="s" r="C261" s="7">
         <v>14</v>
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G261" s="8">
+        <v>135</v>
+      </c>
+      <c t="s" r="H261" s="8">
         <v>16</v>
       </c>
-      <c t="s" r="H261" s="8">
-        <v>135</v>
-      </c>
       <c t="s" r="I261" s="7">
-        <v>187</v>
+        <v>305</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>198</v>
+        <v>259</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9520,81 +9516,81 @@
     </row>
     <row r="262" ht="14.25" customHeight="1">
       <c t="s" r="A262" s="6">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B262" s="7">
-        <v>520</v>
+        <v>982</v>
       </c>
       <c t="s" r="C262" s="7">
         <v>14</v>
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>135</v>
+        <v>16</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
       <c r="M262" s="7"/>
     </row>
     <row r="263" ht="14.25" customHeight="1">
-      <c t="s" r="A263" s="6">
-        <v>22</v>
-      </c>
-      <c r="B263" s="7">
-        <v>982</v>
-      </c>
-      <c t="s" r="C263" s="7">
-        <v>14</v>
-      </c>
+      <c r="A263" s="6"/>
+      <c r="B263" s="7"/>
+      <c r="C263" s="7"/>
       <c r="D263" s="7"/>
-      <c t="s" r="E263" s="7">
-        <v>310</v>
-      </c>
-      <c r="F263" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G263" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H263" s="8">
-        <v>47</v>
-      </c>
-      <c t="s" r="I263" s="7">
-        <v>312</v>
-      </c>
-      <c t="s" r="J263" s="7">
-        <v>283</v>
-      </c>
+      <c r="E263" s="7"/>
+      <c r="F263" s="7"/>
+      <c r="G263" s="8"/>
+      <c r="H263" s="8"/>
+      <c r="I263" s="7"/>
+      <c r="J263" s="7"/>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
       <c r="M263" s="7"/>
     </row>
     <row r="264" ht="14.25" customHeight="1">
-      <c r="A264" s="6"/>
-      <c r="B264" s="7"/>
-      <c r="C264" s="7"/>
+      <c t="s" r="A264" s="6">
+        <v>13</v>
+      </c>
+      <c r="B264" s="7">
+        <v>952</v>
+      </c>
+      <c t="s" r="C264" s="7">
+        <v>14</v>
+      </c>
       <c r="D264" s="7"/>
-      <c r="E264" s="7"/>
-      <c r="F264" s="7"/>
-      <c r="G264" s="8"/>
-      <c r="H264" s="8"/>
-      <c r="I264" s="7"/>
-      <c r="J264" s="7"/>
+      <c t="s" r="E264" s="7">
+        <v>313</v>
+      </c>
+      <c r="F264" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G264" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H264" s="8">
+        <v>314</v>
+      </c>
+      <c t="s" r="I264" s="7">
+        <v>315</v>
+      </c>
+      <c t="s" r="J264" s="7">
+        <v>73</v>
+      </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
       <c r="M264" s="7"/>
@@ -9604,7 +9600,7 @@
         <v>13</v>
       </c>
       <c r="B265" s="7">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c t="s" r="C265" s="7">
         <v>14</v>
@@ -9617,16 +9613,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G265" s="8">
+        <v>314</v>
+      </c>
+      <c t="s" r="H265" s="8">
         <v>16</v>
       </c>
-      <c t="s" r="H265" s="8">
-        <v>314</v>
-      </c>
       <c t="s" r="I265" s="7">
-        <v>315</v>
+        <v>103</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>73</v>
+        <v>179</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9637,7 +9633,7 @@
         <v>13</v>
       </c>
       <c r="B266" s="7">
-        <v>953</v>
+        <v>913</v>
       </c>
       <c t="s" r="C266" s="7">
         <v>14</v>
@@ -9650,16 +9646,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>314</v>
+        <v>16</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>16</v>
+        <v>316</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>103</v>
+        <v>265</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>179</v>
+        <v>317</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9670,7 +9666,7 @@
         <v>13</v>
       </c>
       <c r="B267" s="7">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c t="s" r="C267" s="7">
         <v>14</v>
@@ -9683,65 +9679,65 @@
         <v>320</v>
       </c>
       <c t="s" r="G267" s="8">
+        <v>316</v>
+      </c>
+      <c t="s" r="H267" s="8">
         <v>16</v>
       </c>
-      <c t="s" r="H267" s="8">
-        <v>316</v>
-      </c>
       <c t="s" r="I267" s="7">
-        <v>271</v>
+        <v>122</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>317</v>
+        <v>181</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c r="M267" s="7"/>
     </row>
     <row r="268" ht="14.25" customHeight="1">
-      <c t="s" r="A268" s="6">
-        <v>13</v>
-      </c>
-      <c r="B268" s="7">
-        <v>914</v>
-      </c>
-      <c t="s" r="C268" s="7">
-        <v>14</v>
-      </c>
+      <c r="A268" s="6"/>
+      <c r="B268" s="7"/>
+      <c r="C268" s="7"/>
       <c r="D268" s="7"/>
-      <c t="s" r="E268" s="7">
-        <v>313</v>
-      </c>
-      <c r="F268" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G268" s="8">
-        <v>316</v>
-      </c>
-      <c t="s" r="H268" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I268" s="7">
-        <v>122</v>
-      </c>
-      <c t="s" r="J268" s="7">
-        <v>181</v>
-      </c>
+      <c r="E268" s="7"/>
+      <c r="F268" s="7"/>
+      <c r="G268" s="8"/>
+      <c r="H268" s="8"/>
+      <c r="I268" s="7"/>
+      <c r="J268" s="7"/>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
       <c r="M268" s="7"/>
     </row>
     <row r="269" ht="14.25" customHeight="1">
-      <c r="A269" s="6"/>
-      <c r="B269" s="7"/>
-      <c r="C269" s="7"/>
+      <c t="s" r="A269" s="6">
+        <v>13</v>
+      </c>
+      <c r="B269" s="7">
+        <v>339</v>
+      </c>
+      <c t="s" r="C269" s="7">
+        <v>14</v>
+      </c>
       <c r="D269" s="7"/>
-      <c r="E269" s="7"/>
-      <c r="F269" s="7"/>
-      <c r="G269" s="8"/>
-      <c r="H269" s="8"/>
-      <c r="I269" s="7"/>
-      <c r="J269" s="7"/>
+      <c t="s" r="E269" s="7">
+        <v>318</v>
+      </c>
+      <c r="F269" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G269" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H269" s="8">
+        <v>45</v>
+      </c>
+      <c t="s" r="I269" s="7">
+        <v>106</v>
+      </c>
+      <c t="s" r="J269" s="7">
+        <v>91</v>
+      </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
       <c r="M269" s="7"/>
@@ -9751,7 +9747,7 @@
         <v>13</v>
       </c>
       <c r="B270" s="7">
-        <v>339</v>
+        <v>718</v>
       </c>
       <c t="s" r="C270" s="7">
         <v>14</v>
@@ -9764,16 +9760,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G270" s="8">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c t="s" r="H270" s="8">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -9784,7 +9780,7 @@
         <v>13</v>
       </c>
       <c r="B271" s="7">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c t="s" r="C271" s="7">
         <v>14</v>
@@ -9797,16 +9793,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G271" s="8">
+        <v>135</v>
+      </c>
+      <c t="s" r="H271" s="8">
         <v>45</v>
       </c>
-      <c t="s" r="H271" s="8">
-        <v>135</v>
-      </c>
       <c t="s" r="I271" s="7">
-        <v>63</v>
+        <v>184</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>114</v>
+        <v>319</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9817,7 +9813,7 @@
         <v>13</v>
       </c>
       <c r="B272" s="7">
-        <v>719</v>
+        <v>452</v>
       </c>
       <c t="s" r="C272" s="7">
         <v>14</v>
@@ -9830,16 +9826,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G272" s="8">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>184</v>
+        <v>123</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9850,7 +9846,7 @@
         <v>13</v>
       </c>
       <c r="B273" s="7">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c t="s" r="C273" s="7">
         <v>14</v>
@@ -9863,16 +9859,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G273" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H273" s="8">
         <v>45</v>
       </c>
-      <c t="s" r="H273" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I273" s="7">
-        <v>123</v>
+        <v>196</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>320</v>
+        <v>67</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -9883,7 +9879,7 @@
         <v>13</v>
       </c>
       <c r="B274" s="7">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c t="s" r="C274" s="7">
         <v>14</v>
@@ -9896,16 +9892,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G274" s="8">
+        <v>45</v>
+      </c>
+      <c t="s" r="H274" s="8">
         <v>16</v>
       </c>
-      <c t="s" r="H274" s="8">
-        <v>45</v>
-      </c>
       <c t="s" r="I274" s="7">
-        <v>196</v>
+        <v>57</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>67</v>
+        <v>230</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -9916,7 +9912,7 @@
         <v>13</v>
       </c>
       <c r="B275" s="7">
-        <v>442</v>
+        <v>167</v>
       </c>
       <c t="s" r="C275" s="7">
         <v>14</v>
@@ -9929,65 +9925,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G275" s="8">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c t="s" r="H275" s="8">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>57</v>
+        <v>321</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>231</v>
+        <v>322</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
       <c r="M275" s="7"/>
     </row>
     <row r="276" ht="14.25" customHeight="1">
-      <c t="s" r="A276" s="6">
-        <v>13</v>
-      </c>
-      <c r="B276" s="7">
-        <v>167</v>
-      </c>
-      <c t="s" r="C276" s="7">
-        <v>14</v>
-      </c>
+      <c r="A276" s="6"/>
+      <c r="B276" s="7"/>
+      <c r="C276" s="7"/>
       <c r="D276" s="7"/>
-      <c t="s" r="E276" s="7">
-        <v>318</v>
-      </c>
-      <c r="F276" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G276" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H276" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="I276" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="J276" s="7">
-        <v>322</v>
-      </c>
+      <c r="E276" s="7"/>
+      <c r="F276" s="7"/>
+      <c r="G276" s="8"/>
+      <c r="H276" s="8"/>
+      <c r="I276" s="7"/>
+      <c r="J276" s="7"/>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
       <c r="M276" s="7"/>
     </row>
     <row r="277" ht="14.25" customHeight="1">
-      <c r="A277" s="6"/>
-      <c r="B277" s="7"/>
-      <c r="C277" s="7"/>
+      <c t="s" r="A277" s="6">
+        <v>13</v>
+      </c>
+      <c r="B277" s="7">
+        <v>809</v>
+      </c>
+      <c t="s" r="C277" s="7">
+        <v>14</v>
+      </c>
       <c r="D277" s="7"/>
-      <c r="E277" s="7"/>
-      <c r="F277" s="7"/>
-      <c r="G277" s="8"/>
-      <c r="H277" s="8"/>
-      <c r="I277" s="7"/>
-      <c r="J277" s="7"/>
+      <c t="s" r="E277" s="7">
+        <v>323</v>
+      </c>
+      <c r="F277" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G277" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H277" s="8">
+        <v>324</v>
+      </c>
+      <c t="s" r="I277" s="7">
+        <v>91</v>
+      </c>
+      <c t="s" r="J277" s="7">
+        <v>136</v>
+      </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
       <c r="M277" s="7"/>
@@ -9997,7 +9993,7 @@
         <v>13</v>
       </c>
       <c r="B278" s="7">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c t="s" r="C278" s="7">
         <v>14</v>
@@ -10010,16 +10006,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>26</v>
+        <v>324</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>324</v>
+        <v>26</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>136</v>
+        <v>211</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -10030,7 +10026,7 @@
         <v>13</v>
       </c>
       <c r="B279" s="7">
-        <v>808</v>
+        <v>327</v>
       </c>
       <c t="s" r="C279" s="7">
         <v>14</v>
@@ -10043,16 +10039,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>324</v>
+        <v>26</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -10063,7 +10059,7 @@
         <v>13</v>
       </c>
       <c r="B280" s="7">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c t="s" r="C280" s="7">
         <v>14</v>
@@ -10076,16 +10072,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c t="s" r="H280" s="8">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>99</v>
+        <v>157</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>236</v>
+        <v>141</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10096,7 +10092,7 @@
         <v>13</v>
       </c>
       <c r="B281" s="7">
-        <v>326</v>
+        <v>352</v>
       </c>
       <c t="s" r="C281" s="7">
         <v>14</v>
@@ -10109,16 +10105,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>157</v>
+        <v>34</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>141</v>
+        <v>44</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10129,7 +10125,7 @@
         <v>13</v>
       </c>
       <c r="B282" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c t="s" r="C282" s="7">
         <v>14</v>
@@ -10142,16 +10138,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G282" s="8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c t="s" r="H282" s="8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>34</v>
+        <v>159</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10162,7 +10158,7 @@
         <v>13</v>
       </c>
       <c r="B283" s="7">
-        <v>353</v>
+        <v>822</v>
       </c>
       <c t="s" r="C283" s="7">
         <v>14</v>
@@ -10175,65 +10171,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G283" s="8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c t="s" r="H283" s="8">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>159</v>
+        <v>59</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>118</v>
+        <v>18</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
       <c r="M283" s="7"/>
     </row>
     <row r="284" ht="14.25" customHeight="1">
-      <c t="s" r="A284" s="6">
-        <v>13</v>
-      </c>
-      <c r="B284" s="7">
-        <v>822</v>
-      </c>
-      <c t="s" r="C284" s="7">
-        <v>14</v>
-      </c>
+      <c r="A284" s="6"/>
+      <c r="B284" s="7"/>
+      <c r="C284" s="7"/>
       <c r="D284" s="7"/>
-      <c t="s" r="E284" s="7">
-        <v>323</v>
-      </c>
-      <c r="F284" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G284" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="H284" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I284" s="7">
-        <v>59</v>
-      </c>
-      <c t="s" r="J284" s="7">
-        <v>18</v>
-      </c>
+      <c r="E284" s="7"/>
+      <c r="F284" s="7"/>
+      <c r="G284" s="8"/>
+      <c r="H284" s="8"/>
+      <c r="I284" s="7"/>
+      <c r="J284" s="7"/>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
       <c r="M284" s="7"/>
     </row>
     <row r="285" ht="15" customHeight="1">
-      <c r="A285" s="6"/>
-      <c r="B285" s="7"/>
-      <c r="C285" s="7"/>
+      <c t="s" r="A285" s="6">
+        <v>13</v>
+      </c>
+      <c r="B285" s="7">
+        <v>130</v>
+      </c>
+      <c t="s" r="C285" s="7">
+        <v>14</v>
+      </c>
       <c r="D285" s="7"/>
-      <c r="E285" s="7"/>
-      <c r="F285" s="7"/>
-      <c r="G285" s="8"/>
-      <c r="H285" s="8"/>
-      <c r="I285" s="7"/>
-      <c r="J285" s="7"/>
+      <c t="s" r="E285" s="7">
+        <v>325</v>
+      </c>
+      <c r="F285" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G285" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H285" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I285" s="7">
+        <v>133</v>
+      </c>
+      <c t="s" r="J285" s="7">
+        <v>96</v>
+      </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
       <c r="M285" s="7"/>
@@ -10243,7 +10239,7 @@
         <v>13</v>
       </c>
       <c r="B286" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c t="s" r="C286" s="7">
         <v>14</v>
@@ -10256,16 +10252,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G286" s="8">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c t="s" r="H286" s="8">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10276,7 +10272,7 @@
         <v>13</v>
       </c>
       <c r="B287" s="7">
-        <v>133</v>
+        <v>640</v>
       </c>
       <c t="s" r="C287" s="7">
         <v>14</v>
@@ -10289,16 +10285,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c t="s" r="H287" s="8">
-        <v>26</v>
+        <v>135</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>93</v>
+        <v>203</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>103</v>
+        <v>20</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10309,7 +10305,7 @@
         <v>13</v>
       </c>
       <c r="B288" s="7">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c t="s" r="C288" s="7">
         <v>14</v>
@@ -10322,16 +10318,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G288" s="8">
-        <v>26</v>
+        <v>135</v>
       </c>
       <c t="s" r="H288" s="8">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>204</v>
+        <v>326</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>20</v>
+        <v>244</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -10342,7 +10338,7 @@
         <v>13</v>
       </c>
       <c r="B289" s="7">
-        <v>639</v>
+        <v>895</v>
       </c>
       <c t="s" r="C289" s="7">
         <v>14</v>
@@ -10355,16 +10351,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G289" s="8">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>26</v>
+        <v>327</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>326</v>
+        <v>122</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>245</v>
+        <v>306</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10372,10 +10368,10 @@
     </row>
     <row r="290" ht="15" customHeight="1">
       <c t="s" r="A290" s="6">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B290" s="7">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c t="s" r="C290" s="7">
         <v>14</v>
@@ -10388,65 +10384,65 @@
         <v>320</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>26</v>
+        <v>327</v>
       </c>
       <c t="s" r="H290" s="8">
-        <v>327</v>
+        <v>26</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>122</v>
+        <v>328</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>307</v>
+        <v>131</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c r="M290" s="7"/>
     </row>
     <row r="291" ht="14.25" customHeight="1">
-      <c t="s" r="A291" s="6">
-        <v>22</v>
-      </c>
-      <c r="B291" s="7">
-        <v>896</v>
-      </c>
-      <c t="s" r="C291" s="7">
-        <v>14</v>
-      </c>
+      <c r="A291" s="6"/>
+      <c r="B291" s="7"/>
+      <c r="C291" s="7"/>
       <c r="D291" s="7"/>
-      <c t="s" r="E291" s="7">
-        <v>325</v>
-      </c>
-      <c r="F291" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G291" s="8">
-        <v>327</v>
-      </c>
-      <c t="s" r="H291" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="I291" s="7">
-        <v>328</v>
-      </c>
-      <c t="s" r="J291" s="7">
-        <v>131</v>
-      </c>
+      <c r="E291" s="7"/>
+      <c r="F291" s="7"/>
+      <c r="G291" s="8"/>
+      <c r="H291" s="8"/>
+      <c r="I291" s="7"/>
+      <c r="J291" s="7"/>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
       <c r="M291" s="7"/>
     </row>
     <row r="292" ht="14.25" customHeight="1">
-      <c r="A292" s="6"/>
-      <c r="B292" s="7"/>
-      <c r="C292" s="7"/>
+      <c t="s" r="A292" s="6">
+        <v>13</v>
+      </c>
+      <c r="B292" s="7">
+        <v>127</v>
+      </c>
+      <c t="s" r="C292" s="7">
+        <v>14</v>
+      </c>
       <c r="D292" s="7"/>
-      <c r="E292" s="7"/>
-      <c r="F292" s="7"/>
-      <c r="G292" s="8"/>
-      <c r="H292" s="8"/>
-      <c r="I292" s="7"/>
-      <c r="J292" s="7"/>
+      <c t="s" r="E292" s="7">
+        <v>329</v>
+      </c>
+      <c r="F292" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G292" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H292" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="I292" s="7">
+        <v>132</v>
+      </c>
+      <c t="s" r="J292" s="7">
+        <v>191</v>
+      </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
       <c r="M292" s="7"/>
@@ -10456,7 +10452,7 @@
         <v>13</v>
       </c>
       <c r="B293" s="7">
-        <v>127</v>
+        <v>887</v>
       </c>
       <c t="s" r="C293" s="7">
         <v>14</v>
@@ -10469,16 +10465,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G293" s="8">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c t="s" r="H293" s="8">
-        <v>26</v>
+        <v>277</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>191</v>
+        <v>249</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10489,7 +10485,7 @@
         <v>13</v>
       </c>
       <c r="B294" s="7">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c t="s" r="C294" s="7">
         <v>14</v>
@@ -10502,16 +10498,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>26</v>
+        <v>277</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>281</v>
+        <v>26</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>114</v>
+        <v>227</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10522,7 +10518,7 @@
         <v>13</v>
       </c>
       <c r="B295" s="7">
-        <v>882</v>
+        <v>310</v>
       </c>
       <c t="s" r="C295" s="7">
         <v>14</v>
@@ -10535,27 +10531,31 @@
         <v>321</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>281</v>
+        <v>26</v>
       </c>
       <c t="s" r="H295" s="8">
-        <v>26</v>
+        <v>209</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>20</v>
-      </c>
-      <c r="K295" s="7"/>
+        <v>158</v>
+      </c>
+      <c t="s" r="K295" s="7">
+        <v>304</v>
+      </c>
       <c r="L295" s="7"/>
-      <c r="M295" s="7"/>
+      <c t="s" r="M295" s="7">
+        <v>317</v>
+      </c>
     </row>
     <row r="296" ht="14.25" customHeight="1">
       <c t="s" r="A296" s="6">
         <v>13</v>
       </c>
       <c r="B296" s="7">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c t="s" r="C296" s="7">
         <v>14</v>
@@ -10568,73 +10568,69 @@
         <v>321</v>
       </c>
       <c t="s" r="G296" s="8">
-        <v>26</v>
+        <v>209</v>
       </c>
       <c t="s" r="H296" s="8">
-        <v>210</v>
+        <v>26</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>271</v>
+        <v>67</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>158</v>
+        <v>330</v>
       </c>
       <c t="s" r="K296" s="7">
-        <v>305</v>
+        <v>147</v>
       </c>
       <c r="L296" s="7"/>
       <c t="s" r="M296" s="7">
-        <v>317</v>
+        <v>180</v>
       </c>
     </row>
     <row r="297" ht="14.25" customHeight="1">
-      <c t="s" r="A297" s="6">
-        <v>13</v>
-      </c>
-      <c r="B297" s="7">
-        <v>309</v>
-      </c>
-      <c t="s" r="C297" s="7">
-        <v>14</v>
-      </c>
+      <c r="A297" s="6"/>
+      <c r="B297" s="7"/>
+      <c r="C297" s="7"/>
       <c r="D297" s="7"/>
-      <c t="s" r="E297" s="7">
-        <v>329</v>
-      </c>
-      <c r="F297" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G297" s="8">
-        <v>210</v>
-      </c>
-      <c t="s" r="H297" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="I297" s="7">
-        <v>67</v>
-      </c>
-      <c t="s" r="J297" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="K297" s="7">
-        <v>147</v>
-      </c>
+      <c r="E297" s="7"/>
+      <c r="F297" s="7"/>
+      <c r="G297" s="8"/>
+      <c r="H297" s="8"/>
+      <c r="I297" s="7"/>
+      <c r="J297" s="7"/>
+      <c r="K297" s="7"/>
       <c r="L297" s="7"/>
-      <c t="s" r="M297" s="7">
-        <v>180</v>
-      </c>
+      <c r="M297" s="7"/>
     </row>
     <row r="298" ht="14.25" customHeight="1">
-      <c r="A298" s="6"/>
-      <c r="B298" s="7"/>
-      <c r="C298" s="7"/>
+      <c t="s" r="A298" s="6">
+        <v>13</v>
+      </c>
+      <c r="B298" s="7">
+        <v>421</v>
+      </c>
+      <c t="s" r="C298" s="7">
+        <v>14</v>
+      </c>
       <c r="D298" s="7"/>
-      <c r="E298" s="7"/>
-      <c r="F298" s="7"/>
-      <c r="G298" s="8"/>
-      <c r="H298" s="8"/>
-      <c r="I298" s="7"/>
-      <c r="J298" s="7"/>
+      <c t="s" r="E298" s="7">
+        <v>331</v>
+      </c>
+      <c r="F298" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G298" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H298" s="8">
+        <v>117</v>
+      </c>
+      <c t="s" r="I298" s="7">
+        <v>312</v>
+      </c>
+      <c t="s" r="J298" s="7">
+        <v>52</v>
+      </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
       <c r="M298" s="7"/>
@@ -10644,7 +10640,7 @@
         <v>13</v>
       </c>
       <c r="B299" s="7">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c t="s" r="C299" s="7">
         <v>14</v>
@@ -10657,16 +10653,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G299" s="8">
+        <v>117</v>
+      </c>
+      <c t="s" r="H299" s="8">
         <v>16</v>
       </c>
-      <c t="s" r="H299" s="8">
-        <v>117</v>
-      </c>
       <c t="s" r="I299" s="7">
-        <v>283</v>
+        <v>176</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10677,7 +10673,7 @@
         <v>13</v>
       </c>
       <c r="B300" s="7">
-        <v>422</v>
+        <v>7076</v>
       </c>
       <c t="s" r="C300" s="7">
         <v>14</v>
@@ -10690,16 +10686,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>117</v>
+        <v>16</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>16</v>
+        <v>332</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>176</v>
+        <v>333</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>96</v>
+        <v>156</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10710,7 +10706,7 @@
         <v>13</v>
       </c>
       <c r="B301" s="7">
-        <v>7076</v>
+        <v>7077</v>
       </c>
       <c t="s" r="C301" s="7">
         <v>14</v>
@@ -10723,16 +10719,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G301" s="8">
+        <v>332</v>
+      </c>
+      <c t="s" r="H301" s="8">
         <v>16</v>
       </c>
-      <c t="s" r="H301" s="8">
-        <v>332</v>
-      </c>
       <c t="s" r="I301" s="7">
-        <v>333</v>
+        <v>194</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>156</v>
+        <v>265</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10743,7 +10739,7 @@
         <v>13</v>
       </c>
       <c r="B302" s="7">
-        <v>7077</v>
+        <v>495</v>
       </c>
       <c t="s" r="C302" s="7">
         <v>14</v>
@@ -10756,16 +10752,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>332</v>
+        <v>16</v>
       </c>
       <c t="s" r="H302" s="8">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>194</v>
+        <v>141</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>271</v>
+        <v>147</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10776,7 +10772,7 @@
         <v>13</v>
       </c>
       <c r="B303" s="7">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c t="s" r="C303" s="7">
         <v>14</v>
@@ -10789,65 +10785,65 @@
         <v>320</v>
       </c>
       <c t="s" r="G303" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="H303" s="8">
         <v>16</v>
       </c>
-      <c t="s" r="H303" s="8">
-        <v>27</v>
-      </c>
       <c t="s" r="I303" s="7">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>147</v>
+        <v>289</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
       <c r="M303" s="7"/>
     </row>
     <row r="304" ht="14.25" customHeight="1">
-      <c t="s" r="A304" s="6">
-        <v>13</v>
-      </c>
-      <c r="B304" s="7">
-        <v>496</v>
-      </c>
-      <c t="s" r="C304" s="7">
-        <v>14</v>
-      </c>
+      <c r="A304" s="6"/>
+      <c r="B304" s="7"/>
+      <c r="C304" s="7"/>
       <c r="D304" s="7"/>
-      <c t="s" r="E304" s="7">
-        <v>331</v>
-      </c>
-      <c r="F304" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G304" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="H304" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I304" s="7">
-        <v>148</v>
-      </c>
-      <c t="s" r="J304" s="7">
-        <v>289</v>
-      </c>
+      <c r="E304" s="7"/>
+      <c r="F304" s="7"/>
+      <c r="G304" s="8"/>
+      <c r="H304" s="8"/>
+      <c r="I304" s="7"/>
+      <c r="J304" s="7"/>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
       <c r="M304" s="7"/>
     </row>
     <row r="305" ht="15" customHeight="1">
-      <c r="A305" s="6"/>
-      <c r="B305" s="7"/>
-      <c r="C305" s="7"/>
+      <c t="s" r="A305" s="6">
+        <v>13</v>
+      </c>
+      <c r="B305" s="7">
+        <v>813</v>
+      </c>
+      <c t="s" r="C305" s="7">
+        <v>14</v>
+      </c>
       <c r="D305" s="7"/>
-      <c r="E305" s="7"/>
-      <c r="F305" s="7"/>
-      <c r="G305" s="8"/>
-      <c r="H305" s="8"/>
-      <c r="I305" s="7"/>
-      <c r="J305" s="7"/>
+      <c t="s" r="E305" s="7">
+        <v>334</v>
+      </c>
+      <c r="F305" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G305" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H305" s="8">
+        <v>277</v>
+      </c>
+      <c t="s" r="I305" s="7">
+        <v>312</v>
+      </c>
+      <c t="s" r="J305" s="7">
+        <v>134</v>
+      </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c r="M305" s="7"/>
@@ -10857,7 +10853,7 @@
         <v>13</v>
       </c>
       <c r="B306" s="7">
-        <v>120</v>
+        <v>970</v>
       </c>
       <c t="s" r="C306" s="7">
         <v>14</v>
@@ -10870,16 +10866,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G306" s="8">
-        <v>26</v>
+        <v>277</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c t="s" r="I306" s="7">
         <v>335</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>71</v>
+        <v>234</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10890,7 +10886,7 @@
         <v>13</v>
       </c>
       <c r="B307" s="7">
-        <v>929</v>
+        <v>8510</v>
       </c>
       <c t="s" r="C307" s="7">
         <v>14</v>
@@ -10903,16 +10899,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c t="s" r="H307" s="8">
-        <v>163</v>
+        <v>31</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>133</v>
+        <v>33</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -10923,7 +10919,7 @@
         <v>13</v>
       </c>
       <c r="B308" s="7">
-        <v>928</v>
+        <v>8511</v>
       </c>
       <c t="s" r="C308" s="7">
         <v>14</v>
@@ -10936,16 +10932,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G308" s="8">
-        <v>163</v>
+        <v>31</v>
       </c>
       <c t="s" r="H308" s="8">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>123</v>
+        <v>44</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>188</v>
+        <v>68</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -10956,7 +10952,7 @@
         <v>13</v>
       </c>
       <c r="B309" s="7">
-        <v>161</v>
+        <v>645</v>
       </c>
       <c t="s" r="C309" s="7">
         <v>14</v>
@@ -10969,20 +10965,24 @@
         <v>321</v>
       </c>
       <c t="s" r="G309" s="8">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c t="s" r="H309" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>293</v>
+        <v>181</v>
       </c>
       <c t="s" r="J309" s="7">
+        <v>270</v>
+      </c>
+      <c t="s" r="K309" s="7">
+        <v>126</v>
+      </c>
+      <c r="L309" s="7"/>
+      <c t="s" r="M309" s="7">
         <v>336</v>
       </c>
-      <c r="K309" s="7"/>
-      <c r="L309" s="7"/>
-      <c r="M309" s="7"/>
     </row>
     <row r="310" ht="15" customHeight="1">
       <c r="A310" s="6"/>
@@ -11020,7 +11020,7 @@
         <v>26</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c t="s" r="I311" s="7">
         <v>338</v>
@@ -11050,7 +11050,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>26</v>
@@ -11086,7 +11086,7 @@
         <v>26</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c t="s" r="I313" s="7">
         <v>54</v>
@@ -11116,16 +11116,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c t="s" r="H314" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11188,7 +11188,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c t="s" r="J316" s="7">
         <v>174</v>
@@ -11239,7 +11239,7 @@
         <v>39</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11302,7 +11302,7 @@
         <v>342</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c t="s" r="J320" s="7">
         <v>67</v>
@@ -11368,10 +11368,10 @@
         <v>343</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11482,7 +11482,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>283</v>
+        <v>312</v>
       </c>
       <c t="s" r="J326" s="7">
         <v>37</v>
@@ -11512,13 +11512,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c t="s" r="I327" s="7">
         <v>30</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11542,7 +11542,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c t="s" r="H328" s="8">
         <v>26</v>
@@ -11584,7 +11584,7 @@
         <v>146</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11614,7 +11614,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c t="s" r="J330" s="7">
         <v>320</v>
@@ -11647,7 +11647,7 @@
         <v>347</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c t="s" r="J331" s="7">
         <v>148</v>
@@ -11683,7 +11683,7 @@
         <v>330</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11728,7 +11728,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c t="s" r="J334" s="7">
         <v>350</v>
@@ -11761,10 +11761,10 @@
         <v>351</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -11824,7 +11824,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H337" s="8">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c t="s" r="I337" s="7">
         <v>125</v>
@@ -11854,7 +11854,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G338" s="8">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c t="s" r="H338" s="8">
         <v>16</v>
@@ -11908,7 +11908,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c t="s" r="J340" s="7">
         <v>53</v>
@@ -11941,7 +11941,7 @@
         <v>83</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c t="s" r="J341" s="7">
         <v>34</v>
@@ -11977,7 +11977,7 @@
         <v>44</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -12121,10 +12121,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12157,7 +12157,7 @@
         <v>189</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>285</v>
+        <v>199</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12403,7 +12403,7 @@
         <v>326</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12451,7 +12451,7 @@
         <v>362</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12517,7 +12517,7 @@
         <v>120</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12550,7 +12550,7 @@
         <v>178</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12658,7 +12658,7 @@
         <v>121</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c t="s" r="I365" s="7">
         <v>171</v>
@@ -12688,16 +12688,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c t="s" r="H366" s="8">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c t="s" r="I366" s="7">
         <v>179</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12721,13 +12721,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G367" s="8">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c t="s" r="J367" s="7">
         <v>364</v>
@@ -12754,7 +12754,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c t="s" r="H368" s="8">
         <v>121</v>
@@ -12877,7 +12877,7 @@
         <v>40</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12907,10 +12907,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12940,7 +12940,7 @@
         <v>135</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c t="s" r="J374" s="7">
         <v>104</v>
@@ -13009,7 +13009,7 @@
         <v>182</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -13234,7 +13234,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c t="s" r="J384" s="7">
         <v>39</v>
@@ -13267,7 +13267,7 @@
         <v>70</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c t="s" r="J385" s="7">
         <v>103</v>
@@ -13303,7 +13303,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13336,7 +13336,7 @@
         <v>157</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13366,7 +13366,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c t="s" r="J388" s="7">
         <v>181</v>
@@ -13414,7 +13414,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c t="s" r="J390" s="7">
         <v>94</v>
@@ -13516,7 +13516,7 @@
         <v>42</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13624,10 +13624,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H397" s="8">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c t="s" r="J397" s="7">
         <v>91</v>
@@ -13654,7 +13654,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G398" s="8">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c t="s" r="H398" s="8">
         <v>173</v>
@@ -13663,7 +13663,7 @@
         <v>92</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13690,7 +13690,7 @@
         <v>173</v>
       </c>
       <c t="s" r="H399" s="8">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c t="s" r="I399" s="7">
         <v>72</v>
@@ -13720,7 +13720,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G400" s="8">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c t="s" r="H400" s="8">
         <v>16</v>
@@ -13729,7 +13729,7 @@
         <v>53</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -13756,13 +13756,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c t="s" r="I401" s="7">
         <v>194</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -13786,7 +13786,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G402" s="8">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c t="s" r="H402" s="8">
         <v>16</v>
@@ -13942,7 +13942,7 @@
         <v>191</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -13969,13 +13969,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -13999,16 +13999,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -14035,7 +14035,7 @@
         <v>26</v>
       </c>
       <c t="s" r="H410" s="8">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c t="s" r="I410" s="7">
         <v>34</v>
@@ -14065,7 +14065,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G411" s="8">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c t="s" r="H411" s="8">
         <v>26</v>
@@ -14074,7 +14074,7 @@
         <v>118</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>199</v>
+        <v>270</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -14119,10 +14119,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
@@ -14233,10 +14233,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -14269,7 +14269,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14317,7 +14317,7 @@
         <v>132</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14395,7 +14395,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>284</v>
+        <v>335</v>
       </c>
       <c t="s" r="J423" s="7">
         <v>320</v>
@@ -14431,7 +14431,7 @@
         <v>181</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
@@ -14542,7 +14542,7 @@
         <v>81</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c t="s" r="J428" s="7">
         <v>388</v>
@@ -14623,10 +14623,10 @@
         <v>81</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
@@ -14659,7 +14659,7 @@
         <v>53</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
@@ -14770,10 +14770,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>

--- a/Data/FlightPlan/FPL_18OCT26.xlsx
+++ b/Data/FlightPlan/FPL_18OCT26.xlsx
@@ -449,543 +449,543 @@
     <t>VN-A535</t>
   </si>
   <si>
+    <t>HKT</t>
+  </si>
+  <si>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>15:50</t>
+  </si>
+  <si>
+    <t>16:25</t>
+  </si>
+  <si>
+    <t>19:30</t>
+  </si>
+  <si>
+    <t>VN-A536</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>07:35</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>18:20</t>
+  </si>
+  <si>
+    <t>20:50</t>
+  </si>
+  <si>
+    <t>22:40</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>CGK</t>
+  </si>
+  <si>
+    <t>09:45</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>16:40</t>
+  </si>
+  <si>
+    <t>BOM</t>
+  </si>
+  <si>
+    <t>19:40</t>
+  </si>
+  <si>
+    <t>23:15</t>
+  </si>
+  <si>
+    <t>00:15</t>
+  </si>
+  <si>
+    <t>07:15</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>15:40</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>16:35</t>
+  </si>
+  <si>
+    <t>17:45</t>
+  </si>
+  <si>
+    <t>18:15</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>15:55</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>17:20</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>10:25</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>04:05</t>
+  </si>
+  <si>
+    <t>08:03</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>12:25</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>15:35</t>
+  </si>
+  <si>
+    <t>01:10</t>
+  </si>
+  <si>
+    <t>VN-A553</t>
+  </si>
+  <si>
+    <t>HPH</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>13:15</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>18:25</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>BQS</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>04:45</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>VVO</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>16:20</t>
+  </si>
+  <si>
+    <t>22:20</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
     <t>12:55</t>
   </si>
   <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>23:20</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>KHV</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>02:40</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>05:15</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>23:05</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>DLI</t>
+  </si>
+  <si>
+    <t>16:55</t>
+  </si>
+  <si>
+    <t>MFM</t>
+  </si>
+  <si>
+    <t>23:45</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>19:10</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>SIN</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>21:45</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>00:25</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>21:35</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>19:35</t>
+  </si>
+  <si>
+    <t>22:55</t>
+  </si>
+  <si>
+    <t>VN-A648</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>07:10</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>HIJ</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>SAI</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>13:25</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>22:45</t>
+  </si>
+  <si>
+    <t>00:55</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
     <t>19:15</t>
   </si>
   <si>
     <t>19:45</t>
   </si>
   <si>
-    <t>VN-A536</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>07:35</t>
-  </si>
-  <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>15:05</t>
-  </si>
-  <si>
-    <t>16:25</t>
-  </si>
-  <si>
-    <t>18:20</t>
-  </si>
-  <si>
-    <t>19:30</t>
-  </si>
-  <si>
-    <t>20:50</t>
-  </si>
-  <si>
-    <t>22:40</t>
-  </si>
-  <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>CGK</t>
-  </si>
-  <si>
-    <t>09:45</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>16:40</t>
-  </si>
-  <si>
-    <t>BOM</t>
-  </si>
-  <si>
-    <t>19:40</t>
-  </si>
-  <si>
-    <t>23:15</t>
-  </si>
-  <si>
-    <t>00:15</t>
-  </si>
-  <si>
-    <t>07:15</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>10:40</t>
-  </si>
-  <si>
-    <t>15:40</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>20:40</t>
-  </si>
-  <si>
-    <t>21:10</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
-  </si>
-  <si>
-    <t>11:40</t>
-  </si>
-  <si>
-    <t>14:55</t>
-  </si>
-  <si>
-    <t>16:35</t>
-  </si>
-  <si>
-    <t>17:45</t>
-  </si>
-  <si>
-    <t>18:15</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>10:20</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>15:55</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>17:20</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>10:25</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>04:05</t>
-  </si>
-  <si>
-    <t>08:03</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>12:25</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>14:25</t>
-  </si>
-  <si>
-    <t>15:35</t>
-  </si>
-  <si>
-    <t>01:10</t>
-  </si>
-  <si>
-    <t>VN-A553</t>
-  </si>
-  <si>
-    <t>HPH</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>13:15</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>18:25</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>15:25</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>BQS</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>04:45</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>VVO</t>
-  </si>
-  <si>
-    <t>13:10</t>
-  </si>
-  <si>
-    <t>15:50</t>
-  </si>
-  <si>
-    <t>16:20</t>
-  </si>
-  <si>
-    <t>22:20</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>23:20</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>KHV</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>02:40</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>05:15</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>23:05</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>DLI</t>
-  </si>
-  <si>
-    <t>16:55</t>
-  </si>
-  <si>
-    <t>MFM</t>
-  </si>
-  <si>
-    <t>23:45</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>19:10</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>SIN</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>05:35</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>00:25</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>21:35</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>19:35</t>
-  </si>
-  <si>
-    <t>22:55</t>
-  </si>
-  <si>
-    <t>VN-A648</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>07:10</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>HIJ</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>SAI</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>13:25</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>22:45</t>
-  </si>
-  <si>
-    <t>00:55</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>HKT</t>
-  </si>
-  <si>
     <t>VN-A656</t>
   </si>
   <si>
@@ -1196,7 +1196,7 @@
     <t>Total Record(s): 361</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 18, 2026 02:27</t>
+    <t xml:space="preserve">Generated on  Oct 18, 2026 03:06</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3860,7 +3860,7 @@
         <v>13</v>
       </c>
       <c r="B77" s="7">
-        <v>849</v>
+        <v>809</v>
       </c>
       <c t="s" r="C77" s="7">
         <v>14</v>
@@ -3876,13 +3876,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H77" s="8">
-        <v>51</v>
+        <v>146</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -3893,7 +3893,7 @@
         <v>13</v>
       </c>
       <c r="B78" s="7">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c t="s" r="C78" s="7">
         <v>14</v>
@@ -3906,16 +3906,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G78" s="8">
-        <v>51</v>
+        <v>146</v>
       </c>
       <c t="s" r="H78" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>43</v>
+        <v>147</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -3926,7 +3926,7 @@
         <v>13</v>
       </c>
       <c r="B79" s="7">
-        <v>262</v>
+        <v>327</v>
       </c>
       <c t="s" r="C79" s="7">
         <v>14</v>
@@ -3942,13 +3942,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H79" s="8">
-        <v>130</v>
+        <v>45</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
@@ -3959,7 +3959,7 @@
         <v>13</v>
       </c>
       <c r="B80" s="7">
-        <v>263</v>
+        <v>326</v>
       </c>
       <c t="s" r="C80" s="7">
         <v>14</v>
@@ -3972,32 +3972,50 @@
         <v>321</v>
       </c>
       <c t="s" r="G80" s="8">
-        <v>130</v>
+        <v>45</v>
       </c>
       <c t="s" r="H80" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
       <c r="M80" s="7"/>
     </row>
     <row r="81" ht="14.25" customHeight="1">
-      <c r="A81" s="6"/>
-      <c r="B81" s="7"/>
-      <c r="C81" s="7"/>
+      <c t="s" r="A81" s="6">
+        <v>13</v>
+      </c>
+      <c r="B81" s="7">
+        <v>352</v>
+      </c>
+      <c t="s" r="C81" s="7">
+        <v>14</v>
+      </c>
       <c r="D81" s="7"/>
-      <c r="E81" s="7"/>
-      <c r="F81" s="7"/>
-      <c r="G81" s="8"/>
-      <c r="H81" s="8"/>
-      <c r="I81" s="7"/>
-      <c r="J81" s="7"/>
+      <c t="s" r="E81" s="7">
+        <v>145</v>
+      </c>
+      <c r="F81" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G81" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H81" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="I81" s="7">
+        <v>34</v>
+      </c>
+      <c t="s" r="J81" s="7">
+        <v>44</v>
+      </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
       <c r="M81" s="7"/>
@@ -4007,63 +4025,45 @@
         <v>13</v>
       </c>
       <c r="B82" s="7">
-        <v>771</v>
+        <v>353</v>
       </c>
       <c t="s" r="C82" s="7">
         <v>14</v>
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G82" s="8">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c t="s" r="H82" s="8">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c t="s" r="I82" s="7">
         <v>150</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>151</v>
+        <v>118</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
       <c r="M82" s="7"/>
     </row>
     <row r="83" ht="14.25" customHeight="1">
-      <c t="s" r="A83" s="6">
-        <v>13</v>
-      </c>
-      <c r="B83" s="7">
-        <v>770</v>
-      </c>
-      <c t="s" r="C83" s="7">
-        <v>14</v>
-      </c>
+      <c r="A83" s="6"/>
+      <c r="B83" s="7"/>
+      <c r="C83" s="7"/>
       <c r="D83" s="7"/>
-      <c t="s" r="E83" s="7">
-        <v>149</v>
-      </c>
-      <c r="F83" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G83" s="8">
-        <v>81</v>
-      </c>
-      <c t="s" r="H83" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I83" s="7">
-        <v>152</v>
-      </c>
-      <c t="s" r="J83" s="7">
-        <v>153</v>
-      </c>
+      <c r="E83" s="7"/>
+      <c r="F83" s="7"/>
+      <c r="G83" s="8"/>
+      <c r="H83" s="8"/>
+      <c r="I83" s="7"/>
+      <c r="J83" s="7"/>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
       <c r="M83" s="7"/>
@@ -4073,14 +4073,14 @@
         <v>13</v>
       </c>
       <c r="B84" s="7">
-        <v>1491</v>
+        <v>771</v>
       </c>
       <c t="s" r="C84" s="7">
         <v>14</v>
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4089,13 +4089,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H84" s="8">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4106,29 +4106,29 @@
         <v>13</v>
       </c>
       <c r="B85" s="7">
-        <v>1492</v>
+        <v>770</v>
       </c>
       <c t="s" r="C85" s="7">
         <v>14</v>
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G85" s="8">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c t="s" r="H85" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I85" s="7">
+        <v>154</v>
+      </c>
+      <c t="s" r="J85" s="7">
         <v>155</v>
-      </c>
-      <c t="s" r="J85" s="7">
-        <v>33</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4139,14 +4139,14 @@
         <v>13</v>
       </c>
       <c r="B86" s="7">
-        <v>1505</v>
+        <v>1491</v>
       </c>
       <c t="s" r="C86" s="7">
         <v>14</v>
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4155,13 +4155,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H86" s="8">
-        <v>135</v>
+        <v>27</v>
       </c>
       <c t="s" r="I86" s="7">
         <v>156</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -4172,29 +4172,29 @@
         <v>13</v>
       </c>
       <c r="B87" s="7">
-        <v>1504</v>
+        <v>1492</v>
       </c>
       <c t="s" r="C87" s="7">
         <v>14</v>
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G87" s="8">
-        <v>135</v>
+        <v>27</v>
       </c>
       <c t="s" r="H87" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>84</v>
+        <v>157</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>158</v>
+        <v>33</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -4205,14 +4205,14 @@
         <v>13</v>
       </c>
       <c r="B88" s="7">
-        <v>519</v>
+        <v>1505</v>
       </c>
       <c t="s" r="C88" s="7">
         <v>14</v>
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4224,10 +4224,10 @@
         <v>135</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4238,14 +4238,14 @@
         <v>13</v>
       </c>
       <c r="B89" s="7">
-        <v>522</v>
+        <v>1504</v>
       </c>
       <c t="s" r="C89" s="7">
         <v>14</v>
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4257,26 +4257,44 @@
         <v>16</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
       <c r="M89" s="7"/>
     </row>
     <row r="90" ht="15" customHeight="1">
-      <c r="A90" s="6"/>
-      <c r="B90" s="7"/>
-      <c r="C90" s="7"/>
+      <c t="s" r="A90" s="6">
+        <v>13</v>
+      </c>
+      <c r="B90" s="7">
+        <v>519</v>
+      </c>
+      <c t="s" r="C90" s="7">
+        <v>14</v>
+      </c>
       <c r="D90" s="7"/>
-      <c r="E90" s="7"/>
-      <c r="F90" s="7"/>
-      <c r="G90" s="8"/>
-      <c r="H90" s="8"/>
-      <c r="I90" s="7"/>
-      <c r="J90" s="7"/>
+      <c t="s" r="E90" s="7">
+        <v>151</v>
+      </c>
+      <c r="F90" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G90" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H90" s="8">
+        <v>135</v>
+      </c>
+      <c t="s" r="I90" s="7">
+        <v>150</v>
+      </c>
+      <c t="s" r="J90" s="7">
+        <v>160</v>
+      </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
       <c r="M90" s="7"/>
@@ -4286,63 +4304,45 @@
         <v>13</v>
       </c>
       <c r="B91" s="7">
-        <v>855</v>
+        <v>522</v>
       </c>
       <c t="s" r="C91" s="7">
         <v>14</v>
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G91" s="8">
-        <v>26</v>
+        <v>135</v>
       </c>
       <c t="s" r="H91" s="8">
-        <v>163</v>
+        <v>16</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>164</v>
+        <v>100</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
       <c r="M91" s="7"/>
     </row>
     <row r="92" ht="14.25" customHeight="1">
-      <c t="s" r="A92" s="6">
-        <v>13</v>
-      </c>
-      <c r="B92" s="7">
-        <v>854</v>
-      </c>
-      <c t="s" r="C92" s="7">
-        <v>14</v>
-      </c>
+      <c r="A92" s="6"/>
+      <c r="B92" s="7"/>
+      <c r="C92" s="7"/>
       <c r="D92" s="7"/>
-      <c t="s" r="E92" s="7">
-        <v>162</v>
-      </c>
-      <c r="F92" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G92" s="8">
-        <v>163</v>
-      </c>
-      <c t="s" r="H92" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="I92" s="7">
-        <v>103</v>
-      </c>
-      <c t="s" r="J92" s="7">
-        <v>166</v>
-      </c>
+      <c r="E92" s="7"/>
+      <c r="F92" s="7"/>
+      <c r="G92" s="8"/>
+      <c r="H92" s="8"/>
+      <c r="I92" s="7"/>
+      <c r="J92" s="7"/>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
       <c r="M92" s="7"/>
@@ -4352,7 +4352,7 @@
         <v>13</v>
       </c>
       <c r="B93" s="7">
-        <v>883</v>
+        <v>855</v>
       </c>
       <c t="s" r="C93" s="7">
         <v>14</v>
@@ -4368,13 +4368,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H93" s="8">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -4382,10 +4382,10 @@
     </row>
     <row r="94" ht="14.25" customHeight="1">
       <c t="s" r="A94" s="6">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B94" s="7">
-        <v>884</v>
+        <v>854</v>
       </c>
       <c t="s" r="C94" s="7">
         <v>14</v>
@@ -4398,98 +4398,98 @@
         <v>321</v>
       </c>
       <c t="s" r="G94" s="8">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c t="s" r="H94" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>170</v>
+        <v>103</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
       <c r="M94" s="7"/>
     </row>
     <row r="95" ht="15" customHeight="1">
-      <c r="A95" s="6"/>
-      <c r="B95" s="7"/>
-      <c r="C95" s="7"/>
+      <c t="s" r="A95" s="6">
+        <v>13</v>
+      </c>
+      <c r="B95" s="7">
+        <v>883</v>
+      </c>
+      <c t="s" r="C95" s="7">
+        <v>14</v>
+      </c>
       <c r="D95" s="7"/>
-      <c r="E95" s="7"/>
-      <c r="F95" s="7"/>
-      <c r="G95" s="8"/>
-      <c r="H95" s="8"/>
-      <c r="I95" s="7"/>
-      <c r="J95" s="7"/>
+      <c t="s" r="E95" s="7">
+        <v>162</v>
+      </c>
+      <c r="F95" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G95" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H95" s="8">
+        <v>167</v>
+      </c>
+      <c t="s" r="I95" s="7">
+        <v>168</v>
+      </c>
+      <c t="s" r="J95" s="7">
+        <v>169</v>
+      </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
       <c r="M95" s="7"/>
     </row>
     <row r="96" ht="14.25" customHeight="1">
       <c t="s" r="A96" s="6">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B96" s="7">
-        <v>224</v>
+        <v>884</v>
       </c>
       <c t="s" r="C96" s="7">
         <v>14</v>
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G96" s="8">
-        <v>26</v>
+        <v>167</v>
       </c>
       <c t="s" r="H96" s="8">
-        <v>173</v>
+        <v>26</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>90</v>
+        <v>171</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
       <c r="M96" s="7"/>
     </row>
     <row r="97" ht="14.25" customHeight="1">
-      <c t="s" r="A97" s="6">
-        <v>13</v>
-      </c>
-      <c r="B97" s="7">
-        <v>741</v>
-      </c>
-      <c t="s" r="C97" s="7">
-        <v>14</v>
-      </c>
+      <c r="A97" s="6"/>
+      <c r="B97" s="7"/>
+      <c r="C97" s="7"/>
       <c r="D97" s="7"/>
-      <c t="s" r="E97" s="7">
-        <v>172</v>
-      </c>
-      <c r="F97" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G97" s="8">
-        <v>173</v>
-      </c>
-      <c t="s" r="H97" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="I97" s="7">
-        <v>175</v>
-      </c>
-      <c t="s" r="J97" s="7">
-        <v>52</v>
-      </c>
+      <c r="E97" s="7"/>
+      <c r="F97" s="7"/>
+      <c r="G97" s="8"/>
+      <c r="H97" s="8"/>
+      <c r="I97" s="7"/>
+      <c r="J97" s="7"/>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
       <c r="M97" s="7"/>
@@ -4499,7 +4499,7 @@
         <v>13</v>
       </c>
       <c r="B98" s="7">
-        <v>740</v>
+        <v>224</v>
       </c>
       <c t="s" r="C98" s="7">
         <v>14</v>
@@ -4512,16 +4512,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G98" s="8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c t="s" r="H98" s="8">
         <v>173</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>177</v>
+        <v>90</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -4532,7 +4532,7 @@
         <v>13</v>
       </c>
       <c r="B99" s="7">
-        <v>227</v>
+        <v>741</v>
       </c>
       <c t="s" r="C99" s="7">
         <v>14</v>
@@ -4548,13 +4548,13 @@
         <v>173</v>
       </c>
       <c t="s" r="H99" s="8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>114</v>
+        <v>175</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -4565,7 +4565,7 @@
         <v>13</v>
       </c>
       <c r="B100" s="7">
-        <v>252</v>
+        <v>740</v>
       </c>
       <c t="s" r="C100" s="7">
         <v>14</v>
@@ -4578,16 +4578,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G100" s="8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c t="s" r="H100" s="8">
-        <v>89</v>
+        <v>173</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>98</v>
+        <v>176</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -4598,7 +4598,7 @@
         <v>13</v>
       </c>
       <c r="B101" s="7">
-        <v>253</v>
+        <v>227</v>
       </c>
       <c t="s" r="C101" s="7">
         <v>14</v>
@@ -4611,16 +4611,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G101" s="8">
-        <v>89</v>
+        <v>173</v>
       </c>
       <c t="s" r="H101" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>179</v>
+        <v>114</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -4631,7 +4631,7 @@
         <v>13</v>
       </c>
       <c r="B102" s="7">
-        <v>216</v>
+        <v>252</v>
       </c>
       <c t="s" r="C102" s="7">
         <v>14</v>
@@ -4647,13 +4647,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H102" s="8">
-        <v>173</v>
+        <v>89</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -4664,7 +4664,7 @@
         <v>13</v>
       </c>
       <c r="B103" s="7">
-        <v>217</v>
+        <v>253</v>
       </c>
       <c t="s" r="C103" s="7">
         <v>14</v>
@@ -4677,32 +4677,50 @@
         <v>321</v>
       </c>
       <c t="s" r="G103" s="8">
-        <v>173</v>
+        <v>89</v>
       </c>
       <c t="s" r="H103" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>182</v>
+        <v>76</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
       <c r="M103" s="7"/>
     </row>
     <row r="104" ht="14.25" customHeight="1">
-      <c r="A104" s="6"/>
-      <c r="B104" s="7"/>
-      <c r="C104" s="7"/>
+      <c t="s" r="A104" s="6">
+        <v>13</v>
+      </c>
+      <c r="B104" s="7">
+        <v>216</v>
+      </c>
+      <c t="s" r="C104" s="7">
+        <v>14</v>
+      </c>
       <c r="D104" s="7"/>
-      <c r="E104" s="7"/>
-      <c r="F104" s="7"/>
-      <c r="G104" s="8"/>
-      <c r="H104" s="8"/>
-      <c r="I104" s="7"/>
-      <c r="J104" s="7"/>
+      <c t="s" r="E104" s="7">
+        <v>172</v>
+      </c>
+      <c r="F104" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G104" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H104" s="8">
+        <v>173</v>
+      </c>
+      <c t="s" r="I104" s="7">
+        <v>67</v>
+      </c>
+      <c t="s" r="J104" s="7">
+        <v>180</v>
+      </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
       <c r="M104" s="7"/>
@@ -4712,63 +4730,45 @@
         <v>13</v>
       </c>
       <c r="B105" s="7">
-        <v>863</v>
+        <v>217</v>
       </c>
       <c t="s" r="C105" s="7">
         <v>14</v>
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G105" s="8">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c t="s" r="H105" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
       <c r="M105" s="7"/>
     </row>
     <row r="106" ht="14.25" customHeight="1">
-      <c t="s" r="A106" s="6">
-        <v>13</v>
-      </c>
-      <c r="B106" s="7">
-        <v>384</v>
-      </c>
-      <c t="s" r="C106" s="7">
-        <v>14</v>
-      </c>
+      <c r="A106" s="6"/>
+      <c r="B106" s="7"/>
+      <c r="C106" s="7"/>
       <c r="D106" s="7"/>
-      <c t="s" r="E106" s="7">
-        <v>183</v>
-      </c>
-      <c r="F106" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G106" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="H106" s="8">
-        <v>110</v>
-      </c>
-      <c t="s" r="I106" s="7">
-        <v>186</v>
-      </c>
-      <c t="s" r="J106" s="7">
-        <v>187</v>
-      </c>
+      <c r="E106" s="7"/>
+      <c r="F106" s="7"/>
+      <c r="G106" s="8"/>
+      <c r="H106" s="8"/>
+      <c r="I106" s="7"/>
+      <c r="J106" s="7"/>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
       <c r="M106" s="7"/>
@@ -4778,7 +4778,7 @@
         <v>13</v>
       </c>
       <c r="B107" s="7">
-        <v>385</v>
+        <v>863</v>
       </c>
       <c t="s" r="C107" s="7">
         <v>14</v>
@@ -4791,16 +4791,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G107" s="8">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c t="s" r="H107" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>57</v>
+        <v>185</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -4811,7 +4811,7 @@
         <v>13</v>
       </c>
       <c r="B108" s="7">
-        <v>644</v>
+        <v>384</v>
       </c>
       <c t="s" r="C108" s="7">
         <v>14</v>
@@ -4827,33 +4827,47 @@
         <v>26</v>
       </c>
       <c t="s" r="H108" s="8">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c t="s" r="I108" s="7">
+        <v>186</v>
+      </c>
+      <c t="s" r="J108" s="7">
+        <v>187</v>
+      </c>
+      <c r="K108" s="7"/>
+      <c r="L108" s="7"/>
+      <c r="M108" s="7"/>
+    </row>
+    <row r="109" ht="14.25" customHeight="1">
+      <c t="s" r="A109" s="6">
+        <v>13</v>
+      </c>
+      <c r="B109" s="7">
+        <v>385</v>
+      </c>
+      <c t="s" r="C109" s="7">
+        <v>14</v>
+      </c>
+      <c r="D109" s="7"/>
+      <c t="s" r="E109" s="7">
+        <v>183</v>
+      </c>
+      <c r="F109" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G109" s="8">
+        <v>110</v>
+      </c>
+      <c t="s" r="H109" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="I109" s="7">
+        <v>188</v>
+      </c>
+      <c t="s" r="J109" s="7">
         <v>57</v>
       </c>
-      <c t="s" r="J108" s="7">
-        <v>180</v>
-      </c>
-      <c t="s" r="K108" s="7">
-        <v>189</v>
-      </c>
-      <c r="L108" s="7"/>
-      <c t="s" r="M108" s="7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="109" ht="14.25" customHeight="1">
-      <c r="A109" s="6"/>
-      <c r="B109" s="7"/>
-      <c r="C109" s="7"/>
-      <c r="D109" s="7"/>
-      <c r="E109" s="7"/>
-      <c r="F109" s="7"/>
-      <c r="G109" s="8"/>
-      <c r="H109" s="8"/>
-      <c r="I109" s="7"/>
-      <c r="J109" s="7"/>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
       <c r="M109" s="7"/>
@@ -4863,14 +4877,14 @@
         <v>13</v>
       </c>
       <c r="B110" s="7">
-        <v>630</v>
+        <v>644</v>
       </c>
       <c t="s" r="C110" s="7">
         <v>14</v>
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -4882,44 +4896,30 @@
         <v>135</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>191</v>
-      </c>
-      <c r="K110" s="7"/>
+        <v>180</v>
+      </c>
+      <c t="s" r="K110" s="7">
+        <v>189</v>
+      </c>
       <c r="L110" s="7"/>
-      <c r="M110" s="7"/>
+      <c t="s" r="M110" s="7">
+        <v>100</v>
+      </c>
     </row>
     <row r="111" ht="14.25" customHeight="1">
-      <c t="s" r="A111" s="6">
-        <v>13</v>
-      </c>
-      <c r="B111" s="7">
-        <v>629</v>
-      </c>
-      <c t="s" r="C111" s="7">
-        <v>14</v>
-      </c>
+      <c r="A111" s="6"/>
+      <c r="B111" s="7"/>
+      <c r="C111" s="7"/>
       <c r="D111" s="7"/>
-      <c t="s" r="E111" s="7">
-        <v>190</v>
-      </c>
-      <c r="F111" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G111" s="8">
-        <v>135</v>
-      </c>
-      <c t="s" r="H111" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="I111" s="7">
-        <v>96</v>
-      </c>
-      <c t="s" r="J111" s="7">
-        <v>137</v>
-      </c>
+      <c r="E111" s="7"/>
+      <c r="F111" s="7"/>
+      <c r="G111" s="8"/>
+      <c r="H111" s="8"/>
+      <c r="I111" s="7"/>
+      <c r="J111" s="7"/>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
       <c r="M111" s="7"/>
@@ -4929,7 +4929,7 @@
         <v>13</v>
       </c>
       <c r="B112" s="7">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c t="s" r="C112" s="7">
         <v>14</v>
@@ -4948,10 +4948,10 @@
         <v>135</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -4962,7 +4962,7 @@
         <v>13</v>
       </c>
       <c r="B113" s="7">
-        <v>715</v>
+        <v>629</v>
       </c>
       <c t="s" r="C113" s="7">
         <v>14</v>
@@ -4978,28 +4978,24 @@
         <v>135</v>
       </c>
       <c t="s" r="H113" s="8">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>193</v>
+        <v>96</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>194</v>
-      </c>
-      <c t="s" r="K113" s="7">
-        <v>195</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="K113" s="7"/>
       <c r="L113" s="7"/>
-      <c t="s" r="M113" s="7">
-        <v>196</v>
-      </c>
+      <c r="M113" s="7"/>
     </row>
     <row r="114" ht="14.25" customHeight="1">
       <c t="s" r="A114" s="6">
         <v>13</v>
       </c>
       <c r="B114" s="7">
-        <v>714</v>
+        <v>636</v>
       </c>
       <c t="s" r="C114" s="7">
         <v>14</v>
@@ -5012,31 +5008,27 @@
         <v>321</v>
       </c>
       <c t="s" r="G114" s="8">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c t="s" r="H114" s="8">
         <v>135</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>188</v>
-      </c>
-      <c t="s" r="K114" s="7">
-        <v>197</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="K114" s="7"/>
       <c r="L114" s="7"/>
-      <c t="s" r="M114" s="7">
-        <v>198</v>
-      </c>
+      <c r="M114" s="7"/>
     </row>
     <row r="115" ht="15" customHeight="1">
       <c t="s" r="A115" s="6">
         <v>13</v>
       </c>
       <c r="B115" s="7">
-        <v>631</v>
+        <v>715</v>
       </c>
       <c t="s" r="C115" s="7">
         <v>14</v>
@@ -5052,95 +5044,103 @@
         <v>135</v>
       </c>
       <c t="s" r="H115" s="8">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>199</v>
-      </c>
-      <c r="K115" s="7"/>
+        <v>194</v>
+      </c>
+      <c t="s" r="K115" s="7">
+        <v>195</v>
+      </c>
       <c r="L115" s="7"/>
-      <c r="M115" s="7"/>
+      <c t="s" r="M115" s="7">
+        <v>196</v>
+      </c>
     </row>
     <row r="116" ht="14.25" customHeight="1">
-      <c r="A116" s="6"/>
-      <c r="B116" s="7"/>
-      <c r="C116" s="7"/>
+      <c t="s" r="A116" s="6">
+        <v>13</v>
+      </c>
+      <c r="B116" s="7">
+        <v>714</v>
+      </c>
+      <c t="s" r="C116" s="7">
+        <v>14</v>
+      </c>
       <c r="D116" s="7"/>
-      <c r="E116" s="7"/>
-      <c r="F116" s="7"/>
-      <c r="G116" s="8"/>
-      <c r="H116" s="8"/>
-      <c r="I116" s="7"/>
-      <c r="J116" s="7"/>
-      <c r="K116" s="7"/>
+      <c t="s" r="E116" s="7">
+        <v>190</v>
+      </c>
+      <c r="F116" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G116" s="8">
+        <v>45</v>
+      </c>
+      <c t="s" r="H116" s="8">
+        <v>135</v>
+      </c>
+      <c t="s" r="I116" s="7">
+        <v>20</v>
+      </c>
+      <c t="s" r="J116" s="7">
+        <v>188</v>
+      </c>
+      <c t="s" r="K116" s="7">
+        <v>197</v>
+      </c>
       <c r="L116" s="7"/>
-      <c r="M116" s="7"/>
+      <c t="s" r="M116" s="7">
+        <v>198</v>
+      </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
       <c t="s" r="A117" s="6">
         <v>13</v>
       </c>
       <c r="B117" s="7">
-        <v>505</v>
+        <v>631</v>
       </c>
       <c t="s" r="C117" s="7">
         <v>14</v>
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G117" s="8">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c t="s" r="H117" s="8">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>201</v>
+        <v>182</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
       <c r="M117" s="7"/>
     </row>
     <row r="118" ht="14.25" customHeight="1">
-      <c t="s" r="A118" s="6">
-        <v>13</v>
-      </c>
-      <c r="B118" s="7">
-        <v>506</v>
-      </c>
-      <c t="s" r="C118" s="7">
-        <v>14</v>
-      </c>
+      <c r="A118" s="6"/>
+      <c r="B118" s="7"/>
+      <c r="C118" s="7"/>
       <c r="D118" s="7"/>
-      <c t="s" r="E118" s="7">
-        <v>200</v>
-      </c>
-      <c r="F118" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G118" s="8">
-        <v>135</v>
-      </c>
-      <c t="s" r="H118" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I118" s="7">
-        <v>136</v>
-      </c>
-      <c t="s" r="J118" s="7">
-        <v>137</v>
-      </c>
+      <c r="E118" s="7"/>
+      <c r="F118" s="7"/>
+      <c r="G118" s="8"/>
+      <c r="H118" s="8"/>
+      <c r="I118" s="7"/>
+      <c r="J118" s="7"/>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
       <c r="M118" s="7"/>
@@ -5150,7 +5150,7 @@
         <v>13</v>
       </c>
       <c r="B119" s="7">
-        <v>453</v>
+        <v>505</v>
       </c>
       <c t="s" r="C119" s="7">
         <v>14</v>
@@ -5166,13 +5166,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H119" s="8">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>40</v>
+        <v>201</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5183,7 +5183,7 @@
         <v>13</v>
       </c>
       <c r="B120" s="7">
-        <v>456</v>
+        <v>506</v>
       </c>
       <c t="s" r="C120" s="7">
         <v>14</v>
@@ -5196,16 +5196,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G120" s="8">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c t="s" r="H120" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>187</v>
+        <v>137</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5216,7 +5216,7 @@
         <v>13</v>
       </c>
       <c r="B121" s="7">
-        <v>521</v>
+        <v>453</v>
       </c>
       <c t="s" r="C121" s="7">
         <v>14</v>
@@ -5232,13 +5232,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H121" s="8">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>204</v>
+        <v>40</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5249,7 +5249,7 @@
         <v>13</v>
       </c>
       <c r="B122" s="7">
-        <v>518</v>
+        <v>456</v>
       </c>
       <c t="s" r="C122" s="7">
         <v>14</v>
@@ -5262,32 +5262,50 @@
         <v>321</v>
       </c>
       <c t="s" r="G122" s="8">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c t="s" r="H122" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>205</v>
+        <v>178</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>126</v>
+        <v>187</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
       <c r="M122" s="7"/>
     </row>
     <row r="123" ht="14.25" customHeight="1">
-      <c r="A123" s="6"/>
-      <c r="B123" s="7"/>
-      <c r="C123" s="7"/>
+      <c t="s" r="A123" s="6">
+        <v>13</v>
+      </c>
+      <c r="B123" s="7">
+        <v>521</v>
+      </c>
+      <c t="s" r="C123" s="7">
+        <v>14</v>
+      </c>
       <c r="D123" s="7"/>
-      <c r="E123" s="7"/>
-      <c r="F123" s="7"/>
-      <c r="G123" s="8"/>
-      <c r="H123" s="8"/>
-      <c r="I123" s="7"/>
-      <c r="J123" s="7"/>
+      <c t="s" r="E123" s="7">
+        <v>200</v>
+      </c>
+      <c r="F123" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G123" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H123" s="8">
+        <v>135</v>
+      </c>
+      <c t="s" r="I123" s="7">
+        <v>204</v>
+      </c>
+      <c t="s" r="J123" s="7">
+        <v>21</v>
+      </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
       <c r="M123" s="7"/>
@@ -5297,65 +5315,45 @@
         <v>13</v>
       </c>
       <c r="B124" s="7">
-        <v>979</v>
+        <v>518</v>
       </c>
       <c t="s" r="C124" s="7">
         <v>14</v>
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G124" s="8">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c t="s" r="H124" s="8">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>151</v>
+        <v>126</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
-      <c t="s" r="M124" s="7">
-        <v>208</v>
-      </c>
+      <c r="M124" s="7"/>
     </row>
     <row r="125" ht="15" customHeight="1">
-      <c t="s" r="A125" s="6">
-        <v>13</v>
-      </c>
-      <c r="B125" s="7">
-        <v>336</v>
-      </c>
-      <c t="s" r="C125" s="7">
-        <v>14</v>
-      </c>
+      <c r="A125" s="6"/>
+      <c r="B125" s="7"/>
+      <c r="C125" s="7"/>
       <c r="D125" s="7"/>
-      <c t="s" r="E125" s="7">
-        <v>206</v>
-      </c>
-      <c r="F125" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G125" s="8">
-        <v>45</v>
-      </c>
-      <c t="s" r="H125" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="I125" s="7">
-        <v>37</v>
-      </c>
-      <c t="s" r="J125" s="7">
-        <v>112</v>
-      </c>
+      <c r="E125" s="7"/>
+      <c r="F125" s="7"/>
+      <c r="G125" s="8"/>
+      <c r="H125" s="8"/>
+      <c r="I125" s="7"/>
+      <c r="J125" s="7"/>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
       <c r="M125" s="7"/>
@@ -5365,7 +5363,7 @@
         <v>13</v>
       </c>
       <c r="B126" s="7">
-        <v>306</v>
+        <v>979</v>
       </c>
       <c t="s" r="C126" s="7">
         <v>14</v>
@@ -5378,27 +5376,29 @@
         <v>321</v>
       </c>
       <c t="s" r="G126" s="8">
-        <v>26</v>
+        <v>121</v>
       </c>
       <c t="s" r="H126" s="8">
-        <v>209</v>
+        <v>45</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>154</v>
+        <v>207</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>97</v>
+        <v>153</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
-      <c r="M126" s="7"/>
+      <c t="s" r="M126" s="7">
+        <v>208</v>
+      </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
       <c t="s" r="A127" s="6">
         <v>13</v>
       </c>
       <c r="B127" s="7">
-        <v>305</v>
+        <v>336</v>
       </c>
       <c t="s" r="C127" s="7">
         <v>14</v>
@@ -5411,16 +5411,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G127" s="8">
-        <v>209</v>
+        <v>45</v>
       </c>
       <c t="s" r="H127" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>210</v>
+        <v>37</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>211</v>
+        <v>112</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -5431,7 +5431,7 @@
         <v>13</v>
       </c>
       <c r="B128" s="7">
-        <v>325</v>
+        <v>306</v>
       </c>
       <c t="s" r="C128" s="7">
         <v>14</v>
@@ -5447,13 +5447,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H128" s="8">
-        <v>45</v>
+        <v>209</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>212</v>
+        <v>156</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>213</v>
+        <v>97</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5464,7 +5464,7 @@
         <v>13</v>
       </c>
       <c r="B129" s="7">
-        <v>978</v>
+        <v>305</v>
       </c>
       <c t="s" r="C129" s="7">
         <v>14</v>
@@ -5477,32 +5477,50 @@
         <v>321</v>
       </c>
       <c t="s" r="G129" s="8">
-        <v>45</v>
+        <v>209</v>
       </c>
       <c t="s" r="H129" s="8">
-        <v>121</v>
+        <v>26</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>214</v>
+        <v>147</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
       <c r="M129" s="7"/>
     </row>
     <row r="130" ht="15" customHeight="1">
-      <c r="A130" s="6"/>
-      <c r="B130" s="7"/>
-      <c r="C130" s="7"/>
+      <c t="s" r="A130" s="6">
+        <v>13</v>
+      </c>
+      <c r="B130" s="7">
+        <v>325</v>
+      </c>
+      <c t="s" r="C130" s="7">
+        <v>14</v>
+      </c>
       <c r="D130" s="7"/>
-      <c r="E130" s="7"/>
-      <c r="F130" s="7"/>
-      <c r="G130" s="8"/>
-      <c r="H130" s="8"/>
-      <c r="I130" s="7"/>
-      <c r="J130" s="7"/>
+      <c t="s" r="E130" s="7">
+        <v>206</v>
+      </c>
+      <c r="F130" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G130" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H130" s="8">
+        <v>45</v>
+      </c>
+      <c t="s" r="I130" s="7">
+        <v>211</v>
+      </c>
+      <c t="s" r="J130" s="7">
+        <v>212</v>
+      </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
       <c r="M130" s="7"/>
@@ -5512,63 +5530,45 @@
         <v>13</v>
       </c>
       <c r="B131" s="7">
-        <v>270</v>
+        <v>978</v>
       </c>
       <c t="s" r="C131" s="7">
         <v>14</v>
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G131" s="8">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c t="s" r="H131" s="8">
-        <v>216</v>
+        <v>121</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>108</v>
+        <v>187</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>29</v>
+        <v>213</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
       <c r="M131" s="7"/>
     </row>
     <row r="132" ht="14.25" customHeight="1">
-      <c t="s" r="A132" s="6">
-        <v>13</v>
-      </c>
-      <c r="B132" s="7">
-        <v>271</v>
-      </c>
-      <c t="s" r="C132" s="7">
-        <v>14</v>
-      </c>
+      <c r="A132" s="6"/>
+      <c r="B132" s="7"/>
+      <c r="C132" s="7"/>
       <c r="D132" s="7"/>
-      <c t="s" r="E132" s="7">
-        <v>215</v>
-      </c>
-      <c r="F132" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G132" s="8">
-        <v>216</v>
-      </c>
-      <c t="s" r="H132" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="I132" s="7">
-        <v>24</v>
-      </c>
-      <c t="s" r="J132" s="7">
-        <v>217</v>
-      </c>
+      <c r="E132" s="7"/>
+      <c r="F132" s="7"/>
+      <c r="G132" s="8"/>
+      <c r="H132" s="8"/>
+      <c r="I132" s="7"/>
+      <c r="J132" s="7"/>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
       <c r="M132" s="7"/>
@@ -5578,29 +5578,29 @@
         <v>13</v>
       </c>
       <c r="B133" s="7">
-        <v>244</v>
+        <v>270</v>
       </c>
       <c t="s" r="C133" s="7">
         <v>14</v>
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
+        <v>214</v>
+      </c>
+      <c r="F133" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G133" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H133" s="8">
         <v>215</v>
       </c>
-      <c r="F133" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G133" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="H133" s="8">
-        <v>89</v>
-      </c>
       <c t="s" r="I133" s="7">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>155</v>
+        <v>29</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5611,29 +5611,29 @@
         <v>13</v>
       </c>
       <c r="B134" s="7">
-        <v>245</v>
+        <v>271</v>
       </c>
       <c t="s" r="C134" s="7">
         <v>14</v>
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
+        <v>214</v>
+      </c>
+      <c r="F134" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G134" s="8">
         <v>215</v>
       </c>
-      <c r="F134" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G134" s="8">
-        <v>89</v>
-      </c>
       <c t="s" r="H134" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>218</v>
+        <v>24</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5644,14 +5644,14 @@
         <v>13</v>
       </c>
       <c r="B135" s="7">
-        <v>280</v>
+        <v>244</v>
       </c>
       <c t="s" r="C135" s="7">
         <v>14</v>
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5660,13 +5660,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H135" s="8">
-        <v>216</v>
+        <v>89</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>194</v>
+        <v>82</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>220</v>
+        <v>157</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5677,45 +5677,63 @@
         <v>13</v>
       </c>
       <c r="B136" s="7">
-        <v>281</v>
+        <v>245</v>
       </c>
       <c t="s" r="C136" s="7">
         <v>14</v>
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G136" s="8">
-        <v>216</v>
+        <v>89</v>
       </c>
       <c t="s" r="H136" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
       <c r="M136" s="7"/>
     </row>
     <row r="137" ht="14.25" customHeight="1">
-      <c r="A137" s="6"/>
-      <c r="B137" s="7"/>
-      <c r="C137" s="7"/>
+      <c t="s" r="A137" s="6">
+        <v>13</v>
+      </c>
+      <c r="B137" s="7">
+        <v>280</v>
+      </c>
+      <c t="s" r="C137" s="7">
+        <v>14</v>
+      </c>
       <c r="D137" s="7"/>
-      <c r="E137" s="7"/>
-      <c r="F137" s="7"/>
-      <c r="G137" s="8"/>
-      <c r="H137" s="8"/>
-      <c r="I137" s="7"/>
-      <c r="J137" s="7"/>
+      <c t="s" r="E137" s="7">
+        <v>214</v>
+      </c>
+      <c r="F137" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G137" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H137" s="8">
+        <v>215</v>
+      </c>
+      <c t="s" r="I137" s="7">
+        <v>194</v>
+      </c>
+      <c t="s" r="J137" s="7">
+        <v>219</v>
+      </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
       <c r="M137" s="7"/>
@@ -5725,63 +5743,45 @@
         <v>13</v>
       </c>
       <c r="B138" s="7">
-        <v>461</v>
+        <v>281</v>
       </c>
       <c t="s" r="C138" s="7">
         <v>14</v>
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G138" s="8">
-        <v>16</v>
+        <v>215</v>
       </c>
       <c t="s" r="H138" s="8">
-        <v>138</v>
+        <v>26</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
       <c r="M138" s="7"/>
     </row>
     <row r="139" ht="14.25" customHeight="1">
-      <c t="s" r="A139" s="6">
-        <v>13</v>
-      </c>
-      <c r="B139" s="7">
-        <v>462</v>
-      </c>
-      <c t="s" r="C139" s="7">
-        <v>14</v>
-      </c>
+      <c r="A139" s="6"/>
+      <c r="B139" s="7"/>
+      <c r="C139" s="7"/>
       <c r="D139" s="7"/>
-      <c t="s" r="E139" s="7">
-        <v>223</v>
-      </c>
-      <c r="F139" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G139" s="8">
-        <v>138</v>
-      </c>
-      <c t="s" r="H139" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I139" s="7">
-        <v>39</v>
-      </c>
-      <c t="s" r="J139" s="7">
-        <v>184</v>
-      </c>
+      <c r="E139" s="7"/>
+      <c r="F139" s="7"/>
+      <c r="G139" s="8"/>
+      <c r="H139" s="8"/>
+      <c r="I139" s="7"/>
+      <c r="J139" s="7"/>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
       <c r="M139" s="7"/>
@@ -5791,14 +5791,14 @@
         <v>13</v>
       </c>
       <c r="B140" s="7">
-        <v>515</v>
+        <v>461</v>
       </c>
       <c t="s" r="C140" s="7">
         <v>14</v>
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5807,13 +5807,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H140" s="8">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>103</v>
+        <v>224</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -5824,29 +5824,29 @@
         <v>13</v>
       </c>
       <c r="B141" s="7">
-        <v>508</v>
+        <v>462</v>
       </c>
       <c t="s" r="C141" s="7">
         <v>14</v>
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="H141" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>227</v>
+        <v>184</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5857,14 +5857,14 @@
         <v>13</v>
       </c>
       <c r="B142" s="7">
-        <v>773</v>
+        <v>515</v>
       </c>
       <c t="s" r="C142" s="7">
         <v>14</v>
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5873,13 +5873,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H142" s="8">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -5890,29 +5890,29 @@
         <v>13</v>
       </c>
       <c r="B143" s="7">
-        <v>7614</v>
+        <v>508</v>
       </c>
       <c t="s" r="C143" s="7">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G143" s="8">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c t="s" r="H143" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>198</v>
+        <v>41</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>160</v>
+        <v>226</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -5923,14 +5923,14 @@
         <v>13</v>
       </c>
       <c r="B144" s="7">
-        <v>7614</v>
+        <v>773</v>
       </c>
       <c t="s" r="C144" s="7">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -5939,29 +5939,47 @@
         <v>16</v>
       </c>
       <c t="s" r="H144" s="8">
-        <v>229</v>
+        <v>81</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>231</v>
+        <v>66</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
       <c r="M144" s="7"/>
     </row>
     <row r="145" ht="15" customHeight="1">
-      <c r="A145" s="6"/>
-      <c r="B145" s="7"/>
-      <c r="C145" s="7"/>
+      <c t="s" r="A145" s="6">
+        <v>13</v>
+      </c>
+      <c r="B145" s="7">
+        <v>7614</v>
+      </c>
+      <c t="s" r="C145" s="7">
+        <v>79</v>
+      </c>
       <c r="D145" s="7"/>
-      <c r="E145" s="7"/>
-      <c r="F145" s="7"/>
-      <c r="G145" s="8"/>
-      <c r="H145" s="8"/>
-      <c r="I145" s="7"/>
-      <c r="J145" s="7"/>
+      <c t="s" r="E145" s="7">
+        <v>222</v>
+      </c>
+      <c r="F145" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G145" s="8">
+        <v>81</v>
+      </c>
+      <c t="s" r="H145" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I145" s="7">
+        <v>198</v>
+      </c>
+      <c t="s" r="J145" s="7">
+        <v>160</v>
+      </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
       <c r="M145" s="7"/>
@@ -5971,63 +5989,45 @@
         <v>13</v>
       </c>
       <c r="B146" s="7">
-        <v>7705</v>
+        <v>7614</v>
       </c>
       <c t="s" r="C146" s="7">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G146" s="8">
-        <v>233</v>
+        <v>16</v>
       </c>
       <c t="s" r="H146" s="8">
-        <v>16</v>
+        <v>228</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c r="M146" s="7"/>
     </row>
     <row r="147" ht="14.25" customHeight="1">
-      <c t="s" r="A147" s="6">
-        <v>13</v>
-      </c>
-      <c r="B147" s="7">
-        <v>7705</v>
-      </c>
-      <c t="s" r="C147" s="7">
-        <v>14</v>
-      </c>
+      <c r="A147" s="6"/>
+      <c r="B147" s="7"/>
+      <c r="C147" s="7"/>
       <c r="D147" s="7"/>
-      <c t="s" r="E147" s="7">
-        <v>232</v>
-      </c>
-      <c r="F147" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G147" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H147" s="8">
-        <v>81</v>
-      </c>
-      <c t="s" r="I147" s="7">
-        <v>236</v>
-      </c>
-      <c t="s" r="J147" s="7">
-        <v>76</v>
-      </c>
+      <c r="E147" s="7"/>
+      <c r="F147" s="7"/>
+      <c r="G147" s="8"/>
+      <c r="H147" s="8"/>
+      <c r="I147" s="7"/>
+      <c r="J147" s="7"/>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
       <c r="M147" s="7"/>
@@ -6037,49 +6037,63 @@
         <v>13</v>
       </c>
       <c r="B148" s="7">
-        <v>776</v>
+        <v>7705</v>
       </c>
       <c t="s" r="C148" s="7">
         <v>14</v>
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
+        <v>231</v>
+      </c>
+      <c r="F148" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G148" s="8">
         <v>232</v>
-      </c>
-      <c r="F148" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G148" s="8">
-        <v>81</v>
       </c>
       <c t="s" r="H148" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>67</v>
+        <v>233</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>180</v>
-      </c>
-      <c t="s" r="K148" s="7">
-        <v>222</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="K148" s="7"/>
       <c r="L148" s="7"/>
-      <c t="s" r="M148" s="7">
-        <v>237</v>
-      </c>
+      <c r="M148" s="7"/>
     </row>
     <row r="149" ht="14.25" customHeight="1">
-      <c r="A149" s="6"/>
-      <c r="B149" s="7"/>
-      <c r="C149" s="7"/>
+      <c t="s" r="A149" s="6">
+        <v>13</v>
+      </c>
+      <c r="B149" s="7">
+        <v>7705</v>
+      </c>
+      <c t="s" r="C149" s="7">
+        <v>14</v>
+      </c>
       <c r="D149" s="7"/>
-      <c r="E149" s="7"/>
-      <c r="F149" s="7"/>
-      <c r="G149" s="8"/>
-      <c r="H149" s="8"/>
-      <c r="I149" s="7"/>
-      <c r="J149" s="7"/>
+      <c t="s" r="E149" s="7">
+        <v>231</v>
+      </c>
+      <c r="F149" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G149" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H149" s="8">
+        <v>81</v>
+      </c>
+      <c t="s" r="I149" s="7">
+        <v>234</v>
+      </c>
+      <c t="s" r="J149" s="7">
+        <v>76</v>
+      </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
       <c r="M149" s="7"/>
@@ -6089,63 +6103,49 @@
         <v>13</v>
       </c>
       <c r="B150" s="7">
-        <v>501</v>
+        <v>776</v>
       </c>
       <c t="s" r="C150" s="7">
         <v>14</v>
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G150" s="8">
+        <v>81</v>
+      </c>
+      <c t="s" r="H150" s="8">
         <v>16</v>
       </c>
-      <c t="s" r="H150" s="8">
-        <v>135</v>
-      </c>
       <c t="s" r="I150" s="7">
-        <v>239</v>
+        <v>67</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>240</v>
-      </c>
-      <c r="K150" s="7"/>
+        <v>180</v>
+      </c>
+      <c t="s" r="K150" s="7">
+        <v>221</v>
+      </c>
       <c r="L150" s="7"/>
-      <c r="M150" s="7"/>
+      <c t="s" r="M150" s="7">
+        <v>235</v>
+      </c>
     </row>
     <row r="151" ht="14.25" customHeight="1">
-      <c t="s" r="A151" s="6">
-        <v>13</v>
-      </c>
-      <c r="B151" s="7">
-        <v>514</v>
-      </c>
-      <c t="s" r="C151" s="7">
-        <v>14</v>
-      </c>
+      <c r="A151" s="6"/>
+      <c r="B151" s="7"/>
+      <c r="C151" s="7"/>
       <c r="D151" s="7"/>
-      <c t="s" r="E151" s="7">
-        <v>238</v>
-      </c>
-      <c r="F151" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G151" s="8">
-        <v>135</v>
-      </c>
-      <c t="s" r="H151" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I151" s="7">
-        <v>29</v>
-      </c>
-      <c t="s" r="J151" s="7">
-        <v>91</v>
-      </c>
+      <c r="E151" s="7"/>
+      <c r="F151" s="7"/>
+      <c r="G151" s="8"/>
+      <c r="H151" s="8"/>
+      <c r="I151" s="7"/>
+      <c r="J151" s="7"/>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
       <c r="M151" s="7"/>
@@ -6155,14 +6155,14 @@
         <v>13</v>
       </c>
       <c r="B152" s="7">
-        <v>563</v>
+        <v>501</v>
       </c>
       <c t="s" r="C152" s="7">
         <v>14</v>
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6171,13 +6171,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H152" s="8">
-        <v>209</v>
+        <v>135</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>92</v>
+        <v>237</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6188,29 +6188,29 @@
         <v>13</v>
       </c>
       <c r="B153" s="7">
-        <v>564</v>
+        <v>514</v>
       </c>
       <c t="s" r="C153" s="7">
         <v>14</v>
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G153" s="8">
-        <v>209</v>
+        <v>135</v>
       </c>
       <c t="s" r="H153" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>242</v>
+        <v>29</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6221,14 +6221,14 @@
         <v>13</v>
       </c>
       <c r="B154" s="7">
-        <v>451</v>
+        <v>563</v>
       </c>
       <c t="s" r="C154" s="7">
         <v>14</v>
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6237,13 +6237,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H154" s="8">
-        <v>45</v>
+        <v>209</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>146</v>
+        <v>92</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>156</v>
+        <v>239</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6254,29 +6254,29 @@
         <v>13</v>
       </c>
       <c r="B155" s="7">
-        <v>454</v>
+        <v>564</v>
       </c>
       <c t="s" r="C155" s="7">
         <v>14</v>
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G155" s="8">
-        <v>45</v>
+        <v>209</v>
       </c>
       <c t="s" r="H155" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>220</v>
+        <v>102</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6287,14 +6287,14 @@
         <v>13</v>
       </c>
       <c r="B156" s="7">
-        <v>1157</v>
+        <v>451</v>
       </c>
       <c t="s" r="C156" s="7">
         <v>14</v>
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6303,13 +6303,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H156" s="8">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>68</v>
+        <v>158</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6320,45 +6320,63 @@
         <v>13</v>
       </c>
       <c r="B157" s="7">
-        <v>1156</v>
+        <v>454</v>
       </c>
       <c t="s" r="C157" s="7">
         <v>14</v>
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G157" s="8">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c t="s" r="H157" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>124</v>
+        <v>242</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>245</v>
+        <v>219</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
       <c r="M157" s="7"/>
     </row>
     <row r="158" ht="14.25" customHeight="1">
-      <c r="A158" s="6"/>
-      <c r="B158" s="7"/>
-      <c r="C158" s="7"/>
+      <c t="s" r="A158" s="6">
+        <v>13</v>
+      </c>
+      <c r="B158" s="7">
+        <v>1157</v>
+      </c>
+      <c t="s" r="C158" s="7">
+        <v>14</v>
+      </c>
       <c r="D158" s="7"/>
-      <c r="E158" s="7"/>
-      <c r="F158" s="7"/>
-      <c r="G158" s="8"/>
-      <c r="H158" s="8"/>
-      <c r="I158" s="7"/>
-      <c r="J158" s="7"/>
+      <c t="s" r="E158" s="7">
+        <v>236</v>
+      </c>
+      <c r="F158" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G158" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H158" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="I158" s="7">
+        <v>243</v>
+      </c>
+      <c t="s" r="J158" s="7">
+        <v>68</v>
+      </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
       <c r="M158" s="7"/>
@@ -6368,63 +6386,45 @@
         <v>13</v>
       </c>
       <c r="B159" s="7">
-        <v>3524</v>
+        <v>1156</v>
       </c>
       <c t="s" r="C159" s="7">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
-        <v>247</v>
+        <v>26</v>
       </c>
       <c t="s" r="H159" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>177</v>
+        <v>124</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
       <c r="M159" s="7"/>
     </row>
     <row r="160" ht="15" customHeight="1">
-      <c t="s" r="A160" s="6">
-        <v>13</v>
-      </c>
-      <c r="B160" s="7">
-        <v>3524</v>
-      </c>
-      <c t="s" r="C160" s="7">
-        <v>79</v>
-      </c>
+      <c r="A160" s="6"/>
+      <c r="B160" s="7"/>
+      <c r="C160" s="7"/>
       <c r="D160" s="7"/>
-      <c t="s" r="E160" s="7">
-        <v>246</v>
-      </c>
-      <c r="F160" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G160" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H160" s="8">
-        <v>45</v>
-      </c>
-      <c t="s" r="I160" s="7">
-        <v>249</v>
-      </c>
-      <c t="s" r="J160" s="7">
-        <v>42</v>
-      </c>
+      <c r="E160" s="7"/>
+      <c r="F160" s="7"/>
+      <c r="G160" s="8"/>
+      <c r="H160" s="8"/>
+      <c r="I160" s="7"/>
+      <c r="J160" s="7"/>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
       <c r="M160" s="7"/>
@@ -6434,45 +6434,63 @@
         <v>13</v>
       </c>
       <c r="B161" s="7">
-        <v>1322</v>
+        <v>3524</v>
       </c>
       <c t="s" r="C161" s="7">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
+        <v>245</v>
+      </c>
+      <c r="F161" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G161" s="8">
         <v>246</v>
       </c>
-      <c r="F161" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G161" s="8">
-        <v>45</v>
-      </c>
       <c t="s" r="H161" s="8">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>67</v>
+        <v>247</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
       <c r="M161" s="7"/>
     </row>
     <row r="162" ht="14.25" customHeight="1">
-      <c r="A162" s="6"/>
-      <c r="B162" s="7"/>
-      <c r="C162" s="7"/>
+      <c t="s" r="A162" s="6">
+        <v>13</v>
+      </c>
+      <c r="B162" s="7">
+        <v>3524</v>
+      </c>
+      <c t="s" r="C162" s="7">
+        <v>79</v>
+      </c>
       <c r="D162" s="7"/>
-      <c r="E162" s="7"/>
-      <c r="F162" s="7"/>
-      <c r="G162" s="8"/>
-      <c r="H162" s="8"/>
-      <c r="I162" s="7"/>
-      <c r="J162" s="7"/>
+      <c t="s" r="E162" s="7">
+        <v>245</v>
+      </c>
+      <c r="F162" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G162" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H162" s="8">
+        <v>45</v>
+      </c>
+      <c t="s" r="I162" s="7">
+        <v>248</v>
+      </c>
+      <c t="s" r="J162" s="7">
+        <v>42</v>
+      </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
       <c r="M162" s="7"/>
@@ -6482,185 +6500,167 @@
         <v>13</v>
       </c>
       <c r="B163" s="7">
-        <v>92</v>
+        <v>1322</v>
       </c>
       <c t="s" r="C163" s="7">
         <v>14</v>
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>251</v>
+        <v>45</v>
       </c>
       <c t="s" r="H163" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>241</v>
+        <v>187</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>179</v>
+        <v>67</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
       <c r="M163" s="7"/>
     </row>
     <row r="164" ht="14.25" customHeight="1">
-      <c t="s" r="A164" s="6">
-        <v>13</v>
-      </c>
-      <c r="B164" s="7">
-        <v>820</v>
-      </c>
-      <c t="s" r="C164" s="7">
-        <v>14</v>
-      </c>
+      <c r="A164" s="6"/>
+      <c r="B164" s="7"/>
+      <c r="C164" s="7"/>
       <c r="D164" s="7"/>
-      <c t="s" r="E164" s="7">
-        <v>250</v>
-      </c>
-      <c r="F164" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G164" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="H164" s="8">
-        <v>252</v>
-      </c>
-      <c t="s" r="I164" s="7">
-        <v>20</v>
-      </c>
-      <c t="s" r="J164" s="7">
-        <v>36</v>
-      </c>
-      <c t="s" r="K164" s="7">
-        <v>253</v>
-      </c>
+      <c r="E164" s="7"/>
+      <c r="F164" s="7"/>
+      <c r="G164" s="8"/>
+      <c r="H164" s="8"/>
+      <c r="I164" s="7"/>
+      <c r="J164" s="7"/>
+      <c r="K164" s="7"/>
       <c r="L164" s="7"/>
-      <c t="s" r="M164" s="7">
-        <v>78</v>
-      </c>
+      <c r="M164" s="7"/>
     </row>
     <row r="165" ht="15" customHeight="1">
       <c t="s" r="A165" s="6">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B165" s="7">
-        <v>821</v>
+        <v>92</v>
       </c>
       <c t="s" r="C165" s="7">
         <v>14</v>
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
+        <v>249</v>
+      </c>
+      <c r="F165" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G165" s="8">
         <v>250</v>
       </c>
-      <c r="F165" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G165" s="8">
+      <c t="s" r="H165" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="I165" s="7">
+        <v>239</v>
+      </c>
+      <c t="s" r="J165" s="7">
+        <v>179</v>
+      </c>
+      <c r="K165" s="7"/>
+      <c r="L165" s="7"/>
+      <c r="M165" s="7"/>
+    </row>
+    <row r="166" ht="14.25" customHeight="1">
+      <c t="s" r="A166" s="6">
+        <v>13</v>
+      </c>
+      <c r="B166" s="7">
+        <v>820</v>
+      </c>
+      <c t="s" r="C166" s="7">
+        <v>14</v>
+      </c>
+      <c r="D166" s="7"/>
+      <c t="s" r="E166" s="7">
+        <v>249</v>
+      </c>
+      <c r="F166" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G166" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H166" s="8">
+        <v>251</v>
+      </c>
+      <c t="s" r="I166" s="7">
+        <v>20</v>
+      </c>
+      <c t="s" r="J166" s="7">
+        <v>36</v>
+      </c>
+      <c t="s" r="K166" s="7">
         <v>252</v>
       </c>
-      <c t="s" r="H165" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="I165" s="7">
-        <v>254</v>
-      </c>
-      <c t="s" r="J165" s="7">
-        <v>255</v>
-      </c>
-      <c t="s" r="K165" s="7">
-        <v>256</v>
-      </c>
-      <c r="L165" s="7"/>
-      <c t="s" r="M165" s="7">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="166" ht="14.25" customHeight="1">
-      <c r="A166" s="6"/>
-      <c r="B166" s="7"/>
-      <c r="C166" s="7"/>
-      <c r="D166" s="7"/>
-      <c r="E166" s="7"/>
-      <c r="F166" s="7"/>
-      <c r="G166" s="8"/>
-      <c r="H166" s="8"/>
-      <c r="I166" s="7"/>
-      <c r="J166" s="7"/>
-      <c r="K166" s="7"/>
       <c r="L166" s="7"/>
-      <c r="M166" s="7"/>
+      <c t="s" r="M166" s="7">
+        <v>78</v>
+      </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
       <c t="s" r="A167" s="6">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B167" s="7">
-        <v>120</v>
+        <v>821</v>
       </c>
       <c t="s" r="C167" s="7">
         <v>14</v>
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G167" s="8">
-        <v>26</v>
+        <v>251</v>
       </c>
       <c t="s" r="H167" s="8">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>71</v>
-      </c>
-      <c r="K167" s="7"/>
+        <v>254</v>
+      </c>
+      <c t="s" r="K167" s="7">
+        <v>255</v>
+      </c>
       <c r="L167" s="7"/>
-      <c r="M167" s="7"/>
+      <c t="s" r="M167" s="7">
+        <v>90</v>
+      </c>
     </row>
     <row r="168" ht="14.25" customHeight="1">
-      <c t="s" r="A168" s="6">
-        <v>13</v>
-      </c>
-      <c r="B168" s="7">
-        <v>929</v>
-      </c>
-      <c t="s" r="C168" s="7">
-        <v>14</v>
-      </c>
+      <c r="A168" s="6"/>
+      <c r="B168" s="7"/>
+      <c r="C168" s="7"/>
       <c r="D168" s="7"/>
-      <c t="s" r="E168" s="7">
-        <v>257</v>
-      </c>
-      <c r="F168" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G168" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H168" s="8">
-        <v>163</v>
-      </c>
-      <c t="s" r="I168" s="7">
-        <v>133</v>
-      </c>
-      <c t="s" r="J168" s="7">
-        <v>120</v>
-      </c>
+      <c r="E168" s="7"/>
+      <c r="F168" s="7"/>
+      <c r="G168" s="8"/>
+      <c r="H168" s="8"/>
+      <c r="I168" s="7"/>
+      <c r="J168" s="7"/>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
       <c r="M168" s="7"/>
@@ -6670,29 +6670,29 @@
         <v>13</v>
       </c>
       <c r="B169" s="7">
-        <v>928</v>
+        <v>120</v>
       </c>
       <c t="s" r="C169" s="7">
         <v>14</v>
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G169" s="8">
-        <v>163</v>
+        <v>26</v>
       </c>
       <c t="s" r="H169" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>123</v>
+        <v>257</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>188</v>
+        <v>71</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -6703,14 +6703,14 @@
         <v>13</v>
       </c>
       <c r="B170" s="7">
-        <v>161</v>
+        <v>929</v>
       </c>
       <c t="s" r="C170" s="7">
         <v>14</v>
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6719,29 +6719,47 @@
         <v>16</v>
       </c>
       <c t="s" r="H170" s="8">
-        <v>26</v>
+        <v>163</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>259</v>
+        <v>133</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>260</v>
+        <v>120</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
       <c r="M170" s="7"/>
     </row>
     <row r="171" ht="14.25" customHeight="1">
-      <c r="A171" s="6"/>
-      <c r="B171" s="7"/>
-      <c r="C171" s="7"/>
+      <c t="s" r="A171" s="6">
+        <v>13</v>
+      </c>
+      <c r="B171" s="7">
+        <v>928</v>
+      </c>
+      <c t="s" r="C171" s="7">
+        <v>14</v>
+      </c>
       <c r="D171" s="7"/>
-      <c r="E171" s="7"/>
-      <c r="F171" s="7"/>
-      <c r="G171" s="8"/>
-      <c r="H171" s="8"/>
-      <c r="I171" s="7"/>
-      <c r="J171" s="7"/>
+      <c t="s" r="E171" s="7">
+        <v>256</v>
+      </c>
+      <c r="F171" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G171" s="8">
+        <v>163</v>
+      </c>
+      <c t="s" r="H171" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I171" s="7">
+        <v>123</v>
+      </c>
+      <c t="s" r="J171" s="7">
+        <v>188</v>
+      </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
       <c r="M171" s="7"/>
@@ -6751,63 +6769,45 @@
         <v>13</v>
       </c>
       <c r="B172" s="7">
-        <v>621</v>
+        <v>161</v>
       </c>
       <c t="s" r="C172" s="7">
         <v>14</v>
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G172" s="8">
-        <v>135</v>
+        <v>16</v>
       </c>
       <c t="s" r="H172" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>29</v>
+        <v>259</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
       <c r="M172" s="7"/>
     </row>
     <row r="173" ht="14.25" customHeight="1">
-      <c t="s" r="A173" s="6">
-        <v>13</v>
-      </c>
-      <c r="B173" s="7">
-        <v>632</v>
-      </c>
-      <c t="s" r="C173" s="7">
-        <v>14</v>
-      </c>
+      <c r="A173" s="6"/>
+      <c r="B173" s="7"/>
+      <c r="C173" s="7"/>
       <c r="D173" s="7"/>
-      <c t="s" r="E173" s="7">
-        <v>261</v>
-      </c>
-      <c r="F173" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G173" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="H173" s="8">
-        <v>135</v>
-      </c>
-      <c t="s" r="I173" s="7">
-        <v>24</v>
-      </c>
-      <c t="s" r="J173" s="7">
-        <v>92</v>
-      </c>
+      <c r="E173" s="7"/>
+      <c r="F173" s="7"/>
+      <c r="G173" s="8"/>
+      <c r="H173" s="8"/>
+      <c r="I173" s="7"/>
+      <c r="J173" s="7"/>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
       <c r="M173" s="7"/>
@@ -6817,14 +6817,14 @@
         <v>13</v>
       </c>
       <c r="B174" s="7">
-        <v>720</v>
+        <v>621</v>
       </c>
       <c t="s" r="C174" s="7">
         <v>14</v>
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -6833,72 +6833,64 @@
         <v>135</v>
       </c>
       <c t="s" r="H174" s="8">
-        <v>216</v>
+        <v>26</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>39</v>
+        <v>261</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>96</v>
-      </c>
-      <c t="s" r="K174" s="7">
-        <v>217</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="K174" s="7"/>
       <c r="L174" s="7"/>
-      <c t="s" r="M174" s="7">
-        <v>93</v>
-      </c>
+      <c r="M174" s="7"/>
     </row>
     <row r="175" ht="15" customHeight="1">
       <c t="s" r="A175" s="6">
         <v>13</v>
       </c>
       <c r="B175" s="7">
-        <v>721</v>
+        <v>632</v>
       </c>
       <c t="s" r="C175" s="7">
         <v>14</v>
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G175" s="8">
-        <v>216</v>
+        <v>26</v>
       </c>
       <c t="s" r="H175" s="8">
         <v>135</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>93</v>
+        <v>24</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>263</v>
-      </c>
-      <c t="s" r="K175" s="7">
-        <v>97</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="K175" s="7"/>
       <c r="L175" s="7"/>
-      <c t="s" r="M175" s="7">
-        <v>234</v>
-      </c>
+      <c r="M175" s="7"/>
     </row>
     <row r="176" ht="14.25" customHeight="1">
       <c t="s" r="A176" s="6">
         <v>13</v>
       </c>
       <c r="B176" s="7">
-        <v>1729</v>
+        <v>720</v>
       </c>
       <c t="s" r="C176" s="7">
         <v>14</v>
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -6907,64 +6899,72 @@
         <v>135</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>264</v>
+        <v>215</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>249</v>
+        <v>39</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>140</v>
-      </c>
-      <c r="K176" s="7"/>
+        <v>96</v>
+      </c>
+      <c t="s" r="K176" s="7">
+        <v>216</v>
+      </c>
       <c r="L176" s="7"/>
-      <c r="M176" s="7"/>
+      <c t="s" r="M176" s="7">
+        <v>93</v>
+      </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
       <c t="s" r="A177" s="6">
         <v>13</v>
       </c>
       <c r="B177" s="7">
-        <v>1728</v>
+        <v>721</v>
       </c>
       <c t="s" r="C177" s="7">
         <v>14</v>
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>264</v>
+        <v>215</v>
       </c>
       <c t="s" r="H177" s="8">
         <v>135</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>235</v>
+        <v>93</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>265</v>
-      </c>
-      <c r="K177" s="7"/>
+        <v>262</v>
+      </c>
+      <c t="s" r="K177" s="7">
+        <v>97</v>
+      </c>
       <c r="L177" s="7"/>
-      <c r="M177" s="7"/>
+      <c t="s" r="M177" s="7">
+        <v>233</v>
+      </c>
     </row>
     <row r="178" ht="14.25" customHeight="1">
       <c t="s" r="A178" s="6">
         <v>13</v>
       </c>
       <c r="B178" s="7">
-        <v>8892</v>
+        <v>1729</v>
       </c>
       <c t="s" r="C178" s="7">
         <v>14</v>
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -6973,13 +6973,13 @@
         <v>135</v>
       </c>
       <c t="s" r="H178" s="8">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>188</v>
+        <v>248</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -6990,29 +6990,29 @@
         <v>13</v>
       </c>
       <c r="B179" s="7">
-        <v>8893</v>
+        <v>1728</v>
       </c>
       <c t="s" r="C179" s="7">
         <v>14</v>
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G179" s="8">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c t="s" r="H179" s="8">
         <v>135</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>161</v>
+        <v>264</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -7023,14 +7023,14 @@
         <v>13</v>
       </c>
       <c r="B180" s="7">
-        <v>878</v>
+        <v>8892</v>
       </c>
       <c t="s" r="C180" s="7">
         <v>14</v>
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7039,29 +7039,47 @@
         <v>135</v>
       </c>
       <c t="s" r="H180" s="8">
-        <v>121</v>
+        <v>265</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>267</v>
+        <v>188</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
       <c r="M180" s="7"/>
     </row>
     <row r="181" ht="14.25" customHeight="1">
-      <c r="A181" s="6"/>
-      <c r="B181" s="7"/>
-      <c r="C181" s="7"/>
+      <c t="s" r="A181" s="6">
+        <v>13</v>
+      </c>
+      <c r="B181" s="7">
+        <v>8893</v>
+      </c>
+      <c t="s" r="C181" s="7">
+        <v>14</v>
+      </c>
       <c r="D181" s="7"/>
-      <c r="E181" s="7"/>
-      <c r="F181" s="7"/>
-      <c r="G181" s="8"/>
-      <c r="H181" s="8"/>
-      <c r="I181" s="7"/>
-      <c r="J181" s="7"/>
+      <c t="s" r="E181" s="7">
+        <v>260</v>
+      </c>
+      <c r="F181" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G181" s="8">
+        <v>265</v>
+      </c>
+      <c t="s" r="H181" s="8">
+        <v>135</v>
+      </c>
+      <c t="s" r="I181" s="7">
+        <v>142</v>
+      </c>
+      <c t="s" r="J181" s="7">
+        <v>161</v>
+      </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c r="M181" s="7"/>
@@ -7071,63 +7089,45 @@
         <v>13</v>
       </c>
       <c r="B182" s="7">
-        <v>503</v>
+        <v>878</v>
       </c>
       <c t="s" r="C182" s="7">
         <v>14</v>
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c t="s" r="H182" s="8">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>29</v>
+        <v>266</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c r="M182" s="7"/>
     </row>
     <row r="183" ht="14.25" customHeight="1">
-      <c t="s" r="A183" s="6">
-        <v>13</v>
-      </c>
-      <c r="B183" s="7">
-        <v>524</v>
-      </c>
-      <c t="s" r="C183" s="7">
-        <v>14</v>
-      </c>
+      <c r="A183" s="6"/>
+      <c r="B183" s="7"/>
+      <c r="C183" s="7"/>
       <c r="D183" s="7"/>
-      <c t="s" r="E183" s="7">
-        <v>268</v>
-      </c>
-      <c r="F183" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G183" s="8">
-        <v>135</v>
-      </c>
-      <c t="s" r="H183" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I183" s="7">
-        <v>92</v>
-      </c>
-      <c t="s" r="J183" s="7">
-        <v>177</v>
-      </c>
+      <c r="E183" s="7"/>
+      <c r="F183" s="7"/>
+      <c r="G183" s="8"/>
+      <c r="H183" s="8"/>
+      <c r="I183" s="7"/>
+      <c r="J183" s="7"/>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
       <c r="M183" s="7"/>
@@ -7137,14 +7137,14 @@
         <v>13</v>
       </c>
       <c r="B184" s="7">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c t="s" r="C184" s="7">
         <v>14</v>
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7156,10 +7156,10 @@
         <v>135</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>114</v>
+        <v>29</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7170,14 +7170,14 @@
         <v>13</v>
       </c>
       <c r="B185" s="7">
-        <v>510</v>
+        <v>524</v>
       </c>
       <c t="s" r="C185" s="7">
         <v>14</v>
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7189,10 +7189,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>218</v>
+        <v>92</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>54</v>
+        <v>177</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7203,14 +7203,14 @@
         <v>13</v>
       </c>
       <c r="B186" s="7">
-        <v>405</v>
+        <v>507</v>
       </c>
       <c t="s" r="C186" s="7">
         <v>14</v>
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7219,13 +7219,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H186" s="8">
-        <v>264</v>
+        <v>135</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>235</v>
+        <v>114</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7236,29 +7236,29 @@
         <v>13</v>
       </c>
       <c r="B187" s="7">
-        <v>406</v>
+        <v>510</v>
       </c>
       <c t="s" r="C187" s="7">
         <v>14</v>
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G187" s="8">
-        <v>264</v>
+        <v>135</v>
       </c>
       <c t="s" r="H187" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>76</v>
+        <v>217</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>189</v>
+        <v>54</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7269,14 +7269,14 @@
         <v>13</v>
       </c>
       <c r="B188" s="7">
-        <v>7526</v>
+        <v>405</v>
       </c>
       <c t="s" r="C188" s="7">
         <v>14</v>
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7285,13 +7285,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H188" s="8">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>270</v>
+        <v>148</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>214</v>
+        <v>75</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7299,114 +7299,114 @@
     </row>
     <row r="189" ht="14.25" customHeight="1">
       <c t="s" r="A189" s="6">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B189" s="7">
-        <v>7527</v>
+        <v>406</v>
       </c>
       <c t="s" r="C189" s="7">
         <v>14</v>
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G189" s="8">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c t="s" r="H189" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>271</v>
+        <v>76</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>272</v>
+        <v>189</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c r="M189" s="7"/>
     </row>
     <row r="190" ht="15" customHeight="1">
-      <c r="A190" s="6"/>
-      <c r="B190" s="7"/>
-      <c r="C190" s="7"/>
+      <c t="s" r="A190" s="6">
+        <v>13</v>
+      </c>
+      <c r="B190" s="7">
+        <v>7526</v>
+      </c>
+      <c t="s" r="C190" s="7">
+        <v>14</v>
+      </c>
       <c r="D190" s="7"/>
-      <c r="E190" s="7"/>
-      <c r="F190" s="7"/>
-      <c r="G190" s="8"/>
-      <c r="H190" s="8"/>
-      <c r="I190" s="7"/>
-      <c r="J190" s="7"/>
+      <c t="s" r="E190" s="7">
+        <v>267</v>
+      </c>
+      <c r="F190" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G190" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H190" s="8">
+        <v>268</v>
+      </c>
+      <c t="s" r="I190" s="7">
+        <v>269</v>
+      </c>
+      <c t="s" r="J190" s="7">
+        <v>213</v>
+      </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
       <c r="M190" s="7"/>
     </row>
     <row r="191" ht="14.25" customHeight="1">
       <c t="s" r="A191" s="6">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B191" s="7">
-        <v>919</v>
+        <v>7527</v>
       </c>
       <c t="s" r="C191" s="7">
         <v>14</v>
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G191" s="8">
-        <v>47</v>
+        <v>268</v>
       </c>
       <c t="s" r="H191" s="8">
-        <v>81</v>
+        <v>16</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>136</v>
+        <v>270</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>53</v>
+        <v>271</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
       <c r="M191" s="7"/>
     </row>
     <row r="192" ht="14.25" customHeight="1">
-      <c t="s" r="A192" s="6">
-        <v>13</v>
-      </c>
-      <c r="B192" s="7">
-        <v>5530</v>
-      </c>
-      <c t="s" r="C192" s="7">
-        <v>14</v>
-      </c>
+      <c r="A192" s="6"/>
+      <c r="B192" s="7"/>
+      <c r="C192" s="7"/>
       <c r="D192" s="7"/>
-      <c t="s" r="E192" s="7">
-        <v>273</v>
-      </c>
-      <c r="F192" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G192" s="8">
-        <v>81</v>
-      </c>
-      <c t="s" r="H192" s="8">
-        <v>266</v>
-      </c>
-      <c t="s" r="I192" s="7">
-        <v>192</v>
-      </c>
-      <c t="s" r="J192" s="7">
-        <v>55</v>
-      </c>
+      <c r="E192" s="7"/>
+      <c r="F192" s="7"/>
+      <c r="G192" s="8"/>
+      <c r="H192" s="8"/>
+      <c r="I192" s="7"/>
+      <c r="J192" s="7"/>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
       <c r="M192" s="7"/>
@@ -7416,29 +7416,29 @@
         <v>13</v>
       </c>
       <c r="B193" s="7">
-        <v>5531</v>
+        <v>919</v>
       </c>
       <c t="s" r="C193" s="7">
         <v>14</v>
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>266</v>
+        <v>47</v>
       </c>
       <c t="s" r="H193" s="8">
         <v>81</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>274</v>
+        <v>53</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7449,14 +7449,14 @@
         <v>13</v>
       </c>
       <c r="B194" s="7">
-        <v>1601</v>
+        <v>5530</v>
       </c>
       <c t="s" r="C194" s="7">
         <v>14</v>
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7465,29 +7465,47 @@
         <v>81</v>
       </c>
       <c t="s" r="H194" s="8">
-        <v>26</v>
+        <v>265</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>275</v>
+        <v>55</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
       <c r="M194" s="7"/>
     </row>
     <row r="195" ht="15" customHeight="1">
-      <c r="A195" s="6"/>
-      <c r="B195" s="7"/>
-      <c r="C195" s="7"/>
+      <c t="s" r="A195" s="6">
+        <v>13</v>
+      </c>
+      <c r="B195" s="7">
+        <v>5531</v>
+      </c>
+      <c t="s" r="C195" s="7">
+        <v>14</v>
+      </c>
       <c r="D195" s="7"/>
-      <c r="E195" s="7"/>
-      <c r="F195" s="7"/>
-      <c r="G195" s="8"/>
-      <c r="H195" s="8"/>
-      <c r="I195" s="7"/>
-      <c r="J195" s="7"/>
+      <c t="s" r="E195" s="7">
+        <v>272</v>
+      </c>
+      <c r="F195" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G195" s="8">
+        <v>265</v>
+      </c>
+      <c t="s" r="H195" s="8">
+        <v>81</v>
+      </c>
+      <c t="s" r="I195" s="7">
+        <v>76</v>
+      </c>
+      <c t="s" r="J195" s="7">
+        <v>273</v>
+      </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
       <c r="M195" s="7"/>
@@ -7497,63 +7515,45 @@
         <v>13</v>
       </c>
       <c r="B196" s="7">
-        <v>811</v>
+        <v>1601</v>
       </c>
       <c t="s" r="C196" s="7">
         <v>14</v>
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>277</v>
+        <v>26</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>30</v>
+        <v>189</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>95</v>
+        <v>274</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
       <c r="M196" s="7"/>
     </row>
     <row r="197" ht="14.25" customHeight="1">
-      <c t="s" r="A197" s="6">
-        <v>13</v>
-      </c>
-      <c r="B197" s="7">
-        <v>984</v>
-      </c>
-      <c t="s" r="C197" s="7">
-        <v>14</v>
-      </c>
+      <c r="A197" s="6"/>
+      <c r="B197" s="7"/>
+      <c r="C197" s="7"/>
       <c r="D197" s="7"/>
-      <c t="s" r="E197" s="7">
-        <v>276</v>
-      </c>
-      <c r="F197" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G197" s="8">
-        <v>277</v>
-      </c>
-      <c t="s" r="H197" s="8">
-        <v>45</v>
-      </c>
-      <c t="s" r="I197" s="7">
-        <v>40</v>
-      </c>
-      <c t="s" r="J197" s="7">
-        <v>248</v>
-      </c>
+      <c r="E197" s="7"/>
+      <c r="F197" s="7"/>
+      <c r="G197" s="8"/>
+      <c r="H197" s="8"/>
+      <c r="I197" s="7"/>
+      <c r="J197" s="7"/>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
       <c r="M197" s="7"/>
@@ -7563,29 +7563,29 @@
         <v>13</v>
       </c>
       <c r="B198" s="7">
-        <v>983</v>
+        <v>811</v>
       </c>
       <c t="s" r="C198" s="7">
         <v>14</v>
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
+        <v>275</v>
+      </c>
+      <c r="F198" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G198" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H198" s="8">
         <v>276</v>
       </c>
-      <c r="F198" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G198" s="8">
-        <v>45</v>
-      </c>
-      <c t="s" r="H198" s="8">
-        <v>277</v>
-      </c>
       <c t="s" r="I198" s="7">
-        <v>243</v>
+        <v>30</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>244</v>
+        <v>95</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7596,45 +7596,63 @@
         <v>13</v>
       </c>
       <c r="B199" s="7">
-        <v>812</v>
+        <v>984</v>
       </c>
       <c t="s" r="C199" s="7">
         <v>14</v>
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
+        <v>275</v>
+      </c>
+      <c r="F199" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G199" s="8">
         <v>276</v>
       </c>
-      <c r="F199" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G199" s="8">
-        <v>277</v>
-      </c>
       <c t="s" r="H199" s="8">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>159</v>
+        <v>40</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>68</v>
+        <v>247</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
       <c r="M199" s="7"/>
     </row>
     <row r="200" ht="15" customHeight="1">
-      <c r="A200" s="6"/>
-      <c r="B200" s="7"/>
-      <c r="C200" s="7"/>
+      <c t="s" r="A200" s="6">
+        <v>13</v>
+      </c>
+      <c r="B200" s="7">
+        <v>983</v>
+      </c>
+      <c t="s" r="C200" s="7">
+        <v>14</v>
+      </c>
       <c r="D200" s="7"/>
-      <c r="E200" s="7"/>
-      <c r="F200" s="7"/>
-      <c r="G200" s="8"/>
-      <c r="H200" s="8"/>
-      <c r="I200" s="7"/>
-      <c r="J200" s="7"/>
+      <c t="s" r="E200" s="7">
+        <v>275</v>
+      </c>
+      <c r="F200" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G200" s="8">
+        <v>45</v>
+      </c>
+      <c t="s" r="H200" s="8">
+        <v>276</v>
+      </c>
+      <c t="s" r="I200" s="7">
+        <v>242</v>
+      </c>
+      <c t="s" r="J200" s="7">
+        <v>243</v>
+      </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
       <c r="M200" s="7"/>
@@ -7644,63 +7662,45 @@
         <v>13</v>
       </c>
       <c r="B201" s="7">
-        <v>1382</v>
+        <v>812</v>
       </c>
       <c t="s" r="C201" s="7">
         <v>14</v>
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G201" s="8">
-        <v>26</v>
+        <v>276</v>
       </c>
       <c t="s" r="H201" s="8">
-        <v>110</v>
+        <v>26</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>279</v>
+        <v>150</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>224</v>
+        <v>68</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c r="M201" s="7"/>
     </row>
     <row r="202" ht="14.25" customHeight="1">
-      <c t="s" r="A202" s="6">
-        <v>13</v>
-      </c>
-      <c r="B202" s="7">
-        <v>1383</v>
-      </c>
-      <c t="s" r="C202" s="7">
-        <v>14</v>
-      </c>
+      <c r="A202" s="6"/>
+      <c r="B202" s="7"/>
+      <c r="C202" s="7"/>
       <c r="D202" s="7"/>
-      <c t="s" r="E202" s="7">
-        <v>278</v>
-      </c>
-      <c r="F202" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G202" s="8">
-        <v>110</v>
-      </c>
-      <c t="s" r="H202" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="I202" s="7">
-        <v>171</v>
-      </c>
-      <c t="s" r="J202" s="7">
-        <v>280</v>
-      </c>
+      <c r="E202" s="7"/>
+      <c r="F202" s="7"/>
+      <c r="G202" s="8"/>
+      <c r="H202" s="8"/>
+      <c r="I202" s="7"/>
+      <c r="J202" s="7"/>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c r="M202" s="7"/>
@@ -7710,29 +7710,29 @@
         <v>13</v>
       </c>
       <c r="B203" s="7">
-        <v>272</v>
+        <v>1382</v>
       </c>
       <c t="s" r="C203" s="7">
         <v>14</v>
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
+        <v>277</v>
+      </c>
+      <c r="F203" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G203" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H203" s="8">
+        <v>110</v>
+      </c>
+      <c t="s" r="I203" s="7">
         <v>278</v>
       </c>
-      <c r="F203" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G203" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="H203" s="8">
-        <v>216</v>
-      </c>
-      <c t="s" r="I203" s="7">
-        <v>30</v>
-      </c>
       <c t="s" r="J203" s="7">
-        <v>281</v>
+        <v>223</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7743,29 +7743,29 @@
         <v>13</v>
       </c>
       <c r="B204" s="7">
-        <v>273</v>
+        <v>1383</v>
       </c>
       <c t="s" r="C204" s="7">
         <v>14</v>
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G204" s="8">
-        <v>216</v>
+        <v>110</v>
       </c>
       <c t="s" r="H204" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>72</v>
+        <v>171</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>103</v>
+        <v>279</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -7776,14 +7776,14 @@
         <v>13</v>
       </c>
       <c r="B205" s="7">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c t="s" r="C205" s="7">
         <v>14</v>
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7792,72 +7792,64 @@
         <v>26</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>116</v>
+        <v>30</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>194</v>
-      </c>
-      <c t="s" r="K205" s="7">
-        <v>193</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="K205" s="7"/>
       <c r="L205" s="7"/>
-      <c t="s" r="M205" s="7">
-        <v>179</v>
-      </c>
+      <c r="M205" s="7"/>
     </row>
     <row r="206" ht="14.25" customHeight="1">
       <c t="s" r="A206" s="6">
         <v>13</v>
       </c>
       <c r="B206" s="7">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c t="s" r="C206" s="7">
         <v>14</v>
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c t="s" r="H206" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>157</v>
+        <v>72</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>221</v>
-      </c>
-      <c t="s" r="K206" s="7">
-        <v>196</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="K206" s="7"/>
       <c r="L206" s="7"/>
-      <c t="s" r="M206" s="7">
-        <v>67</v>
-      </c>
+      <c r="M206" s="7"/>
     </row>
     <row r="207" ht="14.25" customHeight="1">
       <c t="s" r="A207" s="6">
         <v>13</v>
       </c>
       <c r="B207" s="7">
-        <v>3908</v>
+        <v>278</v>
       </c>
       <c t="s" r="C207" s="7">
         <v>14</v>
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7866,128 +7858,136 @@
         <v>26</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>269</v>
+        <v>215</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>282</v>
+        <v>116</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>283</v>
-      </c>
-      <c r="K207" s="7"/>
+        <v>194</v>
+      </c>
+      <c t="s" r="K207" s="7">
+        <v>193</v>
+      </c>
       <c r="L207" s="7"/>
-      <c r="M207" s="7"/>
+      <c t="s" r="M207" s="7">
+        <v>179</v>
+      </c>
     </row>
     <row r="208" ht="14.25" customHeight="1">
       <c t="s" r="A208" s="6">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B208" s="7">
-        <v>3909</v>
+        <v>279</v>
       </c>
       <c t="s" r="C208" s="7">
         <v>14</v>
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>269</v>
+        <v>215</v>
       </c>
       <c t="s" r="H208" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>284</v>
+        <v>149</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>285</v>
-      </c>
-      <c r="K208" s="7"/>
+        <v>220</v>
+      </c>
+      <c t="s" r="K208" s="7">
+        <v>196</v>
+      </c>
       <c r="L208" s="7"/>
-      <c r="M208" s="7"/>
+      <c t="s" r="M208" s="7">
+        <v>67</v>
+      </c>
     </row>
     <row r="209" ht="14.25" customHeight="1">
-      <c r="A209" s="6"/>
-      <c r="B209" s="7"/>
-      <c r="C209" s="7"/>
+      <c t="s" r="A209" s="6">
+        <v>13</v>
+      </c>
+      <c r="B209" s="7">
+        <v>3908</v>
+      </c>
+      <c t="s" r="C209" s="7">
+        <v>14</v>
+      </c>
       <c r="D209" s="7"/>
-      <c r="E209" s="7"/>
-      <c r="F209" s="7"/>
-      <c r="G209" s="8"/>
-      <c r="H209" s="8"/>
-      <c r="I209" s="7"/>
-      <c r="J209" s="7"/>
+      <c t="s" r="E209" s="7">
+        <v>277</v>
+      </c>
+      <c r="F209" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G209" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H209" s="8">
+        <v>268</v>
+      </c>
+      <c t="s" r="I209" s="7">
+        <v>281</v>
+      </c>
+      <c t="s" r="J209" s="7">
+        <v>282</v>
+      </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c r="M209" s="7"/>
     </row>
     <row r="210" ht="15" customHeight="1">
       <c t="s" r="A210" s="6">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B210" s="7">
-        <v>129</v>
+        <v>3909</v>
       </c>
       <c t="s" r="C210" s="7">
         <v>14</v>
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
-        <v>16</v>
+        <v>268</v>
       </c>
       <c t="s" r="H210" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>52</v>
+        <v>283</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>136</v>
+        <v>284</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c r="M210" s="7"/>
     </row>
     <row r="211" ht="14.25" customHeight="1">
-      <c t="s" r="A211" s="6">
-        <v>13</v>
-      </c>
-      <c r="B211" s="7">
-        <v>335</v>
-      </c>
-      <c t="s" r="C211" s="7">
-        <v>14</v>
-      </c>
+      <c r="A211" s="6"/>
+      <c r="B211" s="7"/>
+      <c r="C211" s="7"/>
       <c r="D211" s="7"/>
-      <c t="s" r="E211" s="7">
-        <v>286</v>
-      </c>
-      <c r="F211" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G211" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="H211" s="8">
-        <v>45</v>
-      </c>
-      <c t="s" r="I211" s="7">
-        <v>287</v>
-      </c>
-      <c t="s" r="J211" s="7">
-        <v>210</v>
-      </c>
+      <c r="E211" s="7"/>
+      <c r="F211" s="7"/>
+      <c r="G211" s="8"/>
+      <c r="H211" s="8"/>
+      <c r="I211" s="7"/>
+      <c r="J211" s="7"/>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
       <c r="M211" s="7"/>
@@ -7997,29 +7997,29 @@
         <v>13</v>
       </c>
       <c r="B212" s="7">
-        <v>766</v>
+        <v>129</v>
       </c>
       <c t="s" r="C212" s="7">
         <v>14</v>
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G212" s="8">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c t="s" r="H212" s="8">
-        <v>216</v>
+        <v>26</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -8030,29 +8030,29 @@
         <v>13</v>
       </c>
       <c r="B213" s="7">
-        <v>767</v>
+        <v>335</v>
       </c>
       <c t="s" r="C213" s="7">
         <v>14</v>
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G213" s="8">
-        <v>216</v>
+        <v>26</v>
       </c>
       <c t="s" r="H213" s="8">
         <v>45</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>178</v>
+        <v>286</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8063,14 +8063,14 @@
         <v>13</v>
       </c>
       <c r="B214" s="7">
-        <v>338</v>
+        <v>766</v>
       </c>
       <c t="s" r="C214" s="7">
         <v>14</v>
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8079,29 +8079,47 @@
         <v>45</v>
       </c>
       <c t="s" r="H214" s="8">
-        <v>26</v>
+        <v>215</v>
       </c>
       <c t="s" r="I214" s="7">
+        <v>120</v>
+      </c>
+      <c t="s" r="J214" s="7">
         <v>158</v>
-      </c>
-      <c t="s" r="J214" s="7">
-        <v>57</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
       <c r="M214" s="7"/>
     </row>
     <row r="215" ht="15" customHeight="1">
-      <c r="A215" s="6"/>
-      <c r="B215" s="7"/>
-      <c r="C215" s="7"/>
+      <c t="s" r="A215" s="6">
+        <v>13</v>
+      </c>
+      <c r="B215" s="7">
+        <v>767</v>
+      </c>
+      <c t="s" r="C215" s="7">
+        <v>14</v>
+      </c>
       <c r="D215" s="7"/>
-      <c r="E215" s="7"/>
-      <c r="F215" s="7"/>
-      <c r="G215" s="8"/>
-      <c r="H215" s="8"/>
-      <c r="I215" s="7"/>
-      <c r="J215" s="7"/>
+      <c t="s" r="E215" s="7">
+        <v>285</v>
+      </c>
+      <c r="F215" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G215" s="8">
+        <v>215</v>
+      </c>
+      <c t="s" r="H215" s="8">
+        <v>45</v>
+      </c>
+      <c t="s" r="I215" s="7">
+        <v>178</v>
+      </c>
+      <c t="s" r="J215" s="7">
+        <v>187</v>
+      </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
       <c r="M215" s="7"/>
@@ -8111,63 +8129,45 @@
         <v>13</v>
       </c>
       <c r="B216" s="7">
-        <v>447</v>
+        <v>338</v>
       </c>
       <c t="s" r="C216" s="7">
         <v>14</v>
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G216" s="8">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>52</v>
+        <v>159</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
       <c r="M216" s="7"/>
     </row>
     <row r="217" ht="14.25" customHeight="1">
-      <c t="s" r="A217" s="6">
-        <v>13</v>
-      </c>
-      <c r="B217" s="7">
-        <v>440</v>
-      </c>
-      <c t="s" r="C217" s="7">
-        <v>14</v>
-      </c>
+      <c r="A217" s="6"/>
+      <c r="B217" s="7"/>
+      <c r="C217" s="7"/>
       <c r="D217" s="7"/>
-      <c t="s" r="E217" s="7">
-        <v>288</v>
-      </c>
-      <c r="F217" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G217" s="8">
-        <v>45</v>
-      </c>
-      <c t="s" r="H217" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I217" s="7">
-        <v>287</v>
-      </c>
-      <c t="s" r="J217" s="7">
-        <v>103</v>
-      </c>
+      <c r="E217" s="7"/>
+      <c r="F217" s="7"/>
+      <c r="G217" s="8"/>
+      <c r="H217" s="8"/>
+      <c r="I217" s="7"/>
+      <c r="J217" s="7"/>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
       <c r="M217" s="7"/>
@@ -8177,14 +8177,14 @@
         <v>13</v>
       </c>
       <c r="B218" s="7">
-        <v>407</v>
+        <v>447</v>
       </c>
       <c t="s" r="C218" s="7">
         <v>14</v>
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8193,13 +8193,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H218" s="8">
-        <v>264</v>
+        <v>45</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>194</v>
+        <v>96</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8210,29 +8210,29 @@
         <v>13</v>
       </c>
       <c r="B219" s="7">
-        <v>408</v>
+        <v>440</v>
       </c>
       <c t="s" r="C219" s="7">
         <v>14</v>
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G219" s="8">
-        <v>264</v>
+        <v>45</v>
       </c>
       <c t="s" r="H219" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>157</v>
+        <v>286</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8243,14 +8243,14 @@
         <v>13</v>
       </c>
       <c r="B220" s="7">
-        <v>1127</v>
+        <v>407</v>
       </c>
       <c t="s" r="C220" s="7">
         <v>14</v>
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8259,13 +8259,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>26</v>
+        <v>263</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>289</v>
+        <v>194</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8276,45 +8276,63 @@
         <v>13</v>
       </c>
       <c r="B221" s="7">
-        <v>1128</v>
+        <v>408</v>
       </c>
       <c t="s" r="C221" s="7">
         <v>14</v>
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>26</v>
+        <v>263</v>
       </c>
       <c t="s" r="H221" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>290</v>
+        <v>149</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>291</v>
+        <v>188</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
       <c r="M221" s="7"/>
     </row>
     <row r="222" ht="14.25" customHeight="1">
-      <c r="A222" s="6"/>
-      <c r="B222" s="7"/>
-      <c r="C222" s="7"/>
+      <c t="s" r="A222" s="6">
+        <v>13</v>
+      </c>
+      <c r="B222" s="7">
+        <v>1127</v>
+      </c>
+      <c t="s" r="C222" s="7">
+        <v>14</v>
+      </c>
       <c r="D222" s="7"/>
-      <c r="E222" s="7"/>
-      <c r="F222" s="7"/>
-      <c r="G222" s="8"/>
-      <c r="H222" s="8"/>
-      <c r="I222" s="7"/>
-      <c r="J222" s="7"/>
+      <c t="s" r="E222" s="7">
+        <v>287</v>
+      </c>
+      <c r="F222" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G222" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H222" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="I222" s="7">
+        <v>57</v>
+      </c>
+      <c t="s" r="J222" s="7">
+        <v>288</v>
+      </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
       <c r="M222" s="7"/>
@@ -8324,67 +8342,45 @@
         <v>13</v>
       </c>
       <c r="B223" s="7">
-        <v>869</v>
+        <v>1128</v>
       </c>
       <c t="s" r="C223" s="7">
         <v>14</v>
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G223" s="8">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c t="s" r="H223" s="8">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>132</v>
+        <v>289</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>242</v>
-      </c>
-      <c t="s" r="K223" s="7">
-        <v>91</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="K223" s="7"/>
       <c r="L223" s="7"/>
-      <c t="s" r="M223" s="7">
-        <v>115</v>
-      </c>
+      <c r="M223" s="7"/>
     </row>
     <row r="224" ht="14.25" customHeight="1">
-      <c t="s" r="A224" s="6">
-        <v>13</v>
-      </c>
-      <c r="B224" s="7">
-        <v>214</v>
-      </c>
-      <c t="s" r="C224" s="7">
-        <v>14</v>
-      </c>
+      <c r="A224" s="6"/>
+      <c r="B224" s="7"/>
+      <c r="C224" s="7"/>
       <c r="D224" s="7"/>
-      <c t="s" r="E224" s="7">
-        <v>292</v>
-      </c>
-      <c r="F224" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G224" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="H224" s="8">
-        <v>173</v>
-      </c>
-      <c t="s" r="I224" s="7">
-        <v>123</v>
-      </c>
-      <c t="s" r="J224" s="7">
-        <v>235</v>
-      </c>
+      <c r="E224" s="7"/>
+      <c r="F224" s="7"/>
+      <c r="G224" s="8"/>
+      <c r="H224" s="8"/>
+      <c r="I224" s="7"/>
+      <c r="J224" s="7"/>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
       <c r="M224" s="7"/>
@@ -8394,47 +8390,51 @@
         <v>13</v>
       </c>
       <c r="B225" s="7">
-        <v>213</v>
+        <v>869</v>
       </c>
       <c t="s" r="C225" s="7">
         <v>14</v>
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G225" s="8">
-        <v>173</v>
+        <v>47</v>
       </c>
       <c t="s" r="H225" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>236</v>
+        <v>132</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>76</v>
-      </c>
-      <c r="K225" s="7"/>
+        <v>240</v>
+      </c>
+      <c t="s" r="K225" s="7">
+        <v>91</v>
+      </c>
       <c r="L225" s="7"/>
-      <c r="M225" s="7"/>
+      <c t="s" r="M225" s="7">
+        <v>115</v>
+      </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
       <c t="s" r="A226" s="6">
         <v>13</v>
       </c>
       <c r="B226" s="7">
-        <v>154</v>
+        <v>214</v>
       </c>
       <c t="s" r="C226" s="7">
         <v>14</v>
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8443,13 +8443,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H226" s="8">
-        <v>16</v>
+        <v>173</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>204</v>
+        <v>123</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>259</v>
+        <v>148</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8460,45 +8460,63 @@
         <v>13</v>
       </c>
       <c r="B227" s="7">
-        <v>163</v>
+        <v>213</v>
       </c>
       <c t="s" r="C227" s="7">
         <v>14</v>
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G227" s="8">
-        <v>16</v>
+        <v>173</v>
       </c>
       <c t="s" r="H227" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>293</v>
+        <v>234</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>267</v>
+        <v>76</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
       <c r="M227" s="7"/>
     </row>
     <row r="228" ht="14.25" customHeight="1">
-      <c r="A228" s="6"/>
-      <c r="B228" s="7"/>
-      <c r="C228" s="7"/>
+      <c t="s" r="A228" s="6">
+        <v>13</v>
+      </c>
+      <c r="B228" s="7">
+        <v>154</v>
+      </c>
+      <c t="s" r="C228" s="7">
+        <v>14</v>
+      </c>
       <c r="D228" s="7"/>
-      <c r="E228" s="7"/>
-      <c r="F228" s="7"/>
-      <c r="G228" s="8"/>
-      <c r="H228" s="8"/>
-      <c r="I228" s="7"/>
-      <c r="J228" s="7"/>
+      <c t="s" r="E228" s="7">
+        <v>291</v>
+      </c>
+      <c r="F228" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G228" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H228" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I228" s="7">
+        <v>204</v>
+      </c>
+      <c t="s" r="J228" s="7">
+        <v>258</v>
+      </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
       <c r="M228" s="7"/>
@@ -8508,63 +8526,45 @@
         <v>13</v>
       </c>
       <c r="B229" s="7">
-        <v>989</v>
+        <v>163</v>
       </c>
       <c t="s" r="C229" s="7">
         <v>14</v>
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c t="s" r="H229" s="8">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>32</v>
+        <v>266</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
       <c r="M229" s="7"/>
     </row>
     <row r="230" ht="15" customHeight="1">
-      <c t="s" r="A230" s="6">
-        <v>13</v>
-      </c>
-      <c r="B230" s="7">
-        <v>973</v>
-      </c>
-      <c t="s" r="C230" s="7">
-        <v>14</v>
-      </c>
+      <c r="A230" s="6"/>
+      <c r="B230" s="7"/>
+      <c r="C230" s="7"/>
       <c r="D230" s="7"/>
-      <c t="s" r="E230" s="7">
-        <v>294</v>
-      </c>
-      <c r="F230" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G230" s="8">
-        <v>135</v>
-      </c>
-      <c t="s" r="H230" s="8">
-        <v>277</v>
-      </c>
-      <c t="s" r="I230" s="7">
-        <v>234</v>
-      </c>
-      <c t="s" r="J230" s="7">
-        <v>265</v>
-      </c>
+      <c r="E230" s="7"/>
+      <c r="F230" s="7"/>
+      <c r="G230" s="8"/>
+      <c r="H230" s="8"/>
+      <c r="I230" s="7"/>
+      <c r="J230" s="7"/>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
       <c r="M230" s="7"/>
@@ -8574,29 +8574,29 @@
         <v>13</v>
       </c>
       <c r="B231" s="7">
-        <v>814</v>
+        <v>989</v>
       </c>
       <c t="s" r="C231" s="7">
         <v>14</v>
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
+        <v>293</v>
+      </c>
+      <c r="F231" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G231" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="H231" s="8">
+        <v>135</v>
+      </c>
+      <c t="s" r="I231" s="7">
         <v>294</v>
       </c>
-      <c r="F231" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G231" s="8">
-        <v>277</v>
-      </c>
-      <c t="s" r="H231" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="I231" s="7">
-        <v>220</v>
-      </c>
       <c t="s" r="J231" s="7">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8607,29 +8607,29 @@
         <v>13</v>
       </c>
       <c r="B232" s="7">
-        <v>3900</v>
+        <v>973</v>
       </c>
       <c t="s" r="C232" s="7">
         <v>14</v>
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
-        <v>26</v>
+        <v>135</v>
       </c>
       <c t="s" r="H232" s="8">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>36</v>
+        <v>264</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8637,114 +8637,114 @@
     </row>
     <row r="233" ht="14.25" customHeight="1">
       <c t="s" r="A233" s="6">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B233" s="7">
-        <v>3901</v>
+        <v>814</v>
       </c>
       <c t="s" r="C233" s="7">
         <v>14</v>
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G233" s="8">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c t="s" r="H233" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>297</v>
+        <v>219</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>298</v>
+        <v>44</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
       <c r="M233" s="7"/>
     </row>
     <row r="234" ht="14.25" customHeight="1">
-      <c r="A234" s="6"/>
-      <c r="B234" s="7"/>
-      <c r="C234" s="7"/>
+      <c t="s" r="A234" s="6">
+        <v>13</v>
+      </c>
+      <c r="B234" s="7">
+        <v>3900</v>
+      </c>
+      <c t="s" r="C234" s="7">
+        <v>14</v>
+      </c>
       <c r="D234" s="7"/>
-      <c r="E234" s="7"/>
-      <c r="F234" s="7"/>
-      <c r="G234" s="8"/>
-      <c r="H234" s="8"/>
-      <c r="I234" s="7"/>
-      <c r="J234" s="7"/>
+      <c t="s" r="E234" s="7">
+        <v>293</v>
+      </c>
+      <c r="F234" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G234" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H234" s="8">
+        <v>295</v>
+      </c>
+      <c t="s" r="I234" s="7">
+        <v>189</v>
+      </c>
+      <c t="s" r="J234" s="7">
+        <v>36</v>
+      </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
       <c r="M234" s="7"/>
     </row>
     <row r="235" ht="15" customHeight="1">
       <c t="s" r="A235" s="6">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B235" s="7">
-        <v>879</v>
+        <v>3901</v>
       </c>
       <c t="s" r="C235" s="7">
         <v>14</v>
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G235" s="8">
-        <v>121</v>
+        <v>295</v>
       </c>
       <c t="s" r="H235" s="8">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>240</v>
+        <v>296</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>128</v>
+        <v>297</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
       <c r="M235" s="7"/>
     </row>
     <row r="236" ht="14.25" customHeight="1">
-      <c t="s" r="A236" s="6">
-        <v>13</v>
-      </c>
-      <c r="B236" s="7">
-        <v>8890</v>
-      </c>
-      <c t="s" r="C236" s="7">
-        <v>14</v>
-      </c>
+      <c r="A236" s="6"/>
+      <c r="B236" s="7"/>
+      <c r="C236" s="7"/>
       <c r="D236" s="7"/>
-      <c t="s" r="E236" s="7">
-        <v>299</v>
-      </c>
-      <c r="F236" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G236" s="8">
-        <v>135</v>
-      </c>
-      <c t="s" r="H236" s="8">
-        <v>266</v>
-      </c>
-      <c t="s" r="I236" s="7">
-        <v>137</v>
-      </c>
-      <c t="s" r="J236" s="7">
-        <v>99</v>
-      </c>
+      <c r="E236" s="7"/>
+      <c r="F236" s="7"/>
+      <c r="G236" s="8"/>
+      <c r="H236" s="8"/>
+      <c r="I236" s="7"/>
+      <c r="J236" s="7"/>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
       <c r="M236" s="7"/>
@@ -8754,29 +8754,29 @@
         <v>13</v>
       </c>
       <c r="B237" s="7">
-        <v>8891</v>
+        <v>879</v>
       </c>
       <c t="s" r="C237" s="7">
         <v>14</v>
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>266</v>
+        <v>121</v>
       </c>
       <c t="s" r="H237" s="8">
         <v>135</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>186</v>
+        <v>128</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -8787,14 +8787,14 @@
         <v>13</v>
       </c>
       <c r="B238" s="7">
-        <v>633</v>
+        <v>8890</v>
       </c>
       <c t="s" r="C238" s="7">
         <v>14</v>
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8803,33 +8803,47 @@
         <v>135</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>26</v>
+        <v>265</v>
       </c>
       <c t="s" r="I238" s="7">
+        <v>137</v>
+      </c>
+      <c t="s" r="J238" s="7">
         <v>99</v>
       </c>
-      <c t="s" r="J238" s="7">
-        <v>179</v>
-      </c>
-      <c t="s" r="K238" s="7">
-        <v>141</v>
-      </c>
+      <c r="K238" s="7"/>
       <c r="L238" s="7"/>
-      <c t="s" r="M238" s="7">
-        <v>67</v>
-      </c>
+      <c r="M238" s="7"/>
     </row>
     <row r="239" ht="14.25" customHeight="1">
-      <c r="A239" s="6"/>
-      <c r="B239" s="7"/>
-      <c r="C239" s="7"/>
+      <c t="s" r="A239" s="6">
+        <v>13</v>
+      </c>
+      <c r="B239" s="7">
+        <v>8891</v>
+      </c>
+      <c t="s" r="C239" s="7">
+        <v>14</v>
+      </c>
       <c r="D239" s="7"/>
-      <c r="E239" s="7"/>
-      <c r="F239" s="7"/>
-      <c r="G239" s="8"/>
-      <c r="H239" s="8"/>
-      <c r="I239" s="7"/>
-      <c r="J239" s="7"/>
+      <c t="s" r="E239" s="7">
+        <v>298</v>
+      </c>
+      <c r="F239" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G239" s="8">
+        <v>265</v>
+      </c>
+      <c t="s" r="H239" s="8">
+        <v>135</v>
+      </c>
+      <c t="s" r="I239" s="7">
+        <v>148</v>
+      </c>
+      <c t="s" r="J239" s="7">
+        <v>186</v>
+      </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c r="M239" s="7"/>
@@ -8839,218 +8853,204 @@
         <v>13</v>
       </c>
       <c r="B240" s="7">
-        <v>823</v>
+        <v>633</v>
       </c>
       <c t="s" r="C240" s="7">
         <v>14</v>
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G240" s="8">
-        <v>17</v>
+        <v>135</v>
       </c>
       <c t="s" r="H240" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>225</v>
+        <v>99</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>146</v>
-      </c>
-      <c r="K240" s="7"/>
+        <v>179</v>
+      </c>
+      <c t="s" r="K240" s="7">
+        <v>141</v>
+      </c>
       <c r="L240" s="7"/>
-      <c r="M240" s="7"/>
+      <c t="s" r="M240" s="7">
+        <v>67</v>
+      </c>
     </row>
     <row r="241" ht="14.25" customHeight="1">
-      <c t="s" r="A241" s="6">
-        <v>13</v>
-      </c>
-      <c r="B241" s="7">
-        <v>842</v>
-      </c>
-      <c t="s" r="C241" s="7">
-        <v>14</v>
-      </c>
+      <c r="A241" s="6"/>
+      <c r="B241" s="7"/>
+      <c r="C241" s="7"/>
       <c r="D241" s="7"/>
-      <c t="s" r="E241" s="7">
-        <v>300</v>
-      </c>
-      <c r="F241" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G241" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="H241" s="8">
-        <v>83</v>
-      </c>
-      <c t="s" r="I241" s="7">
-        <v>103</v>
-      </c>
-      <c t="s" r="J241" s="7">
-        <v>34</v>
-      </c>
-      <c t="s" r="K241" s="7">
-        <v>116</v>
-      </c>
+      <c r="E241" s="7"/>
+      <c r="F241" s="7"/>
+      <c r="G241" s="8"/>
+      <c r="H241" s="8"/>
+      <c r="I241" s="7"/>
+      <c r="J241" s="7"/>
+      <c r="K241" s="7"/>
       <c r="L241" s="7"/>
-      <c t="s" r="M241" s="7">
-        <v>221</v>
-      </c>
+      <c r="M241" s="7"/>
     </row>
     <row r="242" ht="14.25" customHeight="1">
       <c t="s" r="A242" s="6">
         <v>13</v>
       </c>
       <c r="B242" s="7">
-        <v>843</v>
+        <v>823</v>
       </c>
       <c t="s" r="C242" s="7">
         <v>14</v>
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c t="s" r="H242" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>44</v>
+        <v>224</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>230</v>
-      </c>
-      <c t="s" r="K242" s="7">
-        <v>122</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="K242" s="7"/>
       <c r="L242" s="7"/>
-      <c t="s" r="M242" s="7">
-        <v>301</v>
-      </c>
+      <c r="M242" s="7"/>
     </row>
     <row r="243" ht="14.25" customHeight="1">
       <c t="s" r="A243" s="6">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B243" s="7">
-        <v>91</v>
+        <v>842</v>
       </c>
       <c t="s" r="C243" s="7">
         <v>14</v>
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
+        <v>299</v>
+      </c>
+      <c r="F243" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G243" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H243" s="8">
+        <v>83</v>
+      </c>
+      <c t="s" r="I243" s="7">
+        <v>103</v>
+      </c>
+      <c t="s" r="J243" s="7">
+        <v>34</v>
+      </c>
+      <c t="s" r="K243" s="7">
+        <v>116</v>
+      </c>
+      <c r="L243" s="7"/>
+      <c t="s" r="M243" s="7">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="244" ht="14.25" customHeight="1">
+      <c t="s" r="A244" s="6">
+        <v>13</v>
+      </c>
+      <c r="B244" s="7">
+        <v>843</v>
+      </c>
+      <c t="s" r="C244" s="7">
+        <v>14</v>
+      </c>
+      <c r="D244" s="7"/>
+      <c t="s" r="E244" s="7">
+        <v>299</v>
+      </c>
+      <c r="F244" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G244" s="8">
+        <v>83</v>
+      </c>
+      <c t="s" r="H244" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="I244" s="7">
+        <v>44</v>
+      </c>
+      <c t="s" r="J244" s="7">
+        <v>229</v>
+      </c>
+      <c t="s" r="K244" s="7">
+        <v>122</v>
+      </c>
+      <c r="L244" s="7"/>
+      <c t="s" r="M244" s="7">
         <v>300</v>
       </c>
-      <c r="F243" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G243" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="H243" s="8">
-        <v>251</v>
-      </c>
-      <c t="s" r="I243" s="7">
-        <v>36</v>
-      </c>
-      <c t="s" r="J243" s="7">
-        <v>225</v>
-      </c>
-      <c r="K243" s="7"/>
-      <c r="L243" s="7"/>
-      <c r="M243" s="7"/>
-    </row>
-    <row r="244" ht="14.25" customHeight="1">
-      <c r="A244" s="6"/>
-      <c r="B244" s="7"/>
-      <c r="C244" s="7"/>
-      <c r="D244" s="7"/>
-      <c r="E244" s="7"/>
-      <c r="F244" s="7"/>
-      <c r="G244" s="8"/>
-      <c r="H244" s="8"/>
-      <c r="I244" s="7"/>
-      <c r="J244" s="7"/>
-      <c r="K244" s="7"/>
-      <c r="L244" s="7"/>
-      <c r="M244" s="7"/>
     </row>
     <row r="245" ht="15" customHeight="1">
       <c t="s" r="A245" s="6">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B245" s="7">
-        <v>835</v>
+        <v>91</v>
       </c>
       <c t="s" r="C245" s="7">
         <v>14</v>
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>121</v>
+        <v>26</v>
       </c>
       <c t="s" r="H245" s="8">
-        <v>81</v>
+        <v>250</v>
       </c>
       <c t="s" r="I245" s="7">
+        <v>36</v>
+      </c>
+      <c t="s" r="J245" s="7">
         <v>224</v>
-      </c>
-      <c t="s" r="J245" s="7">
-        <v>112</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
       <c r="M245" s="7"/>
     </row>
     <row r="246" ht="14.25" customHeight="1">
-      <c t="s" r="A246" s="6">
-        <v>13</v>
-      </c>
-      <c r="B246" s="7">
-        <v>730</v>
-      </c>
-      <c t="s" r="C246" s="7">
-        <v>14</v>
-      </c>
+      <c r="A246" s="6"/>
+      <c r="B246" s="7"/>
+      <c r="C246" s="7"/>
       <c r="D246" s="7"/>
-      <c t="s" r="E246" s="7">
-        <v>302</v>
-      </c>
-      <c r="F246" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G246" s="8">
-        <v>81</v>
-      </c>
-      <c t="s" r="H246" s="8">
-        <v>216</v>
-      </c>
-      <c t="s" r="I246" s="7">
-        <v>241</v>
-      </c>
-      <c t="s" r="J246" s="7">
-        <v>210</v>
-      </c>
+      <c r="E246" s="7"/>
+      <c r="F246" s="7"/>
+      <c r="G246" s="8"/>
+      <c r="H246" s="8"/>
+      <c r="I246" s="7"/>
+      <c r="J246" s="7"/>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
       <c r="M246" s="7"/>
@@ -9060,29 +9060,29 @@
         <v>13</v>
       </c>
       <c r="B247" s="7">
-        <v>731</v>
+        <v>835</v>
       </c>
       <c t="s" r="C247" s="7">
         <v>14</v>
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G247" s="8">
-        <v>216</v>
+        <v>121</v>
       </c>
       <c t="s" r="H247" s="8">
         <v>81</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>146</v>
+        <v>223</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>303</v>
+        <v>112</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9093,14 +9093,14 @@
         <v>13</v>
       </c>
       <c r="B248" s="7">
-        <v>774</v>
+        <v>730</v>
       </c>
       <c t="s" r="C248" s="7">
         <v>14</v>
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9109,13 +9109,13 @@
         <v>81</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>16</v>
+        <v>215</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>304</v>
+        <v>210</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9126,29 +9126,29 @@
         <v>13</v>
       </c>
       <c r="B249" s="7">
-        <v>787</v>
+        <v>731</v>
       </c>
       <c t="s" r="C249" s="7">
         <v>14</v>
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>16</v>
+        <v>215</v>
       </c>
       <c t="s" r="H249" s="8">
         <v>81</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>66</v>
+        <v>241</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -9159,14 +9159,14 @@
         <v>13</v>
       </c>
       <c r="B250" s="7">
-        <v>834</v>
+        <v>774</v>
       </c>
       <c t="s" r="C250" s="7">
         <v>14</v>
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9175,29 +9175,47 @@
         <v>81</v>
       </c>
       <c t="s" r="H250" s="8">
-        <v>121</v>
+        <v>16</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>306</v>
+        <v>226</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>279</v>
+        <v>303</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
       <c r="M250" s="7"/>
     </row>
     <row r="251" ht="14.25" customHeight="1">
-      <c r="A251" s="6"/>
-      <c r="B251" s="7"/>
-      <c r="C251" s="7"/>
+      <c t="s" r="A251" s="6">
+        <v>13</v>
+      </c>
+      <c r="B251" s="7">
+        <v>787</v>
+      </c>
+      <c t="s" r="C251" s="7">
+        <v>14</v>
+      </c>
       <c r="D251" s="7"/>
-      <c r="E251" s="7"/>
-      <c r="F251" s="7"/>
-      <c r="G251" s="8"/>
-      <c r="H251" s="8"/>
-      <c r="I251" s="7"/>
-      <c r="J251" s="7"/>
+      <c t="s" r="E251" s="7">
+        <v>301</v>
+      </c>
+      <c r="F251" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G251" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H251" s="8">
+        <v>81</v>
+      </c>
+      <c t="s" r="I251" s="7">
+        <v>66</v>
+      </c>
+      <c t="s" r="J251" s="7">
+        <v>304</v>
+      </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c r="M251" s="7"/>
@@ -9207,63 +9225,45 @@
         <v>13</v>
       </c>
       <c r="B252" s="7">
-        <v>915</v>
+        <v>834</v>
       </c>
       <c t="s" r="C252" s="7">
         <v>14</v>
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G252" s="8">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c t="s" r="H252" s="8">
-        <v>277</v>
+        <v>121</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>112</v>
+        <v>305</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>116</v>
+        <v>278</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
       <c r="M252" s="7"/>
     </row>
     <row r="253" ht="14.25" customHeight="1">
-      <c t="s" r="A253" s="6">
-        <v>13</v>
-      </c>
-      <c r="B253" s="7">
-        <v>916</v>
-      </c>
-      <c t="s" r="C253" s="7">
-        <v>14</v>
-      </c>
+      <c r="A253" s="6"/>
+      <c r="B253" s="7"/>
+      <c r="C253" s="7"/>
       <c r="D253" s="7"/>
-      <c t="s" r="E253" s="7">
-        <v>307</v>
-      </c>
-      <c r="F253" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G253" s="8">
-        <v>277</v>
-      </c>
-      <c t="s" r="H253" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I253" s="7">
-        <v>185</v>
-      </c>
-      <c t="s" r="J253" s="7">
-        <v>55</v>
-      </c>
+      <c r="E253" s="7"/>
+      <c r="F253" s="7"/>
+      <c r="G253" s="8"/>
+      <c r="H253" s="8"/>
+      <c r="I253" s="7"/>
+      <c r="J253" s="7"/>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
       <c r="M253" s="7"/>
@@ -9273,14 +9273,14 @@
         <v>13</v>
       </c>
       <c r="B254" s="7">
-        <v>781</v>
+        <v>915</v>
       </c>
       <c t="s" r="C254" s="7">
         <v>14</v>
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9289,13 +9289,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H254" s="8">
-        <v>81</v>
+        <v>276</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>188</v>
+        <v>112</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9306,45 +9306,63 @@
         <v>13</v>
       </c>
       <c r="B255" s="7">
-        <v>780</v>
+        <v>916</v>
       </c>
       <c t="s" r="C255" s="7">
         <v>14</v>
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G255" s="8">
-        <v>81</v>
+        <v>276</v>
       </c>
       <c t="s" r="H255" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>68</v>
+        <v>185</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>308</v>
+        <v>55</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
       <c r="M255" s="7"/>
     </row>
     <row r="256" ht="14.25" customHeight="1">
-      <c r="A256" s="6"/>
-      <c r="B256" s="7"/>
-      <c r="C256" s="7"/>
+      <c t="s" r="A256" s="6">
+        <v>13</v>
+      </c>
+      <c r="B256" s="7">
+        <v>781</v>
+      </c>
+      <c t="s" r="C256" s="7">
+        <v>14</v>
+      </c>
       <c r="D256" s="7"/>
-      <c r="E256" s="7"/>
-      <c r="F256" s="7"/>
-      <c r="G256" s="8"/>
-      <c r="H256" s="8"/>
-      <c r="I256" s="7"/>
-      <c r="J256" s="7"/>
+      <c t="s" r="E256" s="7">
+        <v>306</v>
+      </c>
+      <c r="F256" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G256" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H256" s="8">
+        <v>81</v>
+      </c>
+      <c t="s" r="I256" s="7">
+        <v>188</v>
+      </c>
+      <c t="s" r="J256" s="7">
+        <v>21</v>
+      </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c r="M256" s="7"/>
@@ -9354,63 +9372,45 @@
         <v>13</v>
       </c>
       <c r="B257" s="7">
-        <v>981</v>
+        <v>780</v>
       </c>
       <c t="s" r="C257" s="7">
         <v>14</v>
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G257" s="8">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c t="s" r="H257" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>132</v>
+        <v>68</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>177</v>
+        <v>307</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
       <c r="M257" s="7"/>
     </row>
     <row r="258" ht="14.25" customHeight="1">
-      <c t="s" r="A258" s="6">
-        <v>13</v>
-      </c>
-      <c r="B258" s="7">
-        <v>901</v>
-      </c>
-      <c t="s" r="C258" s="7">
-        <v>14</v>
-      </c>
+      <c r="A258" s="6"/>
+      <c r="B258" s="7"/>
+      <c r="C258" s="7"/>
       <c r="D258" s="7"/>
-      <c t="s" r="E258" s="7">
-        <v>309</v>
-      </c>
-      <c r="F258" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G258" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H258" s="8">
-        <v>310</v>
-      </c>
-      <c t="s" r="I258" s="7">
-        <v>72</v>
-      </c>
-      <c t="s" r="J258" s="7">
-        <v>139</v>
-      </c>
+      <c r="E258" s="7"/>
+      <c r="F258" s="7"/>
+      <c r="G258" s="8"/>
+      <c r="H258" s="8"/>
+      <c r="I258" s="7"/>
+      <c r="J258" s="7"/>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
       <c r="M258" s="7"/>
@@ -9420,29 +9420,29 @@
         <v>13</v>
       </c>
       <c r="B259" s="7">
-        <v>902</v>
+        <v>981</v>
       </c>
       <c t="s" r="C259" s="7">
         <v>14</v>
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G259" s="8">
-        <v>310</v>
+        <v>47</v>
       </c>
       <c t="s" r="H259" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>41</v>
+        <v>132</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9453,14 +9453,14 @@
         <v>13</v>
       </c>
       <c r="B260" s="7">
-        <v>517</v>
+        <v>901</v>
       </c>
       <c t="s" r="C260" s="7">
         <v>14</v>
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9469,13 +9469,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>135</v>
+        <v>309</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>187</v>
+        <v>72</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>198</v>
+        <v>139</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -9486,29 +9486,29 @@
         <v>13</v>
       </c>
       <c r="B261" s="7">
-        <v>520</v>
+        <v>902</v>
       </c>
       <c t="s" r="C261" s="7">
         <v>14</v>
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
+        <v>308</v>
+      </c>
+      <c r="F261" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G261" s="8">
         <v>309</v>
-      </c>
-      <c r="F261" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G261" s="8">
-        <v>135</v>
       </c>
       <c t="s" r="H261" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>305</v>
+        <v>41</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>259</v>
+        <v>194</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9516,17 +9516,17 @@
     </row>
     <row r="262" ht="14.25" customHeight="1">
       <c t="s" r="A262" s="6">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B262" s="7">
-        <v>982</v>
+        <v>517</v>
       </c>
       <c t="s" r="C262" s="7">
         <v>14</v>
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9535,95 +9535,95 @@
         <v>16</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>47</v>
+        <v>135</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>311</v>
+        <v>187</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>312</v>
+        <v>198</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
       <c r="M262" s="7"/>
     </row>
     <row r="263" ht="14.25" customHeight="1">
-      <c r="A263" s="6"/>
-      <c r="B263" s="7"/>
-      <c r="C263" s="7"/>
+      <c t="s" r="A263" s="6">
+        <v>13</v>
+      </c>
+      <c r="B263" s="7">
+        <v>520</v>
+      </c>
+      <c t="s" r="C263" s="7">
+        <v>14</v>
+      </c>
       <c r="D263" s="7"/>
-      <c r="E263" s="7"/>
-      <c r="F263" s="7"/>
-      <c r="G263" s="8"/>
-      <c r="H263" s="8"/>
-      <c r="I263" s="7"/>
-      <c r="J263" s="7"/>
+      <c t="s" r="E263" s="7">
+        <v>308</v>
+      </c>
+      <c r="F263" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G263" s="8">
+        <v>135</v>
+      </c>
+      <c t="s" r="H263" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I263" s="7">
+        <v>304</v>
+      </c>
+      <c t="s" r="J263" s="7">
+        <v>258</v>
+      </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
       <c r="M263" s="7"/>
     </row>
     <row r="264" ht="14.25" customHeight="1">
       <c t="s" r="A264" s="6">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B264" s="7">
-        <v>952</v>
+        <v>982</v>
       </c>
       <c t="s" r="C264" s="7">
         <v>14</v>
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="F264" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G264" s="8">
         <v>16</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>314</v>
+        <v>47</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>73</v>
+        <v>311</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
       <c r="M264" s="7"/>
     </row>
     <row r="265" ht="15" customHeight="1">
-      <c t="s" r="A265" s="6">
-        <v>13</v>
-      </c>
-      <c r="B265" s="7">
-        <v>953</v>
-      </c>
-      <c t="s" r="C265" s="7">
-        <v>14</v>
-      </c>
+      <c r="A265" s="6"/>
+      <c r="B265" s="7"/>
+      <c r="C265" s="7"/>
       <c r="D265" s="7"/>
-      <c t="s" r="E265" s="7">
-        <v>313</v>
-      </c>
-      <c r="F265" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G265" s="8">
-        <v>314</v>
-      </c>
-      <c t="s" r="H265" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I265" s="7">
-        <v>103</v>
-      </c>
-      <c t="s" r="J265" s="7">
-        <v>179</v>
-      </c>
+      <c r="E265" s="7"/>
+      <c r="F265" s="7"/>
+      <c r="G265" s="8"/>
+      <c r="H265" s="8"/>
+      <c r="I265" s="7"/>
+      <c r="J265" s="7"/>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c r="M265" s="7"/>
@@ -9633,14 +9633,14 @@
         <v>13</v>
       </c>
       <c r="B266" s="7">
-        <v>913</v>
+        <v>952</v>
       </c>
       <c t="s" r="C266" s="7">
         <v>14</v>
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F266" s="7">
         <v>320</v>
@@ -9649,13 +9649,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>265</v>
+        <v>314</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>317</v>
+        <v>73</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9666,45 +9666,63 @@
         <v>13</v>
       </c>
       <c r="B267" s="7">
-        <v>914</v>
+        <v>953</v>
       </c>
       <c t="s" r="C267" s="7">
         <v>14</v>
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F267" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c t="s" r="H267" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c r="M267" s="7"/>
     </row>
     <row r="268" ht="14.25" customHeight="1">
-      <c r="A268" s="6"/>
-      <c r="B268" s="7"/>
-      <c r="C268" s="7"/>
+      <c t="s" r="A268" s="6">
+        <v>13</v>
+      </c>
+      <c r="B268" s="7">
+        <v>913</v>
+      </c>
+      <c t="s" r="C268" s="7">
+        <v>14</v>
+      </c>
       <c r="D268" s="7"/>
-      <c r="E268" s="7"/>
-      <c r="F268" s="7"/>
-      <c r="G268" s="8"/>
-      <c r="H268" s="8"/>
-      <c r="I268" s="7"/>
-      <c r="J268" s="7"/>
+      <c t="s" r="E268" s="7">
+        <v>312</v>
+      </c>
+      <c r="F268" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G268" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H268" s="8">
+        <v>315</v>
+      </c>
+      <c t="s" r="I268" s="7">
+        <v>264</v>
+      </c>
+      <c t="s" r="J268" s="7">
+        <v>316</v>
+      </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
       <c r="M268" s="7"/>
@@ -9714,63 +9732,45 @@
         <v>13</v>
       </c>
       <c r="B269" s="7">
-        <v>339</v>
+        <v>914</v>
       </c>
       <c t="s" r="C269" s="7">
         <v>14</v>
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="F269" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G269" s="8">
-        <v>26</v>
+        <v>315</v>
       </c>
       <c t="s" r="H269" s="8">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>91</v>
+        <v>181</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
       <c r="M269" s="7"/>
     </row>
     <row r="270" ht="15" customHeight="1">
-      <c t="s" r="A270" s="6">
-        <v>13</v>
-      </c>
-      <c r="B270" s="7">
-        <v>718</v>
-      </c>
-      <c t="s" r="C270" s="7">
-        <v>14</v>
-      </c>
+      <c r="A270" s="6"/>
+      <c r="B270" s="7"/>
+      <c r="C270" s="7"/>
       <c r="D270" s="7"/>
-      <c t="s" r="E270" s="7">
-        <v>318</v>
-      </c>
-      <c r="F270" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G270" s="8">
-        <v>45</v>
-      </c>
-      <c t="s" r="H270" s="8">
-        <v>135</v>
-      </c>
-      <c t="s" r="I270" s="7">
-        <v>63</v>
-      </c>
-      <c t="s" r="J270" s="7">
-        <v>114</v>
-      </c>
+      <c r="E270" s="7"/>
+      <c r="F270" s="7"/>
+      <c r="G270" s="8"/>
+      <c r="H270" s="8"/>
+      <c r="I270" s="7"/>
+      <c r="J270" s="7"/>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
       <c r="M270" s="7"/>
@@ -9780,29 +9780,29 @@
         <v>13</v>
       </c>
       <c r="B271" s="7">
-        <v>719</v>
+        <v>339</v>
       </c>
       <c t="s" r="C271" s="7">
         <v>14</v>
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G271" s="8">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c t="s" r="H271" s="8">
         <v>45</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>184</v>
+        <v>106</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>319</v>
+        <v>91</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9813,14 +9813,14 @@
         <v>13</v>
       </c>
       <c r="B272" s="7">
-        <v>452</v>
+        <v>718</v>
       </c>
       <c t="s" r="C272" s="7">
         <v>14</v>
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -9829,13 +9829,13 @@
         <v>45</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>123</v>
+        <v>63</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>320</v>
+        <v>114</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9846,29 +9846,29 @@
         <v>13</v>
       </c>
       <c r="B273" s="7">
-        <v>441</v>
+        <v>719</v>
       </c>
       <c t="s" r="C273" s="7">
         <v>14</v>
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G273" s="8">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c t="s" r="H273" s="8">
         <v>45</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>67</v>
+        <v>318</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -9879,14 +9879,14 @@
         <v>13</v>
       </c>
       <c r="B274" s="7">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c t="s" r="C274" s="7">
         <v>14</v>
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -9898,10 +9898,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>57</v>
+        <v>123</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>230</v>
+        <v>319</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -9912,14 +9912,14 @@
         <v>13</v>
       </c>
       <c r="B275" s="7">
-        <v>167</v>
+        <v>441</v>
       </c>
       <c t="s" r="C275" s="7">
         <v>14</v>
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -9928,29 +9928,47 @@
         <v>16</v>
       </c>
       <c t="s" r="H275" s="8">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>321</v>
+        <v>196</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>322</v>
+        <v>67</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
       <c r="M275" s="7"/>
     </row>
     <row r="276" ht="14.25" customHeight="1">
-      <c r="A276" s="6"/>
-      <c r="B276" s="7"/>
-      <c r="C276" s="7"/>
+      <c t="s" r="A276" s="6">
+        <v>13</v>
+      </c>
+      <c r="B276" s="7">
+        <v>442</v>
+      </c>
+      <c t="s" r="C276" s="7">
+        <v>14</v>
+      </c>
       <c r="D276" s="7"/>
-      <c r="E276" s="7"/>
-      <c r="F276" s="7"/>
-      <c r="G276" s="8"/>
-      <c r="H276" s="8"/>
-      <c r="I276" s="7"/>
-      <c r="J276" s="7"/>
+      <c t="s" r="E276" s="7">
+        <v>317</v>
+      </c>
+      <c r="F276" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G276" s="8">
+        <v>45</v>
+      </c>
+      <c t="s" r="H276" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I276" s="7">
+        <v>57</v>
+      </c>
+      <c t="s" r="J276" s="7">
+        <v>229</v>
+      </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
       <c r="M276" s="7"/>
@@ -9960,63 +9978,45 @@
         <v>13</v>
       </c>
       <c r="B277" s="7">
-        <v>809</v>
+        <v>167</v>
       </c>
       <c t="s" r="C277" s="7">
         <v>14</v>
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G277" s="8">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c t="s" r="H277" s="8">
-        <v>324</v>
+        <v>26</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>91</v>
+        <v>320</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>136</v>
+        <v>321</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
       <c r="M277" s="7"/>
     </row>
     <row r="278" ht="14.25" customHeight="1">
-      <c t="s" r="A278" s="6">
-        <v>13</v>
-      </c>
-      <c r="B278" s="7">
-        <v>808</v>
-      </c>
-      <c t="s" r="C278" s="7">
-        <v>14</v>
-      </c>
+      <c r="A278" s="6"/>
+      <c r="B278" s="7"/>
+      <c r="C278" s="7"/>
       <c r="D278" s="7"/>
-      <c t="s" r="E278" s="7">
-        <v>323</v>
-      </c>
-      <c r="F278" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G278" s="8">
-        <v>324</v>
-      </c>
-      <c t="s" r="H278" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="I278" s="7">
-        <v>97</v>
-      </c>
-      <c t="s" r="J278" s="7">
-        <v>211</v>
-      </c>
+      <c r="E278" s="7"/>
+      <c r="F278" s="7"/>
+      <c r="G278" s="8"/>
+      <c r="H278" s="8"/>
+      <c r="I278" s="7"/>
+      <c r="J278" s="7"/>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
       <c r="M278" s="7"/>
@@ -10026,14 +10026,14 @@
         <v>13</v>
       </c>
       <c r="B279" s="7">
-        <v>327</v>
+        <v>849</v>
       </c>
       <c t="s" r="C279" s="7">
         <v>14</v>
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -10042,13 +10042,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>99</v>
+        <v>18</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -10059,29 +10059,29 @@
         <v>13</v>
       </c>
       <c r="B280" s="7">
-        <v>326</v>
+        <v>848</v>
       </c>
       <c t="s" r="C280" s="7">
         <v>14</v>
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>157</v>
+        <v>123</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10092,29 +10092,29 @@
         <v>13</v>
       </c>
       <c r="B281" s="7">
-        <v>352</v>
+        <v>262</v>
       </c>
       <c t="s" r="C281" s="7">
         <v>14</v>
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
+        <v>322</v>
+      </c>
+      <c r="F281" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G281" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H281" s="8">
+        <v>130</v>
+      </c>
+      <c t="s" r="I281" s="7">
+        <v>75</v>
+      </c>
+      <c t="s" r="J281" s="7">
         <v>323</v>
-      </c>
-      <c r="F281" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G281" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="H281" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="I281" s="7">
-        <v>34</v>
-      </c>
-      <c t="s" r="J281" s="7">
-        <v>44</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10125,29 +10125,29 @@
         <v>13</v>
       </c>
       <c r="B282" s="7">
-        <v>353</v>
+        <v>263</v>
       </c>
       <c t="s" r="C282" s="7">
         <v>14</v>
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G282" s="8">
-        <v>27</v>
+        <v>130</v>
       </c>
       <c t="s" r="H282" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>159</v>
+        <v>324</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10165,7 +10165,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
@@ -10327,7 +10327,7 @@
         <v>326</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -10360,7 +10360,7 @@
         <v>122</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10468,13 +10468,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H293" s="8">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c t="s" r="I293" s="7">
         <v>114</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10498,13 +10498,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c t="s" r="H294" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c t="s" r="J294" s="7">
         <v>20</v>
@@ -10537,17 +10537,17 @@
         <v>209</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c t="s" r="K295" s="7">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L295" s="7"/>
       <c t="s" r="M295" s="7">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="296" ht="14.25" customHeight="1">
@@ -10580,7 +10580,7 @@
         <v>330</v>
       </c>
       <c t="s" r="K296" s="7">
-        <v>147</v>
+        <v>323</v>
       </c>
       <c r="L296" s="7"/>
       <c t="s" r="M296" s="7">
@@ -10626,7 +10626,7 @@
         <v>117</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c t="s" r="J298" s="7">
         <v>52</v>
@@ -10695,7 +10695,7 @@
         <v>333</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10728,7 +10728,7 @@
         <v>194</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10761,7 +10761,7 @@
         <v>141</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>147</v>
+        <v>323</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10791,10 +10791,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>148</v>
+        <v>324</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
@@ -10836,10 +10836,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H305" s="8">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c t="s" r="J305" s="7">
         <v>134</v>
@@ -10866,7 +10866,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G306" s="8">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c t="s" r="H306" s="8">
         <v>135</v>
@@ -10875,7 +10875,7 @@
         <v>335</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10974,7 +10974,7 @@
         <v>181</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c t="s" r="K309" s="7">
         <v>126</v>
@@ -11020,7 +11020,7 @@
         <v>26</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c t="s" r="I311" s="7">
         <v>338</v>
@@ -11050,7 +11050,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>26</v>
@@ -11086,7 +11086,7 @@
         <v>26</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c t="s" r="I313" s="7">
         <v>54</v>
@@ -11116,16 +11116,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G314" s="8">
+        <v>263</v>
+      </c>
+      <c t="s" r="H314" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="I314" s="7">
+        <v>227</v>
+      </c>
+      <c t="s" r="J314" s="7">
         <v>264</v>
-      </c>
-      <c t="s" r="H314" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="I314" s="7">
-        <v>228</v>
-      </c>
-      <c t="s" r="J314" s="7">
-        <v>265</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11188,7 +11188,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c t="s" r="J316" s="7">
         <v>174</v>
@@ -11239,7 +11239,7 @@
         <v>39</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11338,7 +11338,7 @@
         <v>104</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11368,10 +11368,10 @@
         <v>343</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11482,7 +11482,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c t="s" r="J326" s="7">
         <v>37</v>
@@ -11581,10 +11581,10 @@
         <v>347</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>146</v>
+        <v>241</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11614,10 +11614,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11647,10 +11647,10 @@
         <v>347</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>148</v>
+        <v>324</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11683,7 +11683,7 @@
         <v>330</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11728,7 +11728,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c t="s" r="J334" s="7">
         <v>350</v>
@@ -11761,10 +11761,10 @@
         <v>351</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -11824,7 +11824,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H337" s="8">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c t="s" r="I337" s="7">
         <v>125</v>
@@ -11854,7 +11854,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G338" s="8">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c t="s" r="H338" s="8">
         <v>16</v>
@@ -11908,7 +11908,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c t="s" r="J340" s="7">
         <v>53</v>
@@ -11941,7 +11941,7 @@
         <v>83</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c t="s" r="J341" s="7">
         <v>34</v>
@@ -11977,7 +11977,7 @@
         <v>44</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -12055,7 +12055,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="J345" s="7">
         <v>123</v>
@@ -12088,7 +12088,7 @@
         <v>117</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c t="s" r="J346" s="7">
         <v>166</v>
@@ -12121,7 +12121,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c t="s" r="J347" s="7">
         <v>204</v>
@@ -12271,7 +12271,7 @@
         <v>91</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -12301,7 +12301,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="J353" s="7">
         <v>72</v>
@@ -12367,7 +12367,7 @@
         <v>135</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c t="s" r="J355" s="7">
         <v>20</v>
@@ -12403,7 +12403,7 @@
         <v>326</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12550,7 +12550,7 @@
         <v>178</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12658,13 +12658,13 @@
         <v>121</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c t="s" r="I365" s="7">
         <v>171</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -12688,16 +12688,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c t="s" r="H366" s="8">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c t="s" r="I366" s="7">
         <v>179</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12721,13 +12721,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G367" s="8">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c t="s" r="J367" s="7">
         <v>364</v>
@@ -12754,7 +12754,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c t="s" r="H368" s="8">
         <v>121</v>
@@ -12763,7 +12763,7 @@
         <v>365</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12877,7 +12877,7 @@
         <v>40</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12907,10 +12907,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12940,7 +12940,7 @@
         <v>135</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c t="s" r="J374" s="7">
         <v>104</v>
@@ -13009,7 +13009,7 @@
         <v>182</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -13120,7 +13120,7 @@
         <v>369</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c t="s" r="J380" s="7">
         <v>118</v>
@@ -13153,7 +13153,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c t="s" r="J381" s="7">
         <v>370</v>
@@ -13234,7 +13234,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c t="s" r="J384" s="7">
         <v>39</v>
@@ -13303,7 +13303,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13333,10 +13333,10 @@
         <v>372</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13366,7 +13366,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c t="s" r="J388" s="7">
         <v>181</v>
@@ -13414,7 +13414,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c t="s" r="J390" s="7">
         <v>94</v>
@@ -13516,7 +13516,7 @@
         <v>42</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13624,10 +13624,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H397" s="8">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c t="s" r="J397" s="7">
         <v>91</v>
@@ -13654,7 +13654,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G398" s="8">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c t="s" r="H398" s="8">
         <v>173</v>
@@ -13663,7 +13663,7 @@
         <v>92</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13690,7 +13690,7 @@
         <v>173</v>
       </c>
       <c t="s" r="H399" s="8">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c t="s" r="I399" s="7">
         <v>72</v>
@@ -13720,7 +13720,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G400" s="8">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c t="s" r="H400" s="8">
         <v>16</v>
@@ -13729,7 +13729,7 @@
         <v>53</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -13762,7 +13762,7 @@
         <v>194</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -13825,7 +13825,7 @@
         <v>377</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>148</v>
+        <v>324</v>
       </c>
       <c t="s" r="J403" s="7">
         <v>48</v>
@@ -13942,7 +13942,7 @@
         <v>191</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -13969,13 +13969,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -13999,16 +13999,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -14035,7 +14035,7 @@
         <v>26</v>
       </c>
       <c t="s" r="H410" s="8">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c t="s" r="I410" s="7">
         <v>34</v>
@@ -14065,7 +14065,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G411" s="8">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c t="s" r="H411" s="8">
         <v>26</v>
@@ -14074,7 +14074,7 @@
         <v>118</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -14119,10 +14119,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
@@ -14188,7 +14188,7 @@
         <v>20</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
@@ -14233,10 +14233,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -14269,7 +14269,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14317,7 +14317,7 @@
         <v>132</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14398,7 +14398,7 @@
         <v>335</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -14431,7 +14431,7 @@
         <v>181</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
@@ -14542,7 +14542,7 @@
         <v>81</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c t="s" r="J428" s="7">
         <v>388</v>
@@ -14623,10 +14623,10 @@
         <v>81</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
@@ -14659,7 +14659,7 @@
         <v>53</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
@@ -14689,7 +14689,7 @@
         <v>81</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="J433" s="7">
         <v>391</v>
@@ -14770,10 +14770,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
